--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_appends.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_appends.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_appends" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4667" uniqueCount="1399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4727" uniqueCount="1444">
   <si>
     <r>
       <rPr>
@@ -3231,6 +3236,141 @@
   </si>
   <si>
     <t>卓越的 地之项链</t>
+  </si>
+  <si>
+    <t>20401881</t>
+  </si>
+  <si>
+    <t>圣天使骑士之盔</t>
+  </si>
+  <si>
+    <t>20401882</t>
+  </si>
+  <si>
+    <t>圣天使骑士之铠</t>
+  </si>
+  <si>
+    <t>20401883</t>
+  </si>
+  <si>
+    <t>圣天使骑士护腿</t>
+  </si>
+  <si>
+    <t>20401884</t>
+  </si>
+  <si>
+    <t>圣天使骑士靴子</t>
+  </si>
+  <si>
+    <t>20401885</t>
+  </si>
+  <si>
+    <t>圣天使骑士护手</t>
+  </si>
+  <si>
+    <t>20402881</t>
+  </si>
+  <si>
+    <t>圣天使魔法之盔</t>
+  </si>
+  <si>
+    <t>20402882</t>
+  </si>
+  <si>
+    <t>圣天使魔法之铠</t>
+  </si>
+  <si>
+    <t>20402883</t>
+  </si>
+  <si>
+    <t>圣天使魔法护腿</t>
+  </si>
+  <si>
+    <t>20402884</t>
+  </si>
+  <si>
+    <t>圣天使魔法靴子</t>
+  </si>
+  <si>
+    <t>20402885</t>
+  </si>
+  <si>
+    <t>圣天使魔法护手</t>
+  </si>
+  <si>
+    <t>20403881</t>
+  </si>
+  <si>
+    <t>圣天使精灵之盔</t>
+  </si>
+  <si>
+    <t>20403882</t>
+  </si>
+  <si>
+    <t>圣天使精灵之铠</t>
+  </si>
+  <si>
+    <t>20403883</t>
+  </si>
+  <si>
+    <t>圣天使精灵护腿</t>
+  </si>
+  <si>
+    <t>20403884</t>
+  </si>
+  <si>
+    <t>圣天使精灵靴子</t>
+  </si>
+  <si>
+    <t>20403885</t>
+  </si>
+  <si>
+    <t>圣天使精灵护手</t>
+  </si>
+  <si>
+    <t>2040188199</t>
+  </si>
+  <si>
+    <t>2040188299</t>
+  </si>
+  <si>
+    <t>2040188399</t>
+  </si>
+  <si>
+    <t>2040188499</t>
+  </si>
+  <si>
+    <t>2040188599</t>
+  </si>
+  <si>
+    <t>2040288199</t>
+  </si>
+  <si>
+    <t>2040288299</t>
+  </si>
+  <si>
+    <t>2040288399</t>
+  </si>
+  <si>
+    <t>2040288499</t>
+  </si>
+  <si>
+    <t>2040288599</t>
+  </si>
+  <si>
+    <t>2040388199</t>
+  </si>
+  <si>
+    <t>2040388299</t>
+  </si>
+  <si>
+    <t>2040388399</t>
+  </si>
+  <si>
+    <t>2040388499</t>
+  </si>
+  <si>
+    <t>2040388599</t>
   </si>
   <si>
     <t>虚伪之剑</t>
@@ -5035,7 +5175,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5133,6 +5273,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5491,7 +5633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2042"/>
+  <dimension ref="A1:M2071"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.2857142857143" style="4" customWidth="1"/>
@@ -44817,738 +44959,1545 @@
       </c>
     </row>
     <row r="2042" spans="1:6">
-      <c r="A2042" s="29"/>
-      <c r="B2042" s="29"/>
+      <c r="A2042" s="37" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B2042" s="38" t="s">
+        <v>1029</v>
+      </c>
       <c r="C2042" s="29"/>
+      <c r="D2042" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2042" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2042" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:6">
+      <c r="A2043" s="37" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B2043" s="37" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2043" s="29"/>
+      <c r="D2043" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2043" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2043" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:6">
+      <c r="A2044" s="37" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B2044" s="37" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C2044" s="29"/>
+      <c r="D2044" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2044" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2044" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:6">
+      <c r="A2045" s="37" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B2045" s="37" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C2045" s="29"/>
+      <c r="D2045" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2045" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2045" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:6">
+      <c r="A2046" s="37" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B2046" s="32" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C2046" s="29"/>
+      <c r="D2046" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2046" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2046" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:6">
+      <c r="A2047" s="37" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B2047" s="38" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C2047" s="29"/>
+      <c r="D2047" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2047" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2047" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:6">
+      <c r="A2048" s="37" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B2048" s="37" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C2048" s="29"/>
+      <c r="D2048" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2048" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2048" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:6">
+      <c r="A2049" s="37" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B2049" s="37" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C2049" s="29"/>
+      <c r="D2049" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2049" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2049" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:6">
+      <c r="A2050" s="37" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B2050" s="37" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C2050" s="29"/>
+      <c r="D2050" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2050" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2050" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:6">
+      <c r="A2051" s="37" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2051" s="37" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C2051" s="29"/>
+      <c r="D2051" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2051" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2051" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:6">
+      <c r="A2052" s="37" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B2052" s="37" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C2052" s="29"/>
+      <c r="D2052" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2052" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2052" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:6">
+      <c r="A2053" s="37" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B2053" s="37" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C2053" s="29"/>
+      <c r="D2053" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2053" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2053" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:6">
+      <c r="A2054" s="37" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B2054" s="37" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C2054" s="29"/>
+      <c r="D2054" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2054" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2054" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:6">
+      <c r="A2055" s="37" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B2055" s="37" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C2055" s="29"/>
+      <c r="D2055" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2055" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2055" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:6">
+      <c r="A2056" s="37" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B2056" s="37" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C2056" s="29"/>
+      <c r="D2056" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2056" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2056" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:6">
+      <c r="A2057" s="37" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B2057" s="38" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C2057" s="29"/>
+      <c r="D2057" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2057" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2057" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:6">
+      <c r="A2058" s="37" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B2058" s="37" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C2058" s="29"/>
+      <c r="D2058" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2058" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2058" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:6">
+      <c r="A2059" s="37" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B2059" s="37" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C2059" s="29"/>
+      <c r="D2059" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2059" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2059" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:6">
+      <c r="A2060" s="37" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B2060" s="37" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C2060" s="29"/>
+      <c r="D2060" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2060" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2060" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:6">
+      <c r="A2061" s="37" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B2061" s="32" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C2061" s="29"/>
+      <c r="D2061" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2061" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2061" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:6">
+      <c r="A2062" s="37" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B2062" s="38" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C2062" s="29"/>
+      <c r="D2062" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2062" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2062" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:6">
+      <c r="A2063" s="37" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B2063" s="37" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C2063" s="29"/>
+      <c r="D2063" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2063" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2063" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:6">
+      <c r="A2064" s="37" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B2064" s="37" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C2064" s="29"/>
+      <c r="D2064" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2064" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2064" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:6">
+      <c r="A2065" s="37" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B2065" s="37" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C2065" s="29"/>
+      <c r="D2065" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2065" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2065" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:6">
+      <c r="A2066" s="37" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B2066" s="37" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C2066" s="29"/>
+      <c r="D2066" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2066" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2066" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:6">
+      <c r="A2067" s="37" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B2067" s="37" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C2067" s="29"/>
+      <c r="D2067" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2067" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2067" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:6">
+      <c r="A2068" s="37" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B2068" s="37" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C2068" s="29"/>
+      <c r="D2068" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2068" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2068" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:6">
+      <c r="A2069" s="37" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B2069" s="37" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C2069" s="29"/>
+      <c r="D2069" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2069" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2069" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:6">
+      <c r="A2070" s="37" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B2070" s="37" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C2070" s="29"/>
+      <c r="D2070" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2070" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2070" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:6">
+      <c r="A2071" s="37" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B2071" s="37" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C2071" s="29"/>
+      <c r="D2071" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2071" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2071" s="5">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:F2041" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A719">
-    <cfRule type="duplicateValues" dxfId="0" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="708"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A996">
-    <cfRule type="duplicateValues" dxfId="0" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="307"/>
-    <cfRule type="cellIs" dxfId="1" priority="308" operator="equal">
+    <cfRule type="duplicateValues" dxfId="0" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="700"/>
+    <cfRule type="cellIs" dxfId="1" priority="701" operator="equal">
       <formula>1067000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1206">
-    <cfRule type="duplicateValues" dxfId="0" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="304"/>
-    <cfRule type="cellIs" dxfId="1" priority="305" operator="equal">
+    <cfRule type="duplicateValues" dxfId="0" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="697"/>
+    <cfRule type="cellIs" dxfId="1" priority="698" operator="equal">
       <formula>1067000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1419">
-    <cfRule type="cellIs" dxfId="2" priority="299" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="692" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="689"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1508">
-    <cfRule type="duplicateValues" dxfId="0" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="664"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1509">
-    <cfRule type="duplicateValues" dxfId="0" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="662"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1510">
-    <cfRule type="duplicateValues" dxfId="0" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="658"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1511">
-    <cfRule type="duplicateValues" dxfId="0" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1512">
-    <cfRule type="duplicateValues" dxfId="0" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="654"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1557">
-    <cfRule type="duplicateValues" dxfId="3" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="632"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1558">
-    <cfRule type="duplicateValues" dxfId="3" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="631"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1559">
-    <cfRule type="duplicateValues" dxfId="3" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="638"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1560">
-    <cfRule type="duplicateValues" dxfId="3" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="630"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1561">
-    <cfRule type="duplicateValues" dxfId="3" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="629"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1562">
-    <cfRule type="duplicateValues" dxfId="3" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1563">
-    <cfRule type="duplicateValues" dxfId="3" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="628"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1564">
-    <cfRule type="duplicateValues" dxfId="3" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="636"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1565">
-    <cfRule type="duplicateValues" dxfId="3" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1566">
-    <cfRule type="duplicateValues" dxfId="3" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="637"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1567">
-    <cfRule type="duplicateValues" dxfId="3" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1568">
-    <cfRule type="duplicateValues" dxfId="3" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="625"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1569">
-    <cfRule type="duplicateValues" dxfId="3" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="633"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1570">
-    <cfRule type="duplicateValues" dxfId="3" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="624"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1571">
-    <cfRule type="duplicateValues" dxfId="3" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="635"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1572">
-    <cfRule type="duplicateValues" dxfId="3" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="623"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1573">
-    <cfRule type="duplicateValues" dxfId="3" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1574">
-    <cfRule type="duplicateValues" dxfId="3" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="620"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1575">
-    <cfRule type="duplicateValues" dxfId="3" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="614"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1576">
-    <cfRule type="duplicateValues" dxfId="3" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="618"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1577">
-    <cfRule type="duplicateValues" dxfId="3" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="617"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1578">
-    <cfRule type="duplicateValues" dxfId="3" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="611"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1579">
-    <cfRule type="duplicateValues" dxfId="3" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="619"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1580">
-    <cfRule type="duplicateValues" dxfId="3" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="613"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1581">
-    <cfRule type="duplicateValues" dxfId="3" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1582">
-    <cfRule type="duplicateValues" dxfId="3" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="615"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1648">
-    <cfRule type="duplicateValues" dxfId="3" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="607"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1649">
-    <cfRule type="duplicateValues" dxfId="3" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="606"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1650">
-    <cfRule type="duplicateValues" dxfId="3" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1651">
-    <cfRule type="duplicateValues" dxfId="3" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1652">
-    <cfRule type="duplicateValues" dxfId="3" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="603"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1653">
-    <cfRule type="duplicateValues" dxfId="3" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="602"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1654">
-    <cfRule type="duplicateValues" dxfId="3" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1683">
-    <cfRule type="duplicateValues" dxfId="3" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1696">
-    <cfRule type="duplicateValues" dxfId="3" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1699">
-    <cfRule type="duplicateValues" dxfId="3" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1702">
-    <cfRule type="duplicateValues" dxfId="3" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1705">
-    <cfRule type="duplicateValues" dxfId="3" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1708">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="394"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1711">
-    <cfRule type="duplicateValues" dxfId="3" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="586"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1714">
-    <cfRule type="duplicateValues" dxfId="3" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="588"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1717">
-    <cfRule type="duplicateValues" dxfId="3" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="585"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1720">
-    <cfRule type="duplicateValues" dxfId="3" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1723">
-    <cfRule type="duplicateValues" dxfId="3" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1854">
-    <cfRule type="duplicateValues" dxfId="3" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1854">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="433"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1858">
+    <cfRule type="duplicateValues" dxfId="0" priority="430"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1859">
+    <cfRule type="duplicateValues" dxfId="0" priority="431"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1861">
+    <cfRule type="duplicateValues" dxfId="0" priority="429"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1862">
+    <cfRule type="duplicateValues" dxfId="0" priority="428"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1863">
+    <cfRule type="duplicateValues" dxfId="3" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="518"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1863">
+    <cfRule type="duplicateValues" dxfId="0" priority="427"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1867">
+    <cfRule type="duplicateValues" dxfId="0" priority="424"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1868">
+    <cfRule type="duplicateValues" dxfId="0" priority="425"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1870">
+    <cfRule type="duplicateValues" dxfId="0" priority="423"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1871">
+    <cfRule type="duplicateValues" dxfId="0" priority="422"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1872">
+    <cfRule type="duplicateValues" dxfId="3" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="514"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1880">
+    <cfRule type="duplicateValues" dxfId="0" priority="419"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1881">
+    <cfRule type="duplicateValues" dxfId="3" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="510"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1889">
+    <cfRule type="duplicateValues" dxfId="0" priority="416"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1990">
+    <cfRule type="duplicateValues" dxfId="3" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="448"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1990">
+    <cfRule type="duplicateValues" dxfId="0" priority="415"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1994">
+    <cfRule type="duplicateValues" dxfId="0" priority="412"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1995">
+    <cfRule type="duplicateValues" dxfId="0" priority="413"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1997">
+    <cfRule type="duplicateValues" dxfId="0" priority="411"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1998">
+    <cfRule type="duplicateValues" dxfId="0" priority="410"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1999">
+    <cfRule type="duplicateValues" dxfId="3" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="444"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1999">
+    <cfRule type="duplicateValues" dxfId="0" priority="409"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2003">
+    <cfRule type="duplicateValues" dxfId="0" priority="406"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2004">
+    <cfRule type="duplicateValues" dxfId="0" priority="407"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2006">
+    <cfRule type="duplicateValues" dxfId="0" priority="405"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2007">
+    <cfRule type="duplicateValues" dxfId="0" priority="404"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2008">
+    <cfRule type="duplicateValues" dxfId="3" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="440"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2016">
+    <cfRule type="duplicateValues" dxfId="0" priority="401"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2017">
+    <cfRule type="duplicateValues" dxfId="3" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="436"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2025">
+    <cfRule type="duplicateValues" dxfId="0" priority="398"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2042">
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2043">
+    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+    <cfRule type="cellIs" dxfId="1" priority="136" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2044">
+    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+    <cfRule type="cellIs" dxfId="1" priority="132" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2045">
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+    <cfRule type="cellIs" dxfId="1" priority="128" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2046">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+    <cfRule type="cellIs" dxfId="1" priority="124" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2047">
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
+    <cfRule type="cellIs" dxfId="1" priority="116" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2048">
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+    <cfRule type="cellIs" dxfId="1" priority="112" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2049">
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+    <cfRule type="cellIs" dxfId="1" priority="108" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2050">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+    <cfRule type="cellIs" dxfId="1" priority="104" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2051">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+    <cfRule type="cellIs" dxfId="1" priority="100" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2052">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+    <cfRule type="cellIs" dxfId="1" priority="92" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2053">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+    <cfRule type="cellIs" dxfId="1" priority="88" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2054">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+    <cfRule type="cellIs" dxfId="1" priority="84" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2055">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+    <cfRule type="cellIs" dxfId="1" priority="80" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2056">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+    <cfRule type="cellIs" dxfId="1" priority="76" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2057">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2058">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+    <cfRule type="cellIs" dxfId="1" priority="67" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2059">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+    <cfRule type="cellIs" dxfId="1" priority="63" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2060">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="cellIs" dxfId="1" priority="59" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2061">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+    <cfRule type="cellIs" dxfId="1" priority="55" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2062">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+    <cfRule type="cellIs" dxfId="1" priority="51" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2063">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+    <cfRule type="cellIs" dxfId="1" priority="47" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2064">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+    <cfRule type="cellIs" dxfId="1" priority="43" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2065">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+    <cfRule type="cellIs" dxfId="1" priority="39" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
     <cfRule type="duplicateValues" dxfId="0" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1859">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  <conditionalFormatting sqref="B2066">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1861">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1862">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1863">
-    <cfRule type="duplicateValues" dxfId="3" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1863">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1867">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1868">
+  <conditionalFormatting sqref="B2067">
     <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1870">
+    <cfRule type="cellIs" dxfId="1" priority="31" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1871">
     <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1872">
-    <cfRule type="duplicateValues" dxfId="3" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+  <conditionalFormatting sqref="B2068">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="cellIs" dxfId="1" priority="27" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1880">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  <conditionalFormatting sqref="B2069">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1881">
-    <cfRule type="duplicateValues" dxfId="3" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1889">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1990">
-    <cfRule type="duplicateValues" dxfId="3" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1990">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1994">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1995">
+  <conditionalFormatting sqref="B2070">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1997">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1998">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1999">
-    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1999">
+  <conditionalFormatting sqref="B2071">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2003">
+    <cfRule type="cellIs" dxfId="1" priority="15" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2004">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2006">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2007">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2008">
-    <cfRule type="duplicateValues" dxfId="3" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2016">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2017">
-    <cfRule type="duplicateValues" dxfId="3" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2025">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2042">
-    <cfRule type="duplicateValues" dxfId="0" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="201"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A698:A717">
-    <cfRule type="duplicateValues" dxfId="0" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A997:A1028">
-    <cfRule type="duplicateValues" dxfId="0" priority="310"/>
-    <cfRule type="cellIs" dxfId="1" priority="311" operator="equal">
+    <cfRule type="duplicateValues" dxfId="0" priority="703"/>
+    <cfRule type="cellIs" dxfId="1" priority="704" operator="equal">
       <formula>1067000000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1420:A1431">
-    <cfRule type="duplicateValues" dxfId="0" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="688"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1432:A1437">
-    <cfRule type="duplicateValues" dxfId="0" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="686"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1438:A1451">
-    <cfRule type="duplicateValues" dxfId="0" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="684"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1452:A1457">
-    <cfRule type="duplicateValues" dxfId="0" priority="288"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1458:A1467">
-    <cfRule type="duplicateValues" dxfId="0" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="680"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1478:A1485">
-    <cfRule type="duplicateValues" dxfId="0" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1486:A1497">
-    <cfRule type="duplicateValues" dxfId="0" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="668"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1498:A1507">
-    <cfRule type="duplicateValues" dxfId="0" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="666"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1513:A1522">
-    <cfRule type="duplicateValues" dxfId="0" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1523:A1534">
-    <cfRule type="duplicateValues" dxfId="0" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="650"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1535:A1536">
-    <cfRule type="duplicateValues" dxfId="0" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="648"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1537:A1540">
-    <cfRule type="duplicateValues" dxfId="0" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1541:A1546">
-    <cfRule type="duplicateValues" dxfId="0" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="644"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1547:A1554">
-    <cfRule type="duplicateValues" dxfId="0" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1555:A1556">
-    <cfRule type="duplicateValues" dxfId="0" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="640"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1573:A1582">
-    <cfRule type="duplicateValues" dxfId="0" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="610"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1583:A1647">
-    <cfRule type="duplicateValues" dxfId="3" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="608"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1648:A1653">
-    <cfRule type="duplicateValues" dxfId="0" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="601"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1670:A1673">
-    <cfRule type="duplicateValues" dxfId="3" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="592"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1754:A1763">
-    <cfRule type="duplicateValues" dxfId="3" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="566"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1764:A1773">
-    <cfRule type="duplicateValues" dxfId="3" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1774:A1778">
-    <cfRule type="duplicateValues" dxfId="3" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1779:A1783">
-    <cfRule type="duplicateValues" dxfId="3" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="562"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1784:A1788">
-    <cfRule type="duplicateValues" dxfId="3" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1789:A1793">
-    <cfRule type="duplicateValues" dxfId="3" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="558"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1794:A1798">
-    <cfRule type="duplicateValues" dxfId="3" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="556"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1799:A1803">
-    <cfRule type="duplicateValues" dxfId="3" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="554"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1804:A1808">
-    <cfRule type="duplicateValues" dxfId="3" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1809:A1813">
-    <cfRule type="duplicateValues" dxfId="3" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="540"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1814:A1818">
-    <cfRule type="duplicateValues" dxfId="3" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1819:A1823">
-    <cfRule type="duplicateValues" dxfId="3" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1824:A1828">
-    <cfRule type="duplicateValues" dxfId="3" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1829:A1833">
-    <cfRule type="duplicateValues" dxfId="3" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="532"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1834:A1838">
-    <cfRule type="duplicateValues" dxfId="3" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1839:A1843">
-    <cfRule type="duplicateValues" dxfId="3" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="528"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1844:A1848">
-    <cfRule type="duplicateValues" dxfId="3" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1849:A1853">
-    <cfRule type="duplicateValues" dxfId="3" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1855:A1862">
-    <cfRule type="duplicateValues" dxfId="3" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="520"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1864:A1871">
-    <cfRule type="duplicateValues" dxfId="3" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1873:A1880">
-    <cfRule type="duplicateValues" dxfId="3" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="512"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1882:A1889">
-    <cfRule type="duplicateValues" dxfId="3" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1890:A1899">
-    <cfRule type="duplicateValues" dxfId="3" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="483"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="482"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1900:A1909">
-    <cfRule type="duplicateValues" dxfId="3" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="484"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1910:A1914">
-    <cfRule type="duplicateValues" dxfId="3" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1915:A1919">
-    <cfRule type="duplicateValues" dxfId="3" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="478"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1920:A1924">
-    <cfRule type="duplicateValues" dxfId="3" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="476"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1925:A1929">
-    <cfRule type="duplicateValues" dxfId="3" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="474"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1930:A1934">
-    <cfRule type="duplicateValues" dxfId="3" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="472"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1935:A1939">
-    <cfRule type="duplicateValues" dxfId="3" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="470"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1940:A1944">
-    <cfRule type="duplicateValues" dxfId="3" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="468"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1945:A1949">
-    <cfRule type="duplicateValues" dxfId="3" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="466"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1950:A1954">
-    <cfRule type="duplicateValues" dxfId="3" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="464"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1955:A1959">
-    <cfRule type="duplicateValues" dxfId="3" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="462"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1960:A1964">
-    <cfRule type="duplicateValues" dxfId="3" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="460"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1965:A1969">
-    <cfRule type="duplicateValues" dxfId="3" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="458"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1970:A1974">
-    <cfRule type="duplicateValues" dxfId="3" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="457"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="456"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1975:A1979">
-    <cfRule type="duplicateValues" dxfId="3" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="454"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1980:A1984">
-    <cfRule type="duplicateValues" dxfId="3" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1985:A1989">
-    <cfRule type="duplicateValues" dxfId="3" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="452"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1991:A1998">
-    <cfRule type="duplicateValues" dxfId="3" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="446"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2000:A2007">
-    <cfRule type="duplicateValues" dxfId="3" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="443"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="442"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2009:A2016">
-    <cfRule type="duplicateValues" dxfId="3" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2018:A2025">
-    <cfRule type="duplicateValues" dxfId="3" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="434"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2026:A2033">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="397"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2034:A2041">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="396"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2042:A2046">
+    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+    <cfRule type="cellIs" dxfId="1" priority="120" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2047:A2051">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+    <cfRule type="cellIs" dxfId="1" priority="96" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2052:A2056">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+    <cfRule type="cellIs" dxfId="1" priority="72" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2057:A2061">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2062:A2066">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2067:A2071">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>56510500</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1329:B1412">
-    <cfRule type="duplicateValues" dxfId="0" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="710"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1754:B1758">
-    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1774:B1778">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1779:B1783">
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1784:B1788">
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="506"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1794:B1798">
-    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1799:B1803">
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="502"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1804:B1808">
-    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1809:B1813">
-    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1814:B1818">
-    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="551"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1819:B1823">
-    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1824:B1828">
-    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="549"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1829:B1833">
-    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1834:B1838">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="547"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1839:B1843">
-    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="546"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1844:B1848">
-    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="545"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1849:B1853">
-    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="544"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1872:B1874">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1875:B1879">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1881:B1883">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1884:B1888">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1890:B1894">
-    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1910:B1914">
-    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1915:B1919">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="488"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1920:B1924">
-    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="490"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1930:B1934">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1935:B1939">
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="486"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1940:B1944">
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1945:B1949">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="500"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1950:B1954">
-    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1955:B1959">
-    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1960:B1964">
-    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="497"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1965:B1969">
-    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1970:B1974">
-    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1975:B1979">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="494"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1980:B1984">
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="493"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1985:B1989">
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="492"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2008:B2010">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="403"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2011:B2015">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="402"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2017:B2019">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2020:B2024">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="399"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A995 A1029:A1205 A1207:A1418 A2043:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="312"/>
-    <cfRule type="cellIs" dxfId="1" priority="313" operator="equal">
+  <conditionalFormatting sqref="A1:A995 A1029:A1205 A1207:A1418 A2072:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="705"/>
+    <cfRule type="cellIs" dxfId="1" priority="706" operator="equal">
       <formula>1067000000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A995 A997:A1205 A1207:A1418 A2043:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="309"/>
+  <conditionalFormatting sqref="A1:A995 A997:A1205 A1207:A1418 A2072:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="702"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B614:B658 B660:B663 B665:B697">
-    <cfRule type="duplicateValues" dxfId="0" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="711"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1468 A1469 A1470 A1471 A1472 A1473 A1474 A1475">
-    <cfRule type="duplicateValues" dxfId="3" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="677"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1476 A1477">
-    <cfRule type="duplicateValues" dxfId="3" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="671"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1557 A1558 A1559:A1572">
-    <cfRule type="duplicateValues" dxfId="0" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1674:A1682 A1684:A1695 A1697:A1698 A1700:A1701 A1703:A1704 A1706:A1707 A1709:A1710 A1712:A1713 A1715:A1716 A1718:A1719 A1721:A1722 A1724:A1753">
-    <cfRule type="duplicateValues" dxfId="3" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1855:B1857 B1860">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="432"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1864:B1866 B1869">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1991:B1993 B1996">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2000:B2002 B2005">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="408"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B1880" r:id="rId1" display="恒翼之仗" tooltip="https://mu.dvg.cn/item_info.php?id=2534"/>
@@ -46184,7 +47133,7 @@
         <v>20310811</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>1028</v>
+        <v>1073</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -46204,7 +47153,7 @@
         <v>20310911</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>1029</v>
+        <v>1074</v>
       </c>
       <c r="C32" s="3">
         <v>0</v>
@@ -46224,7 +47173,7 @@
         <v>20311011</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="C33" s="3">
         <v>0</v>
@@ -46244,7 +47193,7 @@
         <v>1029</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="C34" s="3">
         <v>0</v>
@@ -46264,7 +47213,7 @@
         <v>1030</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -46304,7 +47253,7 @@
         <v>1032</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>1033</v>
+        <v>1078</v>
       </c>
       <c r="C37" s="3">
         <v>0</v>
@@ -46324,7 +47273,7 @@
         <v>1033</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
       <c r="C38" s="3">
         <v>0</v>
@@ -46344,7 +47293,7 @@
         <v>1034</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>1035</v>
+        <v>1080</v>
       </c>
       <c r="C39" s="3">
         <v>0</v>
@@ -46866,7 +47815,7 @@
         <v>1059</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>1036</v>
+        <v>1081</v>
       </c>
       <c r="C64" s="3">
         <v>0</v>
@@ -46908,7 +47857,7 @@
         <v>1061</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>1037</v>
+        <v>1082</v>
       </c>
       <c r="C66" s="3">
         <v>0</v>
@@ -46950,7 +47899,7 @@
         <v>1063</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="C68" s="3">
         <v>0</v>
@@ -46971,7 +47920,7 @@
         <v>1064</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>1039</v>
+        <v>1084</v>
       </c>
       <c r="C69" s="3">
         <v>0</v>
@@ -46992,7 +47941,7 @@
         <v>1065</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>1040</v>
+        <v>1085</v>
       </c>
       <c r="C70" s="3">
         <v>0</v>
@@ -47011,7 +47960,7 @@
     <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="11"/>
       <c r="B71" s="13" t="s">
-        <v>1041</v>
+        <v>1086</v>
       </c>
       <c r="C71" s="3">
         <v>0</v>
@@ -47284,7 +48233,7 @@
         <v>1079</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>1042</v>
+        <v>1087</v>
       </c>
       <c r="C84" s="3">
         <v>0</v>
@@ -47781,7 +48730,7 @@
         <v>20130811</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>1043</v>
+        <v>1088</v>
       </c>
       <c r="C108" s="3">
         <v>0</v>
@@ -47821,7 +48770,7 @@
         <v>20131311</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>1044</v>
+        <v>1089</v>
       </c>
       <c r="C110" s="3">
         <v>0</v>
@@ -47841,7 +48790,7 @@
         <v>1106</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>1045</v>
+        <v>1090</v>
       </c>
       <c r="C111" s="3">
         <v>0</v>
@@ -47861,7 +48810,7 @@
         <v>1107</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>1046</v>
+        <v>1091</v>
       </c>
       <c r="C112" s="3">
         <v>0</v>
@@ -47901,7 +48850,7 @@
         <v>20131211</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>1047</v>
+        <v>1092</v>
       </c>
       <c r="C114" s="3">
         <v>0</v>
@@ -47941,7 +48890,7 @@
         <v>1111</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>1048</v>
+        <v>1093</v>
       </c>
       <c r="C116" s="3">
         <v>0</v>
@@ -47961,7 +48910,7 @@
         <v>1112</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>1049</v>
+        <v>1094</v>
       </c>
       <c r="C117" s="3">
         <v>0</v>
@@ -47981,7 +48930,7 @@
         <v>1113</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C118" s="3">
         <v>0</v>
@@ -48221,7 +49170,7 @@
         <v>20120711</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>1051</v>
+        <v>1096</v>
       </c>
       <c r="C130" s="3">
         <v>0</v>
@@ -48382,7 +49331,7 @@
         <v>1133</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>1052</v>
+        <v>1097</v>
       </c>
       <c r="C138" s="3">
         <v>0</v>
@@ -48487,7 +49436,7 @@
         <v>1138</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>1053</v>
+        <v>1098</v>
       </c>
       <c r="C143" s="3">
         <v>0</v>
@@ -48508,7 +49457,7 @@
         <v>20121011</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>1054</v>
+        <v>1099</v>
       </c>
       <c r="C144" s="3">
         <v>0</v>
@@ -48529,7 +49478,7 @@
         <v>1140</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>1055</v>
+        <v>1100</v>
       </c>
       <c r="C145" s="3">
         <v>0</v>
@@ -48550,7 +49499,7 @@
         <v>1141</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>1056</v>
+        <v>1101</v>
       </c>
       <c r="C146" s="3">
         <v>0</v>
@@ -48571,7 +49520,7 @@
         <v>1142</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="C147" s="3">
         <v>0</v>
@@ -48592,7 +49541,7 @@
         <v>1143</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="C148" s="3">
         <v>0</v>
@@ -48634,7 +49583,7 @@
         <v>1145</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>1059</v>
+        <v>1104</v>
       </c>
       <c r="C150" s="3">
         <v>0</v>
@@ -48655,7 +49604,7 @@
         <v>1146</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>1060</v>
+        <v>1105</v>
       </c>
       <c r="C151" s="3">
         <v>0</v>
@@ -49054,7 +50003,7 @@
         <v>1165</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>1061</v>
+        <v>1106</v>
       </c>
       <c r="C170" s="3">
         <v>0</v>
@@ -49075,7 +50024,7 @@
         <v>1166</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>1062</v>
+        <v>1107</v>
       </c>
       <c r="C171" s="3">
         <v>0</v>
@@ -49096,7 +50045,7 @@
         <v>1167</v>
       </c>
       <c r="B172" s="16" t="s">
-        <v>1063</v>
+        <v>1108</v>
       </c>
       <c r="C172" s="3">
         <v>0</v>
@@ -49641,7 +50590,7 @@
         <v>2045010211</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>1064</v>
+        <v>1109</v>
       </c>
       <c r="C198" s="3">
         <v>0</v>
@@ -49721,7 +50670,7 @@
         <v>2045010311</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>1065</v>
+        <v>1110</v>
       </c>
       <c r="C202" s="3">
         <v>0</v>
@@ -49741,7 +50690,7 @@
         <v>20410811</v>
       </c>
       <c r="B203" s="13" t="s">
-        <v>1066</v>
+        <v>1111</v>
       </c>
       <c r="C203" s="3">
         <v>0</v>
@@ -49901,7 +50850,7 @@
         <v>2046010711</v>
       </c>
       <c r="B211" s="13" t="s">
-        <v>1067</v>
+        <v>1112</v>
       </c>
       <c r="C211" s="3">
         <v>0</v>
@@ -49941,7 +50890,7 @@
         <v>20411011</v>
       </c>
       <c r="B213" s="13" t="s">
-        <v>1068</v>
+        <v>1113</v>
       </c>
       <c r="C213" s="3">
         <v>0</v>
@@ -49961,7 +50910,7 @@
         <v>1209</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>1069</v>
+        <v>1114</v>
       </c>
       <c r="C214" s="3">
         <v>0</v>
@@ -49981,7 +50930,7 @@
         <v>20430811</v>
       </c>
       <c r="B215" s="13" t="s">
-        <v>1070</v>
+        <v>1115</v>
       </c>
       <c r="C215" s="3">
         <v>0</v>
@@ -50001,7 +50950,7 @@
         <v>20430911</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>1071</v>
+        <v>1116</v>
       </c>
       <c r="C216" s="3">
         <v>0</v>
@@ -50041,7 +50990,7 @@
         <v>20420811</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>1072</v>
+        <v>1117</v>
       </c>
       <c r="C218" s="3">
         <v>0</v>
@@ -50061,7 +51010,7 @@
         <v>2046010911</v>
       </c>
       <c r="B219" s="13" t="s">
-        <v>1073</v>
+        <v>1118</v>
       </c>
       <c r="C219" s="3">
         <v>0</v>
@@ -50081,7 +51030,7 @@
         <v>1215</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>1074</v>
+        <v>1119</v>
       </c>
       <c r="C220" s="3">
         <v>0</v>
@@ -50101,7 +51050,7 @@
         <v>20421011</v>
       </c>
       <c r="B221" s="13" t="s">
-        <v>1075</v>
+        <v>1120</v>
       </c>
       <c r="C221" s="3">
         <v>0</v>
@@ -50121,7 +51070,7 @@
         <v>1217</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>1076</v>
+        <v>1121</v>
       </c>
       <c r="C222" s="3">
         <v>0</v>
@@ -50141,7 +51090,7 @@
         <v>2045010911</v>
       </c>
       <c r="B223" s="13" t="s">
-        <v>1077</v>
+        <v>1122</v>
       </c>
       <c r="C223" s="3">
         <v>0</v>
@@ -50161,7 +51110,7 @@
         <v>1219</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>1078</v>
+        <v>1123</v>
       </c>
       <c r="C224" s="3">
         <v>0</v>
@@ -50181,7 +51130,7 @@
         <v>1220</v>
       </c>
       <c r="B225" s="13" t="s">
-        <v>1079</v>
+        <v>1124</v>
       </c>
       <c r="C225" s="3">
         <v>0</v>
@@ -50201,7 +51150,7 @@
         <v>1221</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>1080</v>
+        <v>1125</v>
       </c>
       <c r="C226" s="3">
         <v>0</v>
@@ -50241,7 +51190,7 @@
         <v>1226</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="C228" s="3">
         <v>0</v>
@@ -50281,7 +51230,7 @@
         <v>1220</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>1079</v>
+        <v>1124</v>
       </c>
       <c r="C230" s="3">
         <v>0</v>
@@ -50301,7 +51250,7 @@
         <v>1232</v>
       </c>
       <c r="B231" s="13" t="s">
-        <v>1082</v>
+        <v>1127</v>
       </c>
       <c r="C231" s="3">
         <v>0</v>
@@ -50321,7 +51270,7 @@
         <v>1233</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="C232" s="3">
         <v>0</v>
@@ -50341,7 +51290,7 @@
         <v>20431011</v>
       </c>
       <c r="B233" s="13" t="s">
-        <v>1084</v>
+        <v>1129</v>
       </c>
       <c r="C233" s="3">
         <v>0</v>
@@ -50361,7 +51310,7 @@
         <v>1235</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>1085</v>
+        <v>1130</v>
       </c>
       <c r="C234" s="3">
         <v>0</v>
@@ -50381,7 +51330,7 @@
         <v>1236</v>
       </c>
       <c r="B235" s="13" t="s">
-        <v>1086</v>
+        <v>1131</v>
       </c>
       <c r="C235" s="3">
         <v>0</v>
@@ -50401,7 +51350,7 @@
         <v>1237</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>1087</v>
+        <v>1132</v>
       </c>
       <c r="C236" s="3">
         <v>0</v>
@@ -50921,7 +51870,7 @@
         <v>2065010511</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>1088</v>
+        <v>1133</v>
       </c>
       <c r="C262" s="3">
         <v>0</v>
@@ -50981,7 +51930,7 @@
         <v>2065010211</v>
       </c>
       <c r="B265" s="13" t="s">
-        <v>1089</v>
+        <v>1134</v>
       </c>
       <c r="C265" s="3">
         <v>0</v>
@@ -51081,7 +52030,7 @@
         <v>2065010311</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>1090</v>
+        <v>1135</v>
       </c>
       <c r="C270" s="3">
         <v>0</v>
@@ -51101,7 +52050,7 @@
         <v>20610811</v>
       </c>
       <c r="B271" s="13" t="s">
-        <v>1091</v>
+        <v>1136</v>
       </c>
       <c r="C271" s="3">
         <v>0</v>
@@ -51201,7 +52150,7 @@
         <v>2066010111</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>1092</v>
+        <v>1137</v>
       </c>
       <c r="C276" s="3">
         <v>0</v>
@@ -51281,7 +52230,7 @@
         <v>2066010711</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>1093</v>
+        <v>1138</v>
       </c>
       <c r="C280" s="3">
         <v>0</v>
@@ -51321,7 +52270,7 @@
         <v>20611011</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>1094</v>
+        <v>1139</v>
       </c>
       <c r="C282" s="3">
         <v>0</v>
@@ -51341,7 +52290,7 @@
         <v>1284</v>
       </c>
       <c r="B283" s="13" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C283" s="3">
         <v>0</v>
@@ -51361,7 +52310,7 @@
         <v>2064011011</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>1096</v>
+        <v>1141</v>
       </c>
       <c r="C284" s="3">
         <v>0</v>
@@ -51381,7 +52330,7 @@
         <v>2064010811</v>
       </c>
       <c r="B285" s="13" t="s">
-        <v>1097</v>
+        <v>1142</v>
       </c>
       <c r="C285" s="3">
         <v>0</v>
@@ -51401,7 +52350,7 @@
         <v>20630811</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>1098</v>
+        <v>1143</v>
       </c>
       <c r="C286" s="3">
         <v>0</v>
@@ -51421,7 +52370,7 @@
         <v>20630911</v>
       </c>
       <c r="B287" s="13" t="s">
-        <v>1099</v>
+        <v>1144</v>
       </c>
       <c r="C287" s="3">
         <v>0</v>
@@ -51461,7 +52410,7 @@
         <v>20620811</v>
       </c>
       <c r="B289" s="13" t="s">
-        <v>1100</v>
+        <v>1145</v>
       </c>
       <c r="C289" s="3">
         <v>0</v>
@@ -51481,7 +52430,7 @@
         <v>2066010911</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>1101</v>
+        <v>1146</v>
       </c>
       <c r="C290" s="3">
         <v>0</v>
@@ -51501,7 +52450,7 @@
         <v>1292</v>
       </c>
       <c r="B291" s="13" t="s">
-        <v>1102</v>
+        <v>1147</v>
       </c>
       <c r="C291" s="3">
         <v>0</v>
@@ -51521,7 +52470,7 @@
         <v>20621011</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>1103</v>
+        <v>1148</v>
       </c>
       <c r="C292" s="3">
         <v>0</v>
@@ -51541,7 +52490,7 @@
         <v>1294</v>
       </c>
       <c r="B293" s="13" t="s">
-        <v>1104</v>
+        <v>1149</v>
       </c>
       <c r="C293" s="3">
         <v>0</v>
@@ -51561,7 +52510,7 @@
         <v>1295</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>1105</v>
+        <v>1150</v>
       </c>
       <c r="C294" s="3">
         <v>0</v>
@@ -51581,7 +52530,7 @@
         <v>2065010911</v>
       </c>
       <c r="B295" s="13" t="s">
-        <v>1106</v>
+        <v>1151</v>
       </c>
       <c r="C295" s="3">
         <v>0</v>
@@ -51601,7 +52550,7 @@
         <v>1297</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>1107</v>
+        <v>1152</v>
       </c>
       <c r="C296" s="3">
         <v>0</v>
@@ -51621,7 +52570,7 @@
         <v>1298</v>
       </c>
       <c r="B297" s="13" t="s">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="C297" s="3">
         <v>0</v>
@@ -51641,7 +52590,7 @@
         <v>1299</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>1109</v>
+        <v>1154</v>
       </c>
       <c r="C298" s="3">
         <v>0</v>
@@ -51661,7 +52610,7 @@
         <v>2066010111</v>
       </c>
       <c r="B299" s="13" t="s">
-        <v>1092</v>
+        <v>1137</v>
       </c>
       <c r="C299" s="3">
         <v>0</v>
@@ -51681,7 +52630,7 @@
         <v>1304</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>1110</v>
+        <v>1155</v>
       </c>
       <c r="C300" s="3">
         <v>0</v>
@@ -51721,7 +52670,7 @@
         <v>1309</v>
       </c>
       <c r="B302" s="13" t="s">
-        <v>1111</v>
+        <v>1156</v>
       </c>
       <c r="C302" s="3">
         <v>0</v>
@@ -51741,7 +52690,7 @@
         <v>1298</v>
       </c>
       <c r="B303" s="13" t="s">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="C303" s="3">
         <v>0</v>
@@ -51761,7 +52710,7 @@
         <v>1311</v>
       </c>
       <c r="B304" s="13" t="s">
-        <v>1112</v>
+        <v>1157</v>
       </c>
       <c r="C304" s="3">
         <v>0</v>
@@ -51781,7 +52730,7 @@
         <v>1312</v>
       </c>
       <c r="B305" s="13" t="s">
-        <v>1113</v>
+        <v>1158</v>
       </c>
       <c r="C305" s="3">
         <v>0</v>
@@ -51801,7 +52750,7 @@
         <v>20631011</v>
       </c>
       <c r="B306" s="13" t="s">
-        <v>1114</v>
+        <v>1159</v>
       </c>
       <c r="C306" s="3">
         <v>0</v>
@@ -51821,7 +52770,7 @@
         <v>1314</v>
       </c>
       <c r="B307" s="13" t="s">
-        <v>1115</v>
+        <v>1160</v>
       </c>
       <c r="C307" s="3">
         <v>0</v>
@@ -51841,7 +52790,7 @@
         <v>1315</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>1116</v>
+        <v>1161</v>
       </c>
       <c r="C308" s="3">
         <v>0</v>
@@ -51861,7 +52810,7 @@
         <v>1316</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>1117</v>
+        <v>1162</v>
       </c>
       <c r="C309" s="3">
         <v>0</v>
@@ -51881,7 +52830,7 @@
         <v>1317</v>
       </c>
       <c r="B310" s="13" t="s">
-        <v>1118</v>
+        <v>1163</v>
       </c>
       <c r="C310" s="3">
         <v>0</v>
@@ -52461,7 +53410,7 @@
         <v>2085010211</v>
       </c>
       <c r="B339" s="13" t="s">
-        <v>1119</v>
+        <v>1164</v>
       </c>
       <c r="C339" s="3">
         <v>0</v>
@@ -52561,7 +53510,7 @@
         <v>2085010311</v>
       </c>
       <c r="B344" s="13" t="s">
-        <v>1120</v>
+        <v>1165</v>
       </c>
       <c r="C344" s="3">
         <v>0</v>
@@ -52581,7 +53530,7 @@
         <v>20810811</v>
       </c>
       <c r="B345" s="13" t="s">
-        <v>1121</v>
+        <v>1166</v>
       </c>
       <c r="C345" s="3">
         <v>0</v>
@@ -52761,7 +53710,7 @@
         <v>2086010711</v>
       </c>
       <c r="B354" s="13" t="s">
-        <v>1122</v>
+        <v>1167</v>
       </c>
       <c r="C354" s="3">
         <v>0</v>
@@ -52781,7 +53730,7 @@
         <v>2086010811</v>
       </c>
       <c r="B355" s="13" t="s">
-        <v>1123</v>
+        <v>1168</v>
       </c>
       <c r="C355" s="3">
         <v>0</v>
@@ -52801,7 +53750,7 @@
         <v>20811011</v>
       </c>
       <c r="B356" s="13" t="s">
-        <v>1124</v>
+        <v>1169</v>
       </c>
       <c r="C356" s="3">
         <v>0</v>
@@ -52821,7 +53770,7 @@
         <v>1364</v>
       </c>
       <c r="B357" s="13" t="s">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="C357" s="3">
         <v>0</v>
@@ -52841,7 +53790,7 @@
         <v>2084011011</v>
       </c>
       <c r="B358" s="13" t="s">
-        <v>1126</v>
+        <v>1171</v>
       </c>
       <c r="C358" s="3">
         <v>0</v>
@@ -52861,7 +53810,7 @@
         <v>2084010811</v>
       </c>
       <c r="B359" s="13" t="s">
-        <v>1127</v>
+        <v>1172</v>
       </c>
       <c r="C359" s="3">
         <v>0</v>
@@ -52881,7 +53830,7 @@
         <v>20830811</v>
       </c>
       <c r="B360" s="13" t="s">
-        <v>1128</v>
+        <v>1173</v>
       </c>
       <c r="C360" s="3">
         <v>0</v>
@@ -52901,7 +53850,7 @@
         <v>20830911</v>
       </c>
       <c r="B361" s="13" t="s">
-        <v>1129</v>
+        <v>1174</v>
       </c>
       <c r="C361" s="3">
         <v>0</v>
@@ -52921,7 +53870,7 @@
         <v>1369</v>
       </c>
       <c r="B362" s="13" t="s">
-        <v>1130</v>
+        <v>1175</v>
       </c>
       <c r="C362" s="3">
         <v>0</v>
@@ -52941,7 +53890,7 @@
         <v>20820811</v>
       </c>
       <c r="B363" s="13" t="s">
-        <v>1131</v>
+        <v>1176</v>
       </c>
       <c r="C363" s="3">
         <v>0</v>
@@ -52961,7 +53910,7 @@
         <v>2086010911</v>
       </c>
       <c r="B364" s="13" t="s">
-        <v>1132</v>
+        <v>1177</v>
       </c>
       <c r="C364" s="3">
         <v>0</v>
@@ -52981,7 +53930,7 @@
         <v>1372</v>
       </c>
       <c r="B365" s="13" t="s">
-        <v>1133</v>
+        <v>1178</v>
       </c>
       <c r="C365" s="3">
         <v>0</v>
@@ -53001,7 +53950,7 @@
         <v>20821011</v>
       </c>
       <c r="B366" s="13" t="s">
-        <v>1134</v>
+        <v>1179</v>
       </c>
       <c r="C366" s="3">
         <v>0</v>
@@ -53021,7 +53970,7 @@
         <v>1374</v>
       </c>
       <c r="B367" s="13" t="s">
-        <v>1135</v>
+        <v>1180</v>
       </c>
       <c r="C367" s="3">
         <v>0</v>
@@ -53041,7 +53990,7 @@
         <v>1375</v>
       </c>
       <c r="B368" s="13" t="s">
-        <v>1136</v>
+        <v>1181</v>
       </c>
       <c r="C368" s="3">
         <v>0</v>
@@ -53061,7 +54010,7 @@
         <v>2085010911</v>
       </c>
       <c r="B369" s="13" t="s">
-        <v>1137</v>
+        <v>1182</v>
       </c>
       <c r="C369" s="3">
         <v>0</v>
@@ -53081,7 +54030,7 @@
         <v>1377</v>
       </c>
       <c r="B370" s="13" t="s">
-        <v>1138</v>
+        <v>1183</v>
       </c>
       <c r="C370" s="3">
         <v>0</v>
@@ -53101,7 +54050,7 @@
         <v>1378</v>
       </c>
       <c r="B371" s="13" t="s">
-        <v>1139</v>
+        <v>1184</v>
       </c>
       <c r="C371" s="3">
         <v>0</v>
@@ -53121,7 +54070,7 @@
         <v>1379</v>
       </c>
       <c r="B372" s="13" t="s">
-        <v>1140</v>
+        <v>1185</v>
       </c>
       <c r="C372" s="3">
         <v>0</v>
@@ -53161,7 +54110,7 @@
         <v>1384</v>
       </c>
       <c r="B374" s="13" t="s">
-        <v>1141</v>
+        <v>1186</v>
       </c>
       <c r="C374" s="3">
         <v>0</v>
@@ -53201,7 +54150,7 @@
         <v>1389</v>
       </c>
       <c r="B376" s="13" t="s">
-        <v>1142</v>
+        <v>1187</v>
       </c>
       <c r="C376" s="3">
         <v>0</v>
@@ -53221,7 +54170,7 @@
         <v>1378</v>
       </c>
       <c r="B377" s="13" t="s">
-        <v>1139</v>
+        <v>1184</v>
       </c>
       <c r="C377" s="3">
         <v>0</v>
@@ -53241,7 +54190,7 @@
         <v>1391</v>
       </c>
       <c r="B378" s="13" t="s">
-        <v>1143</v>
+        <v>1188</v>
       </c>
       <c r="C378" s="3">
         <v>0</v>
@@ -53261,7 +54210,7 @@
         <v>1392</v>
       </c>
       <c r="B379" s="13" t="s">
-        <v>1144</v>
+        <v>1189</v>
       </c>
       <c r="C379" s="3">
         <v>0</v>
@@ -53281,7 +54230,7 @@
         <v>20831011</v>
       </c>
       <c r="B380" s="13" t="s">
-        <v>1145</v>
+        <v>1190</v>
       </c>
       <c r="C380" s="3">
         <v>0</v>
@@ -53301,7 +54250,7 @@
         <v>1394</v>
       </c>
       <c r="B381" s="13" t="s">
-        <v>1146</v>
+        <v>1191</v>
       </c>
       <c r="C381" s="3">
         <v>0</v>
@@ -53321,7 +54270,7 @@
         <v>1395</v>
       </c>
       <c r="B382" s="13" t="s">
-        <v>1147</v>
+        <v>1192</v>
       </c>
       <c r="C382" s="3">
         <v>0</v>
@@ -53341,7 +54290,7 @@
         <v>1396</v>
       </c>
       <c r="B383" s="13" t="s">
-        <v>1148</v>
+        <v>1193</v>
       </c>
       <c r="C383" s="3">
         <v>0</v>
@@ -53361,7 +54310,7 @@
         <v>1397</v>
       </c>
       <c r="B384" s="13" t="s">
-        <v>1149</v>
+        <v>1194</v>
       </c>
       <c r="C384" s="3">
         <v>0</v>
@@ -53941,7 +54890,7 @@
         <v>2075010211</v>
       </c>
       <c r="B413" s="13" t="s">
-        <v>1150</v>
+        <v>1195</v>
       </c>
       <c r="C413" s="3">
         <v>0</v>
@@ -54041,7 +54990,7 @@
         <v>2075010311</v>
       </c>
       <c r="B418" s="13" t="s">
-        <v>1151</v>
+        <v>1196</v>
       </c>
       <c r="C418" s="3">
         <v>0</v>
@@ -54061,7 +55010,7 @@
         <v>20710811</v>
       </c>
       <c r="B419" s="13" t="s">
-        <v>1152</v>
+        <v>1197</v>
       </c>
       <c r="C419" s="3">
         <v>0</v>
@@ -54241,7 +55190,7 @@
         <v>2076010711</v>
       </c>
       <c r="B428" s="13" t="s">
-        <v>1153</v>
+        <v>1198</v>
       </c>
       <c r="C428" s="3">
         <v>0</v>
@@ -54261,7 +55210,7 @@
         <v>2076010811</v>
       </c>
       <c r="B429" s="13" t="s">
-        <v>1154</v>
+        <v>1199</v>
       </c>
       <c r="C429" s="3">
         <v>0</v>
@@ -54281,7 +55230,7 @@
         <v>20711011</v>
       </c>
       <c r="B430" s="13" t="s">
-        <v>1155</v>
+        <v>1200</v>
       </c>
       <c r="C430" s="3">
         <v>0</v>
@@ -54301,7 +55250,7 @@
         <v>1444</v>
       </c>
       <c r="B431" s="13" t="s">
-        <v>1156</v>
+        <v>1201</v>
       </c>
       <c r="C431" s="3">
         <v>0</v>
@@ -54321,7 +55270,7 @@
         <v>2074011011</v>
       </c>
       <c r="B432" s="13" t="s">
-        <v>1157</v>
+        <v>1202</v>
       </c>
       <c r="C432" s="3">
         <v>0</v>
@@ -54341,7 +55290,7 @@
         <v>2074010811</v>
       </c>
       <c r="B433" s="13" t="s">
-        <v>1158</v>
+        <v>1203</v>
       </c>
       <c r="C433" s="3">
         <v>0</v>
@@ -54361,7 +55310,7 @@
         <v>20730811</v>
       </c>
       <c r="B434" s="13" t="s">
-        <v>1159</v>
+        <v>1204</v>
       </c>
       <c r="C434" s="3">
         <v>0</v>
@@ -54381,7 +55330,7 @@
         <v>20730911</v>
       </c>
       <c r="B435" s="13" t="s">
-        <v>1160</v>
+        <v>1205</v>
       </c>
       <c r="C435" s="3">
         <v>0</v>
@@ -54401,7 +55350,7 @@
         <v>1449</v>
       </c>
       <c r="B436" s="13" t="s">
-        <v>1161</v>
+        <v>1206</v>
       </c>
       <c r="C436" s="3">
         <v>0</v>
@@ -54421,7 +55370,7 @@
         <v>20720811</v>
       </c>
       <c r="B437" s="13" t="s">
-        <v>1162</v>
+        <v>1207</v>
       </c>
       <c r="C437" s="3">
         <v>0</v>
@@ -54441,7 +55390,7 @@
         <v>2076010911</v>
       </c>
       <c r="B438" s="13" t="s">
-        <v>1163</v>
+        <v>1208</v>
       </c>
       <c r="C438" s="3">
         <v>0</v>
@@ -54461,7 +55410,7 @@
         <v>1452</v>
       </c>
       <c r="B439" s="13" t="s">
-        <v>1164</v>
+        <v>1209</v>
       </c>
       <c r="C439" s="3">
         <v>0</v>
@@ -54501,7 +55450,7 @@
         <v>1457</v>
       </c>
       <c r="B441" s="13" t="s">
-        <v>1165</v>
+        <v>1210</v>
       </c>
       <c r="C441" s="3">
         <v>0</v>
@@ -54541,7 +55490,7 @@
         <v>1462</v>
       </c>
       <c r="B443" s="13" t="s">
-        <v>1166</v>
+        <v>1211</v>
       </c>
       <c r="C443" s="3">
         <v>0</v>
@@ -54561,7 +55510,7 @@
         <v>1463</v>
       </c>
       <c r="B444" s="13" t="s">
-        <v>1167</v>
+        <v>1212</v>
       </c>
       <c r="C444" s="3">
         <v>0</v>
@@ -54581,7 +55530,7 @@
         <v>20731011</v>
       </c>
       <c r="B445" s="13" t="s">
-        <v>1168</v>
+        <v>1213</v>
       </c>
       <c r="C445" s="3">
         <v>0</v>
@@ -54601,7 +55550,7 @@
         <v>1465</v>
       </c>
       <c r="B446" s="13" t="s">
-        <v>1169</v>
+        <v>1214</v>
       </c>
       <c r="C446" s="3">
         <v>0</v>
@@ -54621,7 +55570,7 @@
         <v>1466</v>
       </c>
       <c r="B447" s="13" t="s">
-        <v>1170</v>
+        <v>1215</v>
       </c>
       <c r="C447" s="3">
         <v>0</v>
@@ -54641,7 +55590,7 @@
         <v>1467</v>
       </c>
       <c r="B448" s="13" t="s">
-        <v>1171</v>
+        <v>1216</v>
       </c>
       <c r="C448" s="3">
         <v>0</v>
@@ -54661,7 +55610,7 @@
         <v>1468</v>
       </c>
       <c r="B449" s="13" t="s">
-        <v>1172</v>
+        <v>1217</v>
       </c>
       <c r="C449" s="3">
         <v>0</v>
@@ -55241,7 +56190,7 @@
         <v>2095010211</v>
       </c>
       <c r="B478" s="13" t="s">
-        <v>1173</v>
+        <v>1218</v>
       </c>
       <c r="C478" s="3">
         <v>0</v>
@@ -55341,7 +56290,7 @@
         <v>2095010311</v>
       </c>
       <c r="B483" s="13" t="s">
-        <v>1174</v>
+        <v>1219</v>
       </c>
       <c r="C483" s="3">
         <v>0</v>
@@ -55361,7 +56310,7 @@
         <v>20910811</v>
       </c>
       <c r="B484" s="13" t="s">
-        <v>1175</v>
+        <v>1220</v>
       </c>
       <c r="C484" s="3">
         <v>0</v>
@@ -55541,7 +56490,7 @@
         <v>2096010711</v>
       </c>
       <c r="B493" s="13" t="s">
-        <v>1176</v>
+        <v>1221</v>
       </c>
       <c r="C493" s="3">
         <v>0</v>
@@ -55581,7 +56530,7 @@
         <v>20911011</v>
       </c>
       <c r="B495" s="13" t="s">
-        <v>1177</v>
+        <v>1222</v>
       </c>
       <c r="C495" s="3">
         <v>0</v>
@@ -55601,7 +56550,7 @@
         <v>2094011011</v>
       </c>
       <c r="B496" s="13" t="s">
-        <v>1178</v>
+        <v>1223</v>
       </c>
       <c r="C496" s="3">
         <v>0</v>
@@ -55621,7 +56570,7 @@
         <v>2094010811</v>
       </c>
       <c r="B497" s="13" t="s">
-        <v>1179</v>
+        <v>1224</v>
       </c>
       <c r="C497" s="3">
         <v>0</v>
@@ -55641,7 +56590,7 @@
         <v>20930811</v>
       </c>
       <c r="B498" s="13" t="s">
-        <v>1180</v>
+        <v>1225</v>
       </c>
       <c r="C498" s="3">
         <v>0</v>
@@ -55661,7 +56610,7 @@
         <v>20930911</v>
       </c>
       <c r="B499" s="13" t="s">
-        <v>1181</v>
+        <v>1226</v>
       </c>
       <c r="C499" s="3">
         <v>0</v>
@@ -55701,7 +56650,7 @@
         <v>20920811</v>
       </c>
       <c r="B501" s="13" t="s">
-        <v>1182</v>
+        <v>1227</v>
       </c>
       <c r="C501" s="3">
         <v>0</v>
@@ -55721,7 +56670,7 @@
         <v>2096010911</v>
       </c>
       <c r="B502" s="13" t="s">
-        <v>1183</v>
+        <v>1228</v>
       </c>
       <c r="C502" s="3">
         <v>0</v>
@@ -55741,7 +56690,7 @@
         <v>1523</v>
       </c>
       <c r="B503" s="13" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C503" s="3">
         <v>0</v>
@@ -55761,7 +56710,7 @@
         <v>20921011</v>
       </c>
       <c r="B504" s="13" t="s">
-        <v>1185</v>
+        <v>1230</v>
       </c>
       <c r="C504" s="3">
         <v>0</v>
@@ -55781,7 +56730,7 @@
         <v>1525</v>
       </c>
       <c r="B505" s="13" t="s">
-        <v>1186</v>
+        <v>1231</v>
       </c>
       <c r="C505" s="3">
         <v>0</v>
@@ -55801,7 +56750,7 @@
         <v>1526</v>
       </c>
       <c r="B506" s="13" t="s">
-        <v>1187</v>
+        <v>1232</v>
       </c>
       <c r="C506" s="3">
         <v>0</v>
@@ -55821,7 +56770,7 @@
         <v>2095010911</v>
       </c>
       <c r="B507" s="13" t="s">
-        <v>1188</v>
+        <v>1233</v>
       </c>
       <c r="C507" s="3">
         <v>0</v>
@@ -55841,7 +56790,7 @@
         <v>1528</v>
       </c>
       <c r="B508" s="13" t="s">
-        <v>1189</v>
+        <v>1234</v>
       </c>
       <c r="C508" s="3">
         <v>0</v>
@@ -55861,7 +56810,7 @@
         <v>1529</v>
       </c>
       <c r="B509" s="13" t="s">
-        <v>1190</v>
+        <v>1235</v>
       </c>
       <c r="C509" s="3">
         <v>0</v>
@@ -55881,7 +56830,7 @@
         <v>1530</v>
       </c>
       <c r="B510" s="13" t="s">
-        <v>1191</v>
+        <v>1236</v>
       </c>
       <c r="C510" s="3">
         <v>0</v>
@@ -55921,7 +56870,7 @@
         <v>1535</v>
       </c>
       <c r="B512" s="13" t="s">
-        <v>1192</v>
+        <v>1237</v>
       </c>
       <c r="C512" s="3">
         <v>0</v>
@@ -55961,7 +56910,7 @@
         <v>1540</v>
       </c>
       <c r="B514" s="13" t="s">
-        <v>1193</v>
+        <v>1238</v>
       </c>
       <c r="C514" s="3">
         <v>0</v>
@@ -55981,7 +56930,7 @@
         <v>1529</v>
       </c>
       <c r="B515" s="13" t="s">
-        <v>1190</v>
+        <v>1235</v>
       </c>
       <c r="C515" s="3">
         <v>0</v>
@@ -56001,7 +56950,7 @@
         <v>1542</v>
       </c>
       <c r="B516" s="13" t="s">
-        <v>1194</v>
+        <v>1239</v>
       </c>
       <c r="C516" s="3">
         <v>0</v>
@@ -56021,7 +56970,7 @@
         <v>1543</v>
       </c>
       <c r="B517" s="13" t="s">
-        <v>1195</v>
+        <v>1240</v>
       </c>
       <c r="C517" s="3">
         <v>0</v>
@@ -56041,7 +56990,7 @@
         <v>20931011</v>
       </c>
       <c r="B518" s="13" t="s">
-        <v>1196</v>
+        <v>1241</v>
       </c>
       <c r="C518" s="3">
         <v>0</v>
@@ -56061,7 +57010,7 @@
         <v>1545</v>
       </c>
       <c r="B519" s="13" t="s">
-        <v>1197</v>
+        <v>1242</v>
       </c>
       <c r="C519" s="3">
         <v>0</v>
@@ -56081,7 +57030,7 @@
         <v>1546</v>
       </c>
       <c r="B520" s="13" t="s">
-        <v>1198</v>
+        <v>1243</v>
       </c>
       <c r="C520" s="3">
         <v>0</v>
@@ -56101,7 +57050,7 @@
         <v>1547</v>
       </c>
       <c r="B521" s="13" t="s">
-        <v>1199</v>
+        <v>1244</v>
       </c>
       <c r="C521" s="3">
         <v>0</v>
@@ -56121,7 +57070,7 @@
         <v>1548</v>
       </c>
       <c r="B522" s="13" t="s">
-        <v>1200</v>
+        <v>1245</v>
       </c>
       <c r="C522" s="3">
         <v>0</v>
@@ -56141,7 +57090,7 @@
         <v>1549</v>
       </c>
       <c r="B523" s="13" t="s">
-        <v>1201</v>
+        <v>1246</v>
       </c>
       <c r="C523" s="3">
         <v>0</v>
@@ -56161,7 +57110,7 @@
         <v>1550</v>
       </c>
       <c r="B524" s="13" t="s">
-        <v>1202</v>
+        <v>1247</v>
       </c>
       <c r="C524" s="3">
         <v>0</v>
@@ -56181,7 +57130,7 @@
         <v>1551</v>
       </c>
       <c r="B525" s="13" t="s">
-        <v>1203</v>
+        <v>1248</v>
       </c>
       <c r="C525" s="3">
         <v>0</v>
@@ -56201,7 +57150,7 @@
         <v>1552</v>
       </c>
       <c r="B526" s="13" t="s">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="C526" s="3">
         <v>0</v>
@@ -56221,7 +57170,7 @@
         <v>1553</v>
       </c>
       <c r="B527" s="13" t="s">
-        <v>1205</v>
+        <v>1250</v>
       </c>
       <c r="C527" s="3">
         <v>0</v>
@@ -56861,7 +57810,7 @@
         <v>1585</v>
       </c>
       <c r="B559" s="12" t="s">
-        <v>1206</v>
+        <v>1251</v>
       </c>
       <c r="C559" s="3">
         <v>0</v>
@@ -56881,7 +57830,7 @@
         <v>1586</v>
       </c>
       <c r="B560" s="12" t="s">
-        <v>1207</v>
+        <v>1252</v>
       </c>
       <c r="C560" s="3">
         <v>0</v>
@@ -57921,7 +58870,7 @@
         <v>2019</v>
       </c>
       <c r="B612" s="13" t="s">
-        <v>1208</v>
+        <v>1253</v>
       </c>
       <c r="C612" s="3">
         <v>0</v>
@@ -58061,7 +59010,7 @@
         <v>20310821</v>
       </c>
       <c r="B619" s="13" t="s">
-        <v>1209</v>
+        <v>1254</v>
       </c>
       <c r="C619" s="3">
         <v>0</v>
@@ -58081,7 +59030,7 @@
         <v>20310921</v>
       </c>
       <c r="B620" s="13" t="s">
-        <v>1210</v>
+        <v>1255</v>
       </c>
       <c r="C620" s="3">
         <v>0</v>
@@ -58101,7 +59050,7 @@
         <v>20311021</v>
       </c>
       <c r="B621" s="13" t="s">
-        <v>1211</v>
+        <v>1256</v>
       </c>
       <c r="C621" s="3">
         <v>0</v>
@@ -58121,7 +59070,7 @@
         <v>2029</v>
       </c>
       <c r="B622" s="13" t="s">
-        <v>1212</v>
+        <v>1257</v>
       </c>
       <c r="C622" s="3">
         <v>0</v>
@@ -58141,7 +59090,7 @@
         <v>2030</v>
       </c>
       <c r="B623" s="13" t="s">
-        <v>1213</v>
+        <v>1258</v>
       </c>
       <c r="C623" s="3">
         <v>0</v>
@@ -58181,7 +59130,7 @@
         <v>2032</v>
       </c>
       <c r="B625" s="13" t="s">
-        <v>1214</v>
+        <v>1259</v>
       </c>
       <c r="C625" s="3">
         <v>0</v>
@@ -58201,7 +59150,7 @@
         <v>2033</v>
       </c>
       <c r="B626" s="13" t="s">
-        <v>1215</v>
+        <v>1260</v>
       </c>
       <c r="C626" s="3">
         <v>0</v>
@@ -58221,7 +59170,7 @@
         <v>2034</v>
       </c>
       <c r="B627" s="13" t="s">
-        <v>1216</v>
+        <v>1261</v>
       </c>
       <c r="C627" s="3">
         <v>0</v>
@@ -58681,7 +59630,7 @@
         <v>2057</v>
       </c>
       <c r="B650" s="12" t="s">
-        <v>1217</v>
+        <v>1262</v>
       </c>
       <c r="C650" s="3">
         <v>0</v>
@@ -58701,7 +59650,7 @@
         <v>2058</v>
       </c>
       <c r="B651" s="13" t="s">
-        <v>1218</v>
+        <v>1263</v>
       </c>
       <c r="C651" s="3">
         <v>0</v>
@@ -58741,7 +59690,7 @@
         <v>2060</v>
       </c>
       <c r="B653" s="13" t="s">
-        <v>1219</v>
+        <v>1264</v>
       </c>
       <c r="C653" s="3">
         <v>0</v>
@@ -58781,7 +59730,7 @@
         <v>2062</v>
       </c>
       <c r="B655" s="13" t="s">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="C655" s="3">
         <v>0</v>
@@ -58801,7 +59750,7 @@
         <v>2063</v>
       </c>
       <c r="B656" s="13" t="s">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="C656" s="3">
         <v>0</v>
@@ -58821,7 +59770,7 @@
         <v>2064</v>
       </c>
       <c r="B657" s="13" t="s">
-        <v>1222</v>
+        <v>1267</v>
       </c>
       <c r="C657" s="3">
         <v>0</v>
@@ -59081,7 +60030,7 @@
         <v>2077</v>
       </c>
       <c r="B670" s="13" t="s">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="C670" s="3">
         <v>0</v>
@@ -59461,7 +60410,7 @@
         <v>2096</v>
       </c>
       <c r="B689" s="12" t="s">
-        <v>1224</v>
+        <v>1269</v>
       </c>
       <c r="C689" s="3">
         <v>0</v>
@@ -59561,7 +60510,7 @@
         <v>20130821</v>
       </c>
       <c r="B694" s="13" t="s">
-        <v>1225</v>
+        <v>1270</v>
       </c>
       <c r="C694" s="3">
         <v>0</v>
@@ -59601,7 +60550,7 @@
         <v>20131321</v>
       </c>
       <c r="B696" s="13" t="s">
-        <v>1226</v>
+        <v>1271</v>
       </c>
       <c r="C696" s="3">
         <v>0</v>
@@ -59621,7 +60570,7 @@
         <v>2104</v>
       </c>
       <c r="B697" s="13" t="s">
-        <v>1227</v>
+        <v>1272</v>
       </c>
       <c r="C697" s="3">
         <v>0</v>
@@ -59641,7 +60590,7 @@
         <v>20131221</v>
       </c>
       <c r="B698" s="13" t="s">
-        <v>1228</v>
+        <v>1273</v>
       </c>
       <c r="C698" s="3">
         <v>0</v>
@@ -59681,7 +60630,7 @@
         <v>2108</v>
       </c>
       <c r="B700" s="13" t="s">
-        <v>1229</v>
+        <v>1274</v>
       </c>
       <c r="C700" s="3">
         <v>0</v>
@@ -59701,7 +60650,7 @@
         <v>2109</v>
       </c>
       <c r="B701" s="13" t="s">
-        <v>1230</v>
+        <v>1275</v>
       </c>
       <c r="C701" s="3">
         <v>0</v>
@@ -59721,7 +60670,7 @@
         <v>2110</v>
       </c>
       <c r="B702" s="13" t="s">
-        <v>1231</v>
+        <v>1276</v>
       </c>
       <c r="C702" s="3">
         <v>0</v>
@@ -59941,7 +60890,7 @@
         <v>2121</v>
       </c>
       <c r="B713" s="12" t="s">
-        <v>1232</v>
+        <v>1277</v>
       </c>
       <c r="C713" s="3">
         <v>0</v>
@@ -59961,7 +60910,7 @@
         <v>20120721</v>
       </c>
       <c r="B714" s="13" t="s">
-        <v>1233</v>
+        <v>1278</v>
       </c>
       <c r="C714" s="3">
         <v>0</v>
@@ -60121,7 +61070,7 @@
         <v>2130</v>
       </c>
       <c r="B722" s="13" t="s">
-        <v>1234</v>
+        <v>1279</v>
       </c>
       <c r="C722" s="3">
         <v>0</v>
@@ -60221,7 +61170,7 @@
         <v>2135</v>
       </c>
       <c r="B727" s="13" t="s">
-        <v>1235</v>
+        <v>1280</v>
       </c>
       <c r="C727" s="3">
         <v>0</v>
@@ -60241,7 +61190,7 @@
         <v>20121021</v>
       </c>
       <c r="B728" s="13" t="s">
-        <v>1236</v>
+        <v>1281</v>
       </c>
       <c r="C728" s="3">
         <v>0</v>
@@ -60261,7 +61210,7 @@
         <v>2137</v>
       </c>
       <c r="B729" s="13" t="s">
-        <v>1237</v>
+        <v>1282</v>
       </c>
       <c r="C729" s="3">
         <v>0</v>
@@ -60281,7 +61230,7 @@
         <v>2138</v>
       </c>
       <c r="B730" s="13" t="s">
-        <v>1238</v>
+        <v>1283</v>
       </c>
       <c r="C730" s="3">
         <v>0</v>
@@ -60301,7 +61250,7 @@
         <v>2139</v>
       </c>
       <c r="B731" s="13" t="s">
-        <v>1239</v>
+        <v>1284</v>
       </c>
       <c r="C731" s="3">
         <v>0</v>
@@ -60321,7 +61270,7 @@
         <v>2140</v>
       </c>
       <c r="B732" s="13" t="s">
-        <v>1240</v>
+        <v>1285</v>
       </c>
       <c r="C732" s="3">
         <v>0</v>
@@ -60341,7 +61290,7 @@
         <v>2141</v>
       </c>
       <c r="B733" s="12" t="s">
-        <v>1241</v>
+        <v>1286</v>
       </c>
       <c r="C733" s="3">
         <v>0</v>
@@ -60361,7 +61310,7 @@
         <v>2142</v>
       </c>
       <c r="B734" s="13" t="s">
-        <v>1242</v>
+        <v>1287</v>
       </c>
       <c r="C734" s="3">
         <v>0</v>
@@ -60381,7 +61330,7 @@
         <v>2143</v>
       </c>
       <c r="B735" s="12" t="s">
-        <v>1243</v>
+        <v>1288</v>
       </c>
       <c r="C735" s="3">
         <v>0</v>
@@ -60401,7 +61350,7 @@
         <v>2144</v>
       </c>
       <c r="B736" s="12" t="s">
-        <v>1244</v>
+        <v>1289</v>
       </c>
       <c r="C736" s="3">
         <v>0</v>
@@ -60741,7 +61690,7 @@
         <v>2161</v>
       </c>
       <c r="B753" s="12" t="s">
-        <v>1245</v>
+        <v>1290</v>
       </c>
       <c r="C753" s="3">
         <v>0</v>
@@ -60761,7 +61710,7 @@
         <v>2162</v>
       </c>
       <c r="B754" s="13" t="s">
-        <v>1246</v>
+        <v>1291</v>
       </c>
       <c r="C754" s="3">
         <v>0</v>
@@ -61281,7 +62230,7 @@
         <v>2045010221</v>
       </c>
       <c r="B780" s="13" t="s">
-        <v>1247</v>
+        <v>1292</v>
       </c>
       <c r="C780" s="3">
         <v>0</v>
@@ -61381,7 +62330,7 @@
         <v>20410821</v>
       </c>
       <c r="B785" s="13" t="s">
-        <v>1248</v>
+        <v>1293</v>
       </c>
       <c r="C785" s="3">
         <v>0</v>
@@ -61561,7 +62510,7 @@
         <v>2046010821</v>
       </c>
       <c r="B794" s="13" t="s">
-        <v>1249</v>
+        <v>1294</v>
       </c>
       <c r="C794" s="3">
         <v>0</v>
@@ -61581,7 +62530,7 @@
         <v>20411021</v>
       </c>
       <c r="B795" s="13" t="s">
-        <v>1250</v>
+        <v>1295</v>
       </c>
       <c r="C795" s="3">
         <v>0</v>
@@ -61601,7 +62550,7 @@
         <v>2204</v>
       </c>
       <c r="B796" s="13" t="s">
-        <v>1251</v>
+        <v>1296</v>
       </c>
       <c r="C796" s="3">
         <v>0</v>
@@ -61621,7 +62570,7 @@
         <v>20430821</v>
       </c>
       <c r="B797" s="13" t="s">
-        <v>1252</v>
+        <v>1297</v>
       </c>
       <c r="C797" s="3">
         <v>0</v>
@@ -61641,7 +62590,7 @@
         <v>20430921</v>
       </c>
       <c r="B798" s="13" t="s">
-        <v>1253</v>
+        <v>1298</v>
       </c>
       <c r="C798" s="3">
         <v>0</v>
@@ -61661,7 +62610,7 @@
         <v>2207</v>
       </c>
       <c r="B799" s="13" t="s">
-        <v>1254</v>
+        <v>1299</v>
       </c>
       <c r="C799" s="3">
         <v>0</v>
@@ -61681,7 +62630,7 @@
         <v>20420821</v>
       </c>
       <c r="B800" s="13" t="s">
-        <v>1255</v>
+        <v>1300</v>
       </c>
       <c r="C800" s="3">
         <v>0</v>
@@ -61701,7 +62650,7 @@
         <v>2046010921</v>
       </c>
       <c r="B801" s="13" t="s">
-        <v>1256</v>
+        <v>1301</v>
       </c>
       <c r="C801" s="3">
         <v>0</v>
@@ -61721,7 +62670,7 @@
         <v>2210</v>
       </c>
       <c r="B802" s="13" t="s">
-        <v>1257</v>
+        <v>1302</v>
       </c>
       <c r="C802" s="3">
         <v>0</v>
@@ -61741,7 +62690,7 @@
         <v>20421021</v>
       </c>
       <c r="B803" s="13" t="s">
-        <v>1258</v>
+        <v>1303</v>
       </c>
       <c r="C803" s="3">
         <v>0</v>
@@ -61761,7 +62710,7 @@
         <v>2212</v>
       </c>
       <c r="B804" s="13" t="s">
-        <v>1259</v>
+        <v>1304</v>
       </c>
       <c r="C804" s="3">
         <v>0</v>
@@ -61781,7 +62730,7 @@
         <v>2045010921</v>
       </c>
       <c r="B805" s="13" t="s">
-        <v>1260</v>
+        <v>1305</v>
       </c>
       <c r="C805" s="3">
         <v>0</v>
@@ -61801,7 +62750,7 @@
         <v>2214</v>
       </c>
       <c r="B806" s="13" t="s">
-        <v>1261</v>
+        <v>1306</v>
       </c>
       <c r="C806" s="3">
         <v>0</v>
@@ -61821,7 +62770,7 @@
         <v>2215</v>
       </c>
       <c r="B807" s="13" t="s">
-        <v>1262</v>
+        <v>1307</v>
       </c>
       <c r="C807" s="3">
         <v>0</v>
@@ -61841,7 +62790,7 @@
         <v>2216</v>
       </c>
       <c r="B808" s="13" t="s">
-        <v>1263</v>
+        <v>1308</v>
       </c>
       <c r="C808" s="3">
         <v>0</v>
@@ -61901,7 +62850,7 @@
         <v>2215</v>
       </c>
       <c r="B811" s="13" t="s">
-        <v>1262</v>
+        <v>1307</v>
       </c>
       <c r="C811" s="3">
         <v>0</v>
@@ -61921,7 +62870,7 @@
         <v>2226</v>
       </c>
       <c r="B812" s="13" t="s">
-        <v>1264</v>
+        <v>1309</v>
       </c>
       <c r="C812" s="3">
         <v>0</v>
@@ -61941,7 +62890,7 @@
         <v>2227</v>
       </c>
       <c r="B813" s="13" t="s">
-        <v>1265</v>
+        <v>1310</v>
       </c>
       <c r="C813" s="3">
         <v>0</v>
@@ -61961,7 +62910,7 @@
         <v>20431021</v>
       </c>
       <c r="B814" s="13" t="s">
-        <v>1266</v>
+        <v>1311</v>
       </c>
       <c r="C814" s="3">
         <v>0</v>
@@ -62481,7 +63430,7 @@
         <v>2065010521</v>
       </c>
       <c r="B840" s="13" t="s">
-        <v>1267</v>
+        <v>1312</v>
       </c>
       <c r="C840" s="3">
         <v>0</v>
@@ -62541,7 +63490,7 @@
         <v>2065010221</v>
       </c>
       <c r="B843" s="13" t="s">
-        <v>1268</v>
+        <v>1313</v>
       </c>
       <c r="C843" s="3">
         <v>0</v>
@@ -62661,7 +63610,7 @@
         <v>20610821</v>
       </c>
       <c r="B849" s="13" t="s">
-        <v>1269</v>
+        <v>1314</v>
       </c>
       <c r="C849" s="3">
         <v>0</v>
@@ -62761,7 +63710,7 @@
         <v>2066010121</v>
       </c>
       <c r="B854" s="13" t="s">
-        <v>1270</v>
+        <v>1315</v>
       </c>
       <c r="C854" s="3">
         <v>0</v>
@@ -62861,7 +63810,7 @@
         <v>2066010821</v>
       </c>
       <c r="B859" s="13" t="s">
-        <v>1271</v>
+        <v>1316</v>
       </c>
       <c r="C859" s="3">
         <v>0</v>
@@ -62881,7 +63830,7 @@
         <v>20611021</v>
       </c>
       <c r="B860" s="13" t="s">
-        <v>1272</v>
+        <v>1317</v>
       </c>
       <c r="C860" s="3">
         <v>0</v>
@@ -62901,7 +63850,7 @@
         <v>2275</v>
       </c>
       <c r="B861" s="13" t="s">
-        <v>1273</v>
+        <v>1318</v>
       </c>
       <c r="C861" s="3">
         <v>0</v>
@@ -62921,7 +63870,7 @@
         <v>2064011021</v>
       </c>
       <c r="B862" s="13" t="s">
-        <v>1274</v>
+        <v>1319</v>
       </c>
       <c r="C862" s="3">
         <v>0</v>
@@ -62941,7 +63890,7 @@
         <v>2064010821</v>
       </c>
       <c r="B863" s="13" t="s">
-        <v>1275</v>
+        <v>1320</v>
       </c>
       <c r="C863" s="3">
         <v>0</v>
@@ -62961,7 +63910,7 @@
         <v>20630821</v>
       </c>
       <c r="B864" s="13" t="s">
-        <v>1276</v>
+        <v>1321</v>
       </c>
       <c r="C864" s="3">
         <v>0</v>
@@ -62981,7 +63930,7 @@
         <v>20630921</v>
       </c>
       <c r="B865" s="13" t="s">
-        <v>1277</v>
+        <v>1322</v>
       </c>
       <c r="C865" s="3">
         <v>0</v>
@@ -63001,7 +63950,7 @@
         <v>2280</v>
       </c>
       <c r="B866" s="13" t="s">
-        <v>1278</v>
+        <v>1323</v>
       </c>
       <c r="C866" s="3">
         <v>0</v>
@@ -63021,7 +63970,7 @@
         <v>20620821</v>
       </c>
       <c r="B867" s="13" t="s">
-        <v>1279</v>
+        <v>1324</v>
       </c>
       <c r="C867" s="3">
         <v>0</v>
@@ -63041,7 +63990,7 @@
         <v>2066010921</v>
       </c>
       <c r="B868" s="13" t="s">
-        <v>1280</v>
+        <v>1325</v>
       </c>
       <c r="C868" s="3">
         <v>0</v>
@@ -63061,7 +64010,7 @@
         <v>2283</v>
       </c>
       <c r="B869" s="13" t="s">
-        <v>1281</v>
+        <v>1326</v>
       </c>
       <c r="C869" s="3">
         <v>0</v>
@@ -63081,7 +64030,7 @@
         <v>20621021</v>
       </c>
       <c r="B870" s="13" t="s">
-        <v>1282</v>
+        <v>1327</v>
       </c>
       <c r="C870" s="3">
         <v>0</v>
@@ -63101,7 +64050,7 @@
         <v>2285</v>
       </c>
       <c r="B871" s="13" t="s">
-        <v>1283</v>
+        <v>1328</v>
       </c>
       <c r="C871" s="3">
         <v>0</v>
@@ -63121,7 +64070,7 @@
         <v>2286</v>
       </c>
       <c r="B872" s="13" t="s">
-        <v>1284</v>
+        <v>1329</v>
       </c>
       <c r="C872" s="3">
         <v>0</v>
@@ -63141,7 +64090,7 @@
         <v>2065010921</v>
       </c>
       <c r="B873" s="13" t="s">
-        <v>1285</v>
+        <v>1330</v>
       </c>
       <c r="C873" s="3">
         <v>0</v>
@@ -63161,7 +64110,7 @@
         <v>2288</v>
       </c>
       <c r="B874" s="13" t="s">
-        <v>1286</v>
+        <v>1331</v>
       </c>
       <c r="C874" s="3">
         <v>0</v>
@@ -63181,7 +64130,7 @@
         <v>2289</v>
       </c>
       <c r="B875" s="13" t="s">
-        <v>1287</v>
+        <v>1332</v>
       </c>
       <c r="C875" s="3">
         <v>0</v>
@@ -63201,7 +64150,7 @@
         <v>2290</v>
       </c>
       <c r="B876" s="13" t="s">
-        <v>1288</v>
+        <v>1333</v>
       </c>
       <c r="C876" s="3">
         <v>0</v>
@@ -63221,7 +64170,7 @@
         <v>2066010121</v>
       </c>
       <c r="B877" s="13" t="s">
-        <v>1270</v>
+        <v>1315</v>
       </c>
       <c r="C877" s="3">
         <v>0</v>
@@ -63261,7 +64210,7 @@
         <v>2289</v>
       </c>
       <c r="B879" s="13" t="s">
-        <v>1287</v>
+        <v>1332</v>
       </c>
       <c r="C879" s="3">
         <v>0</v>
@@ -63281,7 +64230,7 @@
         <v>2300</v>
       </c>
       <c r="B880" s="13" t="s">
-        <v>1289</v>
+        <v>1334</v>
       </c>
       <c r="C880" s="3">
         <v>0</v>
@@ -63301,7 +64250,7 @@
         <v>2301</v>
       </c>
       <c r="B881" s="13" t="s">
-        <v>1290</v>
+        <v>1335</v>
       </c>
       <c r="C881" s="3">
         <v>0</v>
@@ -63321,7 +64270,7 @@
         <v>20631021</v>
       </c>
       <c r="B882" s="13" t="s">
-        <v>1291</v>
+        <v>1336</v>
       </c>
       <c r="C882" s="3">
         <v>0</v>
@@ -63341,7 +64290,7 @@
         <v>2303</v>
       </c>
       <c r="B883" s="13" t="s">
-        <v>1292</v>
+        <v>1337</v>
       </c>
       <c r="C883" s="3">
         <v>0</v>
@@ -63921,7 +64870,7 @@
         <v>2085010221</v>
       </c>
       <c r="B912" s="13" t="s">
-        <v>1293</v>
+        <v>1338</v>
       </c>
       <c r="C912" s="3">
         <v>0</v>
@@ -64041,7 +64990,7 @@
         <v>20810821</v>
       </c>
       <c r="B918" s="13" t="s">
-        <v>1294</v>
+        <v>1339</v>
       </c>
       <c r="C918" s="3">
         <v>0</v>
@@ -64221,7 +65170,7 @@
         <v>2086010721</v>
       </c>
       <c r="B927" s="13" t="s">
-        <v>1295</v>
+        <v>1340</v>
       </c>
       <c r="C927" s="3">
         <v>0</v>
@@ -64241,7 +65190,7 @@
         <v>2086010821</v>
       </c>
       <c r="B928" s="13" t="s">
-        <v>1296</v>
+        <v>1341</v>
       </c>
       <c r="C928" s="3">
         <v>0</v>
@@ -64261,7 +65210,7 @@
         <v>20811021</v>
       </c>
       <c r="B929" s="13" t="s">
-        <v>1297</v>
+        <v>1342</v>
       </c>
       <c r="C929" s="3">
         <v>0</v>
@@ -64281,7 +65230,7 @@
         <v>2350</v>
       </c>
       <c r="B930" s="13" t="s">
-        <v>1298</v>
+        <v>1343</v>
       </c>
       <c r="C930" s="3">
         <v>0</v>
@@ -64301,7 +65250,7 @@
         <v>2084011021</v>
       </c>
       <c r="B931" s="13" t="s">
-        <v>1299</v>
+        <v>1344</v>
       </c>
       <c r="C931" s="3">
         <v>0</v>
@@ -64321,7 +65270,7 @@
         <v>2084010821</v>
       </c>
       <c r="B932" s="13" t="s">
-        <v>1300</v>
+        <v>1345</v>
       </c>
       <c r="C932" s="3">
         <v>0</v>
@@ -64341,7 +65290,7 @@
         <v>20830821</v>
       </c>
       <c r="B933" s="13" t="s">
-        <v>1301</v>
+        <v>1346</v>
       </c>
       <c r="C933" s="3">
         <v>0</v>
@@ -64361,7 +65310,7 @@
         <v>20830921</v>
       </c>
       <c r="B934" s="13" t="s">
-        <v>1302</v>
+        <v>1347</v>
       </c>
       <c r="C934" s="3">
         <v>0</v>
@@ -64381,7 +65330,7 @@
         <v>2355</v>
       </c>
       <c r="B935" s="13" t="s">
-        <v>1303</v>
+        <v>1348</v>
       </c>
       <c r="C935" s="3">
         <v>0</v>
@@ -64401,7 +65350,7 @@
         <v>20820821</v>
       </c>
       <c r="B936" s="13" t="s">
-        <v>1304</v>
+        <v>1349</v>
       </c>
       <c r="C936" s="3">
         <v>0</v>
@@ -64421,7 +65370,7 @@
         <v>2086010921</v>
       </c>
       <c r="B937" s="13" t="s">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="C937" s="3">
         <v>0</v>
@@ -64441,7 +65390,7 @@
         <v>2358</v>
       </c>
       <c r="B938" s="13" t="s">
-        <v>1306</v>
+        <v>1351</v>
       </c>
       <c r="C938" s="3">
         <v>0</v>
@@ -64461,7 +65410,7 @@
         <v>20821021</v>
       </c>
       <c r="B939" s="13" t="s">
-        <v>1307</v>
+        <v>1352</v>
       </c>
       <c r="C939" s="3">
         <v>0</v>
@@ -64481,7 +65430,7 @@
         <v>2360</v>
       </c>
       <c r="B940" s="13" t="s">
-        <v>1308</v>
+        <v>1353</v>
       </c>
       <c r="C940" s="3">
         <v>0</v>
@@ -64501,7 +65450,7 @@
         <v>2361</v>
       </c>
       <c r="B941" s="13" t="s">
-        <v>1309</v>
+        <v>1354</v>
       </c>
       <c r="C941" s="3">
         <v>0</v>
@@ -64521,7 +65470,7 @@
         <v>2085010921</v>
       </c>
       <c r="B942" s="13" t="s">
-        <v>1310</v>
+        <v>1355</v>
       </c>
       <c r="C942" s="3">
         <v>0</v>
@@ -64541,7 +65490,7 @@
         <v>2363</v>
       </c>
       <c r="B943" s="13" t="s">
-        <v>1311</v>
+        <v>1356</v>
       </c>
       <c r="C943" s="3">
         <v>0</v>
@@ -64561,7 +65510,7 @@
         <v>2364</v>
       </c>
       <c r="B944" s="13" t="s">
-        <v>1312</v>
+        <v>1357</v>
       </c>
       <c r="C944" s="3">
         <v>0</v>
@@ -64581,7 +65530,7 @@
         <v>2365</v>
       </c>
       <c r="B945" s="13" t="s">
-        <v>1313</v>
+        <v>1358</v>
       </c>
       <c r="C945" s="3">
         <v>0</v>
@@ -64641,7 +65590,7 @@
         <v>2364</v>
       </c>
       <c r="B948" s="13" t="s">
-        <v>1312</v>
+        <v>1357</v>
       </c>
       <c r="C948" s="3">
         <v>0</v>
@@ -64661,7 +65610,7 @@
         <v>2375</v>
       </c>
       <c r="B949" s="13" t="s">
-        <v>1314</v>
+        <v>1359</v>
       </c>
       <c r="C949" s="3">
         <v>0</v>
@@ -64681,7 +65630,7 @@
         <v>2376</v>
       </c>
       <c r="B950" s="13" t="s">
-        <v>1315</v>
+        <v>1360</v>
       </c>
       <c r="C950" s="3">
         <v>0</v>
@@ -64701,7 +65650,7 @@
         <v>20831021</v>
       </c>
       <c r="B951" s="13" t="s">
-        <v>1316</v>
+        <v>1361</v>
       </c>
       <c r="C951" s="3">
         <v>0</v>
@@ -64721,7 +65670,7 @@
         <v>2378</v>
       </c>
       <c r="B952" s="13" t="s">
-        <v>1317</v>
+        <v>1362</v>
       </c>
       <c r="C952" s="3">
         <v>0</v>
@@ -65301,7 +66250,7 @@
         <v>2075010221</v>
       </c>
       <c r="B981" s="13" t="s">
-        <v>1318</v>
+        <v>1363</v>
       </c>
       <c r="C981" s="3">
         <v>0</v>
@@ -65421,7 +66370,7 @@
         <v>20710821</v>
       </c>
       <c r="B987" s="13" t="s">
-        <v>1319</v>
+        <v>1364</v>
       </c>
       <c r="C987" s="3">
         <v>0</v>
@@ -65601,7 +66550,7 @@
         <v>2076010721</v>
       </c>
       <c r="B996" s="13" t="s">
-        <v>1320</v>
+        <v>1365</v>
       </c>
       <c r="C996" s="3">
         <v>0</v>
@@ -65621,7 +66570,7 @@
         <v>2076010821</v>
       </c>
       <c r="B997" s="13" t="s">
-        <v>1321</v>
+        <v>1366</v>
       </c>
       <c r="C997" s="3">
         <v>0</v>
@@ -65641,7 +66590,7 @@
         <v>20711021</v>
       </c>
       <c r="B998" s="13" t="s">
-        <v>1322</v>
+        <v>1367</v>
       </c>
       <c r="C998" s="3">
         <v>0</v>
@@ -65661,7 +66610,7 @@
         <v>2425</v>
       </c>
       <c r="B999" s="13" t="s">
-        <v>1323</v>
+        <v>1368</v>
       </c>
       <c r="C999" s="3">
         <v>0</v>
@@ -65681,7 +66630,7 @@
         <v>2074011021</v>
       </c>
       <c r="B1000" s="13" t="s">
-        <v>1324</v>
+        <v>1369</v>
       </c>
       <c r="C1000" s="3">
         <v>0</v>
@@ -65701,7 +66650,7 @@
         <v>2074010821</v>
       </c>
       <c r="B1001" s="13" t="s">
-        <v>1325</v>
+        <v>1370</v>
       </c>
       <c r="C1001" s="3">
         <v>0</v>
@@ -65721,7 +66670,7 @@
         <v>20730821</v>
       </c>
       <c r="B1002" s="13" t="s">
-        <v>1326</v>
+        <v>1371</v>
       </c>
       <c r="C1002" s="3">
         <v>0</v>
@@ -65741,7 +66690,7 @@
         <v>20730921</v>
       </c>
       <c r="B1003" s="13" t="s">
-        <v>1327</v>
+        <v>1372</v>
       </c>
       <c r="C1003" s="3">
         <v>0</v>
@@ -65761,7 +66710,7 @@
         <v>2430</v>
       </c>
       <c r="B1004" s="13" t="s">
-        <v>1328</v>
+        <v>1373</v>
       </c>
       <c r="C1004" s="3">
         <v>0</v>
@@ -65781,7 +66730,7 @@
         <v>20720821</v>
       </c>
       <c r="B1005" s="13" t="s">
-        <v>1329</v>
+        <v>1374</v>
       </c>
       <c r="C1005" s="3">
         <v>0</v>
@@ -65801,7 +66750,7 @@
         <v>2076010921</v>
       </c>
       <c r="B1006" s="13" t="s">
-        <v>1330</v>
+        <v>1375</v>
       </c>
       <c r="C1006" s="3">
         <v>0</v>
@@ -65821,7 +66770,7 @@
         <v>2433</v>
       </c>
       <c r="B1007" s="13" t="s">
-        <v>1331</v>
+        <v>1376</v>
       </c>
       <c r="C1007" s="3">
         <v>0</v>
@@ -65881,7 +66830,7 @@
         <v>2442</v>
       </c>
       <c r="B1010" s="13" t="s">
-        <v>1332</v>
+        <v>1377</v>
       </c>
       <c r="C1010" s="3">
         <v>0</v>
@@ -65901,7 +66850,7 @@
         <v>20731021</v>
       </c>
       <c r="B1011" s="13" t="s">
-        <v>1333</v>
+        <v>1378</v>
       </c>
       <c r="C1011" s="3">
         <v>0</v>
@@ -65921,7 +66870,7 @@
         <v>2444</v>
       </c>
       <c r="B1012" s="13" t="s">
-        <v>1334</v>
+        <v>1379</v>
       </c>
       <c r="C1012" s="3">
         <v>0</v>
@@ -66501,7 +67450,7 @@
         <v>2095010221</v>
       </c>
       <c r="B1041" s="13" t="s">
-        <v>1335</v>
+        <v>1380</v>
       </c>
       <c r="C1041" s="3">
         <v>0</v>
@@ -66621,7 +67570,7 @@
         <v>20910821</v>
       </c>
       <c r="B1047" s="13" t="s">
-        <v>1336</v>
+        <v>1381</v>
       </c>
       <c r="C1047" s="3">
         <v>0</v>
@@ -66821,7 +67770,7 @@
         <v>2096010821</v>
       </c>
       <c r="B1057" s="13" t="s">
-        <v>1337</v>
+        <v>1382</v>
       </c>
       <c r="C1057" s="3">
         <v>0</v>
@@ -66841,7 +67790,7 @@
         <v>20911021</v>
       </c>
       <c r="B1058" s="13" t="s">
-        <v>1338</v>
+        <v>1383</v>
       </c>
       <c r="C1058" s="3">
         <v>0</v>
@@ -66861,7 +67810,7 @@
         <v>2491</v>
       </c>
       <c r="B1059" s="13" t="s">
-        <v>1339</v>
+        <v>1384</v>
       </c>
       <c r="C1059" s="3">
         <v>0</v>
@@ -66881,7 +67830,7 @@
         <v>2094011021</v>
       </c>
       <c r="B1060" s="13" t="s">
-        <v>1340</v>
+        <v>1385</v>
       </c>
       <c r="C1060" s="3">
         <v>0</v>
@@ -66901,7 +67850,7 @@
         <v>2094010821</v>
       </c>
       <c r="B1061" s="13" t="s">
-        <v>1341</v>
+        <v>1386</v>
       </c>
       <c r="C1061" s="3">
         <v>0</v>
@@ -66921,7 +67870,7 @@
         <v>20930821</v>
       </c>
       <c r="B1062" s="13" t="s">
-        <v>1342</v>
+        <v>1387</v>
       </c>
       <c r="C1062" s="3">
         <v>0</v>
@@ -66941,7 +67890,7 @@
         <v>20930921</v>
       </c>
       <c r="B1063" s="13" t="s">
-        <v>1343</v>
+        <v>1388</v>
       </c>
       <c r="C1063" s="3">
         <v>0</v>
@@ -66961,7 +67910,7 @@
         <v>2496</v>
       </c>
       <c r="B1064" s="13" t="s">
-        <v>1344</v>
+        <v>1389</v>
       </c>
       <c r="C1064" s="3">
         <v>0</v>
@@ -66981,7 +67930,7 @@
         <v>20920821</v>
       </c>
       <c r="B1065" s="13" t="s">
-        <v>1345</v>
+        <v>1390</v>
       </c>
       <c r="C1065" s="3">
         <v>0</v>
@@ -67001,7 +67950,7 @@
         <v>2096010921</v>
       </c>
       <c r="B1066" s="13" t="s">
-        <v>1346</v>
+        <v>1391</v>
       </c>
       <c r="C1066" s="3">
         <v>0</v>
@@ -67021,7 +67970,7 @@
         <v>2499</v>
       </c>
       <c r="B1067" s="13" t="s">
-        <v>1347</v>
+        <v>1392</v>
       </c>
       <c r="C1067" s="3">
         <v>0</v>
@@ -67041,7 +67990,7 @@
         <v>20921021</v>
       </c>
       <c r="B1068" s="13" t="s">
-        <v>1348</v>
+        <v>1393</v>
       </c>
       <c r="C1068" s="3">
         <v>0</v>
@@ -67061,7 +68010,7 @@
         <v>2501</v>
       </c>
       <c r="B1069" s="13" t="s">
-        <v>1349</v>
+        <v>1394</v>
       </c>
       <c r="C1069" s="3">
         <v>0</v>
@@ -67081,7 +68030,7 @@
         <v>2502</v>
       </c>
       <c r="B1070" s="13" t="s">
-        <v>1350</v>
+        <v>1395</v>
       </c>
       <c r="C1070" s="3">
         <v>0</v>
@@ -67101,7 +68050,7 @@
         <v>2095010921</v>
       </c>
       <c r="B1071" s="13" t="s">
-        <v>1351</v>
+        <v>1396</v>
       </c>
       <c r="C1071" s="3">
         <v>0</v>
@@ -67121,7 +68070,7 @@
         <v>2504</v>
       </c>
       <c r="B1072" s="13" t="s">
-        <v>1352</v>
+        <v>1397</v>
       </c>
       <c r="C1072" s="3">
         <v>0</v>
@@ -67141,7 +68090,7 @@
         <v>2505</v>
       </c>
       <c r="B1073" s="13" t="s">
-        <v>1353</v>
+        <v>1398</v>
       </c>
       <c r="C1073" s="3">
         <v>0</v>
@@ -67161,7 +68110,7 @@
         <v>2506</v>
       </c>
       <c r="B1074" s="13" t="s">
-        <v>1354</v>
+        <v>1399</v>
       </c>
       <c r="C1074" s="3">
         <v>0</v>
@@ -67221,7 +68170,7 @@
         <v>2505</v>
       </c>
       <c r="B1077" s="13" t="s">
-        <v>1353</v>
+        <v>1398</v>
       </c>
       <c r="C1077" s="3">
         <v>0</v>
@@ -67241,7 +68190,7 @@
         <v>2516</v>
       </c>
       <c r="B1078" s="13" t="s">
-        <v>1355</v>
+        <v>1400</v>
       </c>
       <c r="C1078" s="3">
         <v>0</v>
@@ -67261,7 +68210,7 @@
         <v>2517</v>
       </c>
       <c r="B1079" s="13" t="s">
-        <v>1356</v>
+        <v>1401</v>
       </c>
       <c r="C1079" s="3">
         <v>0</v>
@@ -67281,7 +68230,7 @@
         <v>20931021</v>
       </c>
       <c r="B1080" s="13" t="s">
-        <v>1357</v>
+        <v>1402</v>
       </c>
       <c r="C1080" s="3">
         <v>0</v>
@@ -67301,7 +68250,7 @@
         <v>2519</v>
       </c>
       <c r="B1081" s="13" t="s">
-        <v>1358</v>
+        <v>1403</v>
       </c>
       <c r="C1081" s="3">
         <v>0</v>
@@ -67321,7 +68270,7 @@
         <v>20410131</v>
       </c>
       <c r="B1082" s="12" t="s">
-        <v>1359</v>
+        <v>1404</v>
       </c>
       <c r="C1082" s="3">
         <v>0</v>
@@ -67341,7 +68290,7 @@
         <v>20610131</v>
       </c>
       <c r="B1083" s="12" t="s">
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="C1083" s="3">
         <v>0</v>
@@ -67361,7 +68310,7 @@
         <v>20810131</v>
       </c>
       <c r="B1084" s="12" t="s">
-        <v>1361</v>
+        <v>1406</v>
       </c>
       <c r="C1084" s="3">
         <v>0</v>
@@ -67381,7 +68330,7 @@
         <v>20710131</v>
       </c>
       <c r="B1085" s="12" t="s">
-        <v>1362</v>
+        <v>1407</v>
       </c>
       <c r="C1085" s="3">
         <v>0</v>
@@ -67401,7 +68350,7 @@
         <v>20910131</v>
       </c>
       <c r="B1086" s="12" t="s">
-        <v>1363</v>
+        <v>1408</v>
       </c>
       <c r="C1086" s="3">
         <v>0</v>
@@ -67441,7 +68390,7 @@
         <v>2526</v>
       </c>
       <c r="B1088" s="12" t="s">
-        <v>1364</v>
+        <v>1409</v>
       </c>
       <c r="C1088" s="3">
         <v>0</v>
@@ -67461,7 +68410,7 @@
         <v>2527</v>
       </c>
       <c r="B1089" s="12" t="s">
-        <v>1365</v>
+        <v>1410</v>
       </c>
       <c r="C1089" s="3">
         <v>0</v>
@@ -67501,7 +68450,7 @@
         <v>2529</v>
       </c>
       <c r="B1091" s="12" t="s">
-        <v>1366</v>
+        <v>1411</v>
       </c>
       <c r="C1091" s="3">
         <v>0</v>
@@ -67521,7 +68470,7 @@
         <v>2530</v>
       </c>
       <c r="B1092" s="12" t="s">
-        <v>1367</v>
+        <v>1412</v>
       </c>
       <c r="C1092" s="3">
         <v>0</v>
@@ -67541,7 +68490,7 @@
         <v>2531</v>
       </c>
       <c r="B1093" s="12" t="s">
-        <v>1368</v>
+        <v>1413</v>
       </c>
       <c r="C1093" s="3">
         <v>0</v>
@@ -67561,7 +68510,7 @@
         <v>2532</v>
       </c>
       <c r="B1094" s="12" t="s">
-        <v>1369</v>
+        <v>1414</v>
       </c>
       <c r="C1094" s="3">
         <v>0</v>
@@ -67641,7 +68590,7 @@
         <v>20610231</v>
       </c>
       <c r="B1098" s="12" t="s">
-        <v>1370</v>
+        <v>1415</v>
       </c>
       <c r="C1098" s="3">
         <v>0</v>
@@ -67661,7 +68610,7 @@
         <v>20810231</v>
       </c>
       <c r="B1099" s="12" t="s">
-        <v>1371</v>
+        <v>1416</v>
       </c>
       <c r="C1099" s="3">
         <v>0</v>
@@ -67681,7 +68630,7 @@
         <v>20710231</v>
       </c>
       <c r="B1100" s="12" t="s">
-        <v>1372</v>
+        <v>1417</v>
       </c>
       <c r="C1100" s="3">
         <v>0</v>
@@ -67701,7 +68650,7 @@
         <v>20910231</v>
       </c>
       <c r="B1101" s="12" t="s">
-        <v>1373</v>
+        <v>1418</v>
       </c>
       <c r="C1101" s="3">
         <v>0</v>
@@ -67741,7 +68690,7 @@
         <v>20610331</v>
       </c>
       <c r="B1103" s="12" t="s">
-        <v>1374</v>
+        <v>1419</v>
       </c>
       <c r="C1103" s="3">
         <v>0</v>
@@ -67781,7 +68730,7 @@
         <v>20710331</v>
       </c>
       <c r="B1105" s="12" t="s">
-        <v>1375</v>
+        <v>1420</v>
       </c>
       <c r="C1105" s="3">
         <v>0</v>
@@ -67801,7 +68750,7 @@
         <v>20910331</v>
       </c>
       <c r="B1106" s="12" t="s">
-        <v>1376</v>
+        <v>1421</v>
       </c>
       <c r="C1106" s="3">
         <v>0</v>
@@ -67921,7 +68870,7 @@
         <v>20420131</v>
       </c>
       <c r="B1112" s="12" t="s">
-        <v>1377</v>
+        <v>1422</v>
       </c>
       <c r="C1112" s="3">
         <v>0</v>
@@ -67941,7 +68890,7 @@
         <v>20620131</v>
       </c>
       <c r="B1113" s="12" t="s">
-        <v>1378</v>
+        <v>1423</v>
       </c>
       <c r="C1113" s="3">
         <v>0</v>
@@ -67961,7 +68910,7 @@
         <v>20820131</v>
       </c>
       <c r="B1114" s="12" t="s">
-        <v>1379</v>
+        <v>1424</v>
       </c>
       <c r="C1114" s="3">
         <v>0</v>
@@ -67981,7 +68930,7 @@
         <v>20720131</v>
       </c>
       <c r="B1115" s="12" t="s">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="C1115" s="3">
         <v>0</v>
@@ -68121,7 +69070,7 @@
         <v>20420331</v>
       </c>
       <c r="B1122" s="12" t="s">
-        <v>1381</v>
+        <v>1426</v>
       </c>
       <c r="C1122" s="3">
         <v>0</v>
@@ -68141,7 +69090,7 @@
         <v>20620331</v>
       </c>
       <c r="B1123" s="12" t="s">
-        <v>1382</v>
+        <v>1427</v>
       </c>
       <c r="C1123" s="3">
         <v>0</v>
@@ -68161,7 +69110,7 @@
         <v>20820331</v>
       </c>
       <c r="B1124" s="12" t="s">
-        <v>1383</v>
+        <v>1428</v>
       </c>
       <c r="C1124" s="3">
         <v>0</v>
@@ -68181,7 +69130,7 @@
         <v>20720331</v>
       </c>
       <c r="B1125" s="12" t="s">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="C1125" s="3">
         <v>0</v>
@@ -68201,7 +69150,7 @@
         <v>20920331</v>
       </c>
       <c r="B1126" s="12" t="s">
-        <v>1385</v>
+        <v>1430</v>
       </c>
       <c r="C1126" s="3">
         <v>0</v>
@@ -68421,7 +69370,7 @@
         <v>20430231</v>
       </c>
       <c r="B1137" s="12" t="s">
-        <v>1386</v>
+        <v>1431</v>
       </c>
       <c r="C1137" s="3">
         <v>0</v>
@@ -68441,7 +69390,7 @@
         <v>20630231</v>
       </c>
       <c r="B1138" s="12" t="s">
-        <v>1387</v>
+        <v>1432</v>
       </c>
       <c r="C1138" s="3">
         <v>0</v>
@@ -68461,7 +69410,7 @@
         <v>20830231</v>
       </c>
       <c r="B1139" s="12" t="s">
-        <v>1388</v>
+        <v>1433</v>
       </c>
       <c r="C1139" s="3">
         <v>0</v>
@@ -68481,7 +69430,7 @@
         <v>20730231</v>
       </c>
       <c r="B1140" s="12" t="s">
-        <v>1389</v>
+        <v>1434</v>
       </c>
       <c r="C1140" s="3">
         <v>0</v>
@@ -68641,7 +69590,7 @@
         <v>2586</v>
       </c>
       <c r="B1148" s="12" t="s">
-        <v>1390</v>
+        <v>1435</v>
       </c>
       <c r="C1148" s="3">
         <v>0</v>
@@ -68661,7 +69610,7 @@
         <v>2587</v>
       </c>
       <c r="B1149" s="12" t="s">
-        <v>1391</v>
+        <v>1436</v>
       </c>
       <c r="C1149" s="3">
         <v>0</v>
@@ -68681,7 +69630,7 @@
         <v>2588</v>
       </c>
       <c r="B1150" s="12" t="s">
-        <v>1392</v>
+        <v>1437</v>
       </c>
       <c r="C1150" s="3">
         <v>0</v>
@@ -68721,7 +69670,7 @@
         <v>20430431</v>
       </c>
       <c r="B1152" s="12" t="s">
-        <v>1393</v>
+        <v>1438</v>
       </c>
       <c r="C1152" s="3">
         <v>0</v>
@@ -68741,7 +69690,7 @@
         <v>20630431</v>
       </c>
       <c r="B1153" s="12" t="s">
-        <v>1394</v>
+        <v>1439</v>
       </c>
       <c r="C1153" s="3">
         <v>0</v>
@@ -68761,7 +69710,7 @@
         <v>20830431</v>
       </c>
       <c r="B1154" s="12" t="s">
-        <v>1395</v>
+        <v>1440</v>
       </c>
       <c r="C1154" s="3">
         <v>0</v>
@@ -68781,7 +69730,7 @@
         <v>20730431</v>
       </c>
       <c r="B1155" s="12" t="s">
-        <v>1396</v>
+        <v>1441</v>
       </c>
       <c r="C1155" s="3">
         <v>0</v>
@@ -68801,7 +69750,7 @@
         <v>20930431</v>
       </c>
       <c r="B1156" s="12" t="s">
-        <v>1397</v>
+        <v>1442</v>
       </c>
       <c r="C1156" s="3">
         <v>0</v>
@@ -69021,7 +69970,7 @@
         <v>1015343</v>
       </c>
       <c r="B1167" s="19" t="s">
-        <v>1398</v>
+        <v>1443</v>
       </c>
       <c r="C1167" s="3">
         <v>0</v>
@@ -69671,7 +70620,7 @@
         <v>2031081199</v>
       </c>
       <c r="B1210" s="13" t="s">
-        <v>1028</v>
+        <v>1073</v>
       </c>
       <c r="C1210" s="3">
         <v>0</v>
@@ -69691,7 +70640,7 @@
         <v>2031091199</v>
       </c>
       <c r="B1211" s="13" t="s">
-        <v>1029</v>
+        <v>1074</v>
       </c>
       <c r="C1211" s="3">
         <v>0</v>
@@ -69711,7 +70660,7 @@
         <v>2031101199</v>
       </c>
       <c r="B1212" s="13" t="s">
-        <v>1030</v>
+        <v>1075</v>
       </c>
       <c r="C1212" s="3">
         <v>0</v>
@@ -69731,7 +70680,7 @@
         <v>102999</v>
       </c>
       <c r="B1213" s="13" t="s">
-        <v>1031</v>
+        <v>1076</v>
       </c>
       <c r="C1213" s="3">
         <v>0</v>
@@ -69751,7 +70700,7 @@
         <v>103099</v>
       </c>
       <c r="B1214" s="13" t="s">
-        <v>1032</v>
+        <v>1077</v>
       </c>
       <c r="C1214" s="3">
         <v>0</v>
@@ -69791,7 +70740,7 @@
         <v>103299</v>
       </c>
       <c r="B1216" s="13" t="s">
-        <v>1033</v>
+        <v>1078</v>
       </c>
       <c r="C1216" s="3">
         <v>0</v>
@@ -69811,7 +70760,7 @@
         <v>103399</v>
       </c>
       <c r="B1217" s="13" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
       <c r="C1217" s="3">
         <v>0</v>
@@ -69831,7 +70780,7 @@
         <v>103499</v>
       </c>
       <c r="B1218" s="13" t="s">
-        <v>1035</v>
+        <v>1080</v>
       </c>
       <c r="C1218" s="3">
         <v>0</v>
@@ -70353,7 +71302,7 @@
         <v>105999</v>
       </c>
       <c r="B1243" s="13" t="s">
-        <v>1036</v>
+        <v>1081</v>
       </c>
       <c r="C1243" s="3">
         <v>0</v>
@@ -70395,7 +71344,7 @@
         <v>106199</v>
       </c>
       <c r="B1245" s="13" t="s">
-        <v>1037</v>
+        <v>1082</v>
       </c>
       <c r="C1245" s="3">
         <v>0</v>
@@ -70437,7 +71386,7 @@
         <v>106399</v>
       </c>
       <c r="B1247" s="13" t="s">
-        <v>1038</v>
+        <v>1083</v>
       </c>
       <c r="C1247" s="3">
         <v>0</v>
@@ -70458,7 +71407,7 @@
         <v>106499</v>
       </c>
       <c r="B1248" s="13" t="s">
-        <v>1039</v>
+        <v>1084</v>
       </c>
       <c r="C1248" s="3">
         <v>0</v>
@@ -70479,7 +71428,7 @@
         <v>106599</v>
       </c>
       <c r="B1249" s="13" t="s">
-        <v>1040</v>
+        <v>1085</v>
       </c>
       <c r="C1249" s="3">
         <v>0</v>
@@ -70752,7 +71701,7 @@
         <v>107999</v>
       </c>
       <c r="B1262" s="13" t="s">
-        <v>1042</v>
+        <v>1087</v>
       </c>
       <c r="C1262" s="3">
         <v>0</v>
@@ -71249,7 +72198,7 @@
         <v>2013081199</v>
       </c>
       <c r="B1286" s="13" t="s">
-        <v>1043</v>
+        <v>1088</v>
       </c>
       <c r="C1286" s="3">
         <v>0</v>
@@ -71289,7 +72238,7 @@
         <v>2013131199</v>
       </c>
       <c r="B1288" s="13" t="s">
-        <v>1044</v>
+        <v>1089</v>
       </c>
       <c r="C1288" s="3">
         <v>0</v>
@@ -71309,7 +72258,7 @@
         <v>110699</v>
       </c>
       <c r="B1289" s="13" t="s">
-        <v>1045</v>
+        <v>1090</v>
       </c>
       <c r="C1289" s="3">
         <v>0</v>
@@ -71329,7 +72278,7 @@
         <v>110799</v>
       </c>
       <c r="B1290" s="13" t="s">
-        <v>1046</v>
+        <v>1091</v>
       </c>
       <c r="C1290" s="3">
         <v>0</v>
@@ -71369,7 +72318,7 @@
         <v>2013121199</v>
       </c>
       <c r="B1292" s="13" t="s">
-        <v>1047</v>
+        <v>1092</v>
       </c>
       <c r="C1292" s="3">
         <v>0</v>
@@ -71409,7 +72358,7 @@
         <v>111199</v>
       </c>
       <c r="B1294" s="13" t="s">
-        <v>1048</v>
+        <v>1093</v>
       </c>
       <c r="C1294" s="3">
         <v>0</v>
@@ -71429,7 +72378,7 @@
         <v>111299</v>
       </c>
       <c r="B1295" s="13" t="s">
-        <v>1049</v>
+        <v>1094</v>
       </c>
       <c r="C1295" s="3">
         <v>0</v>
@@ -71449,7 +72398,7 @@
         <v>111399</v>
       </c>
       <c r="B1296" s="13" t="s">
-        <v>1050</v>
+        <v>1095</v>
       </c>
       <c r="C1296" s="3">
         <v>0</v>
@@ -71689,7 +72638,7 @@
         <v>2012071199</v>
       </c>
       <c r="B1308" s="13" t="s">
-        <v>1051</v>
+        <v>1096</v>
       </c>
       <c r="C1308" s="3">
         <v>0</v>
@@ -71850,7 +72799,7 @@
         <v>113399</v>
       </c>
       <c r="B1316" s="13" t="s">
-        <v>1052</v>
+        <v>1097</v>
       </c>
       <c r="C1316" s="3">
         <v>0</v>
@@ -71955,7 +72904,7 @@
         <v>113899</v>
       </c>
       <c r="B1321" s="13" t="s">
-        <v>1053</v>
+        <v>1098</v>
       </c>
       <c r="C1321" s="3">
         <v>0</v>
@@ -71976,7 +72925,7 @@
         <v>2012101199</v>
       </c>
       <c r="B1322" s="13" t="s">
-        <v>1054</v>
+        <v>1099</v>
       </c>
       <c r="C1322" s="3">
         <v>0</v>
@@ -71997,7 +72946,7 @@
         <v>114099</v>
       </c>
       <c r="B1323" s="13" t="s">
-        <v>1055</v>
+        <v>1100</v>
       </c>
       <c r="C1323" s="3">
         <v>0</v>
@@ -72018,7 +72967,7 @@
         <v>114199</v>
       </c>
       <c r="B1324" s="13" t="s">
-        <v>1056</v>
+        <v>1101</v>
       </c>
       <c r="C1324" s="3">
         <v>0</v>
@@ -72039,7 +72988,7 @@
         <v>114299</v>
       </c>
       <c r="B1325" s="13" t="s">
-        <v>1057</v>
+        <v>1102</v>
       </c>
       <c r="C1325" s="3">
         <v>0</v>
@@ -72060,7 +73009,7 @@
         <v>114399</v>
       </c>
       <c r="B1326" s="13" t="s">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="C1326" s="3">
         <v>0</v>
@@ -72102,7 +73051,7 @@
         <v>114599</v>
       </c>
       <c r="B1328" s="13" t="s">
-        <v>1059</v>
+        <v>1104</v>
       </c>
       <c r="C1328" s="3">
         <v>0</v>
@@ -72123,7 +73072,7 @@
         <v>114699</v>
       </c>
       <c r="B1329" s="13" t="s">
-        <v>1060</v>
+        <v>1105</v>
       </c>
       <c r="C1329" s="3">
         <v>0</v>
@@ -72522,7 +73471,7 @@
         <v>116599</v>
       </c>
       <c r="B1348" s="16" t="s">
-        <v>1061</v>
+        <v>1106</v>
       </c>
       <c r="C1348" s="3">
         <v>0</v>
@@ -72543,7 +73492,7 @@
         <v>116799</v>
       </c>
       <c r="B1349" s="16" t="s">
-        <v>1063</v>
+        <v>1108</v>
       </c>
       <c r="C1349" s="3">
         <v>0</v>
@@ -73088,7 +74037,7 @@
         <v>1280045099</v>
       </c>
       <c r="B1375" s="13" t="s">
-        <v>1064</v>
+        <v>1109</v>
       </c>
       <c r="C1375" s="3">
         <v>0</v>
@@ -73168,7 +74117,7 @@
         <v>1280045599</v>
       </c>
       <c r="B1379" s="13" t="s">
-        <v>1065</v>
+        <v>1110</v>
       </c>
       <c r="C1379" s="3">
         <v>0</v>
@@ -73188,7 +74137,7 @@
         <v>2041081199</v>
       </c>
       <c r="B1380" s="13" t="s">
-        <v>1066</v>
+        <v>1111</v>
       </c>
       <c r="C1380" s="3">
         <v>0</v>
@@ -73348,7 +74297,7 @@
         <v>1280065599</v>
       </c>
       <c r="B1388" s="13" t="s">
-        <v>1067</v>
+        <v>1112</v>
       </c>
       <c r="C1388" s="3">
         <v>0</v>
@@ -73388,7 +74337,7 @@
         <v>2041101199</v>
       </c>
       <c r="B1390" s="13" t="s">
-        <v>1068</v>
+        <v>1113</v>
       </c>
       <c r="C1390" s="3">
         <v>0</v>
@@ -73408,7 +74357,7 @@
         <v>120999</v>
       </c>
       <c r="B1391" s="13" t="s">
-        <v>1069</v>
+        <v>1114</v>
       </c>
       <c r="C1391" s="3">
         <v>0</v>
@@ -73428,7 +74377,7 @@
         <v>2043081199</v>
       </c>
       <c r="B1392" s="13" t="s">
-        <v>1070</v>
+        <v>1115</v>
       </c>
       <c r="C1392" s="3">
         <v>0</v>
@@ -73448,7 +74397,7 @@
         <v>2043091199</v>
       </c>
       <c r="B1393" s="13" t="s">
-        <v>1071</v>
+        <v>1116</v>
       </c>
       <c r="C1393" s="3">
         <v>0</v>
@@ -73488,7 +74437,7 @@
         <v>2042081199</v>
       </c>
       <c r="B1395" s="13" t="s">
-        <v>1072</v>
+        <v>1117</v>
       </c>
       <c r="C1395" s="3">
         <v>0</v>
@@ -73508,7 +74457,7 @@
         <v>1280066599</v>
       </c>
       <c r="B1396" s="13" t="s">
-        <v>1073</v>
+        <v>1118</v>
       </c>
       <c r="C1396" s="3">
         <v>0</v>
@@ -73528,7 +74477,7 @@
         <v>121599</v>
       </c>
       <c r="B1397" s="13" t="s">
-        <v>1074</v>
+        <v>1119</v>
       </c>
       <c r="C1397" s="3">
         <v>0</v>
@@ -73548,7 +74497,7 @@
         <v>2042101199</v>
       </c>
       <c r="B1398" s="13" t="s">
-        <v>1075</v>
+        <v>1120</v>
       </c>
       <c r="C1398" s="3">
         <v>0</v>
@@ -73568,7 +74517,7 @@
         <v>121799</v>
       </c>
       <c r="B1399" s="13" t="s">
-        <v>1076</v>
+        <v>1121</v>
       </c>
       <c r="C1399" s="3">
         <v>0</v>
@@ -73588,7 +74537,7 @@
         <v>1280048599</v>
       </c>
       <c r="B1400" s="13" t="s">
-        <v>1077</v>
+        <v>1122</v>
       </c>
       <c r="C1400" s="3">
         <v>0</v>
@@ -73608,7 +74557,7 @@
         <v>121999</v>
       </c>
       <c r="B1401" s="13" t="s">
-        <v>1078</v>
+        <v>1123</v>
       </c>
       <c r="C1401" s="3">
         <v>0</v>
@@ -73628,7 +74577,7 @@
         <v>122099</v>
       </c>
       <c r="B1402" s="13" t="s">
-        <v>1079</v>
+        <v>1124</v>
       </c>
       <c r="C1402" s="3">
         <v>0</v>
@@ -73648,7 +74597,7 @@
         <v>122199</v>
       </c>
       <c r="B1403" s="13" t="s">
-        <v>1080</v>
+        <v>1125</v>
       </c>
       <c r="C1403" s="3">
         <v>0</v>
@@ -73688,7 +74637,7 @@
         <v>122699</v>
       </c>
       <c r="B1405" s="13" t="s">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="C1405" s="3">
         <v>0</v>
@@ -73728,7 +74677,7 @@
         <v>122099</v>
       </c>
       <c r="B1407" s="13" t="s">
-        <v>1079</v>
+        <v>1124</v>
       </c>
       <c r="C1407" s="3">
         <v>0</v>
@@ -73748,7 +74697,7 @@
         <v>123299</v>
       </c>
       <c r="B1408" s="13" t="s">
-        <v>1082</v>
+        <v>1127</v>
       </c>
       <c r="C1408" s="3">
         <v>0</v>
@@ -73768,7 +74717,7 @@
         <v>123399</v>
       </c>
       <c r="B1409" s="13" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="C1409" s="3">
         <v>0</v>
@@ -73788,7 +74737,7 @@
         <v>2043101199</v>
       </c>
       <c r="B1410" s="13" t="s">
-        <v>1084</v>
+        <v>1129</v>
       </c>
       <c r="C1410" s="3">
         <v>0</v>
@@ -73808,7 +74757,7 @@
         <v>123599</v>
       </c>
       <c r="B1411" s="13" t="s">
-        <v>1085</v>
+        <v>1130</v>
       </c>
       <c r="C1411" s="3">
         <v>0</v>
@@ -73828,7 +74777,7 @@
         <v>123699</v>
       </c>
       <c r="B1412" s="13" t="s">
-        <v>1086</v>
+        <v>1131</v>
       </c>
       <c r="C1412" s="3">
         <v>0</v>
@@ -73848,7 +74797,7 @@
         <v>123799</v>
       </c>
       <c r="B1413" s="13" t="s">
-        <v>1087</v>
+        <v>1132</v>
       </c>
       <c r="C1413" s="3">
         <v>0</v>
@@ -74368,7 +75317,7 @@
         <v>1280064599</v>
       </c>
       <c r="B1439" s="13" t="s">
-        <v>1088</v>
+        <v>1133</v>
       </c>
       <c r="C1439" s="3">
         <v>0</v>
@@ -74428,7 +75377,7 @@
         <v>1280045199</v>
       </c>
       <c r="B1442" s="13" t="s">
-        <v>1089</v>
+        <v>1134</v>
       </c>
       <c r="C1442" s="3">
         <v>0</v>
@@ -74528,7 +75477,7 @@
         <v>1280045699</v>
       </c>
       <c r="B1447" s="13" t="s">
-        <v>1090</v>
+        <v>1135</v>
       </c>
       <c r="C1447" s="3">
         <v>0</v>
@@ -74548,7 +75497,7 @@
         <v>2061081199</v>
       </c>
       <c r="B1448" s="13" t="s">
-        <v>1091</v>
+        <v>1136</v>
       </c>
       <c r="C1448" s="3">
         <v>0</v>
@@ -74648,7 +75597,7 @@
         <v>1280062699</v>
       </c>
       <c r="B1453" s="13" t="s">
-        <v>1092</v>
+        <v>1137</v>
       </c>
       <c r="C1453" s="3">
         <v>0</v>
@@ -74728,7 +75677,7 @@
         <v>1280065699</v>
       </c>
       <c r="B1457" s="13" t="s">
-        <v>1093</v>
+        <v>1138</v>
       </c>
       <c r="C1457" s="3">
         <v>0</v>
@@ -74768,7 +75717,7 @@
         <v>2061101199</v>
       </c>
       <c r="B1459" s="13" t="s">
-        <v>1094</v>
+        <v>1139</v>
       </c>
       <c r="C1459" s="3">
         <v>0</v>
@@ -74788,7 +75737,7 @@
         <v>128499</v>
       </c>
       <c r="B1460" s="13" t="s">
-        <v>1095</v>
+        <v>1140</v>
       </c>
       <c r="C1460" s="3">
         <v>0</v>
@@ -74808,7 +75757,7 @@
         <v>1280031199</v>
       </c>
       <c r="B1461" s="13" t="s">
-        <v>1096</v>
+        <v>1141</v>
       </c>
       <c r="C1461" s="3">
         <v>0</v>
@@ -74828,7 +75777,7 @@
         <v>1280030199</v>
       </c>
       <c r="B1462" s="13" t="s">
-        <v>1097</v>
+        <v>1142</v>
       </c>
       <c r="C1462" s="3">
         <v>0</v>
@@ -74848,7 +75797,7 @@
         <v>2063081199</v>
       </c>
       <c r="B1463" s="13" t="s">
-        <v>1098</v>
+        <v>1143</v>
       </c>
       <c r="C1463" s="3">
         <v>0</v>
@@ -74868,7 +75817,7 @@
         <v>2063091199</v>
       </c>
       <c r="B1464" s="13" t="s">
-        <v>1099</v>
+        <v>1144</v>
       </c>
       <c r="C1464" s="3">
         <v>0</v>
@@ -74908,7 +75857,7 @@
         <v>2062081199</v>
       </c>
       <c r="B1466" s="13" t="s">
-        <v>1100</v>
+        <v>1145</v>
       </c>
       <c r="C1466" s="3">
         <v>0</v>
@@ -74928,7 +75877,7 @@
         <v>1280066699</v>
       </c>
       <c r="B1467" s="13" t="s">
-        <v>1101</v>
+        <v>1146</v>
       </c>
       <c r="C1467" s="3">
         <v>0</v>
@@ -74948,7 +75897,7 @@
         <v>129299</v>
       </c>
       <c r="B1468" s="13" t="s">
-        <v>1102</v>
+        <v>1147</v>
       </c>
       <c r="C1468" s="3">
         <v>0</v>
@@ -74968,7 +75917,7 @@
         <v>2062101199</v>
       </c>
       <c r="B1469" s="13" t="s">
-        <v>1103</v>
+        <v>1148</v>
       </c>
       <c r="C1469" s="3">
         <v>0</v>
@@ -74988,7 +75937,7 @@
         <v>129499</v>
       </c>
       <c r="B1470" s="13" t="s">
-        <v>1104</v>
+        <v>1149</v>
       </c>
       <c r="C1470" s="3">
         <v>0</v>
@@ -75008,7 +75957,7 @@
         <v>129599</v>
       </c>
       <c r="B1471" s="13" t="s">
-        <v>1105</v>
+        <v>1150</v>
       </c>
       <c r="C1471" s="3">
         <v>0</v>
@@ -75028,7 +75977,7 @@
         <v>1280048699</v>
       </c>
       <c r="B1472" s="13" t="s">
-        <v>1106</v>
+        <v>1151</v>
       </c>
       <c r="C1472" s="3">
         <v>0</v>
@@ -75048,7 +75997,7 @@
         <v>129799</v>
       </c>
       <c r="B1473" s="13" t="s">
-        <v>1107</v>
+        <v>1152</v>
       </c>
       <c r="C1473" s="3">
         <v>0</v>
@@ -75068,7 +76017,7 @@
         <v>129899</v>
       </c>
       <c r="B1474" s="13" t="s">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="C1474" s="3">
         <v>0</v>
@@ -75088,7 +76037,7 @@
         <v>129999</v>
       </c>
       <c r="B1475" s="13" t="s">
-        <v>1109</v>
+        <v>1154</v>
       </c>
       <c r="C1475" s="3">
         <v>0</v>
@@ -75108,7 +76057,7 @@
         <v>1280062699</v>
       </c>
       <c r="B1476" s="13" t="s">
-        <v>1092</v>
+        <v>1137</v>
       </c>
       <c r="C1476" s="3">
         <v>0</v>
@@ -75128,7 +76077,7 @@
         <v>130499</v>
       </c>
       <c r="B1477" s="13" t="s">
-        <v>1110</v>
+        <v>1155</v>
       </c>
       <c r="C1477" s="3">
         <v>0</v>
@@ -75168,7 +76117,7 @@
         <v>130999</v>
       </c>
       <c r="B1479" s="13" t="s">
-        <v>1111</v>
+        <v>1156</v>
       </c>
       <c r="C1479" s="3">
         <v>0</v>
@@ -75188,7 +76137,7 @@
         <v>129899</v>
       </c>
       <c r="B1480" s="13" t="s">
-        <v>1108</v>
+        <v>1153</v>
       </c>
       <c r="C1480" s="3">
         <v>0</v>
@@ -75208,7 +76157,7 @@
         <v>131199</v>
       </c>
       <c r="B1481" s="13" t="s">
-        <v>1112</v>
+        <v>1157</v>
       </c>
       <c r="C1481" s="3">
         <v>0</v>
@@ -75228,7 +76177,7 @@
         <v>131299</v>
       </c>
       <c r="B1482" s="13" t="s">
-        <v>1113</v>
+        <v>1158</v>
       </c>
       <c r="C1482" s="3">
         <v>0</v>
@@ -75248,7 +76197,7 @@
         <v>2063101199</v>
       </c>
       <c r="B1483" s="13" t="s">
-        <v>1114</v>
+        <v>1159</v>
       </c>
       <c r="C1483" s="3">
         <v>0</v>
@@ -75268,7 +76217,7 @@
         <v>131499</v>
       </c>
       <c r="B1484" s="13" t="s">
-        <v>1115</v>
+        <v>1160</v>
       </c>
       <c r="C1484" s="3">
         <v>0</v>
@@ -75288,7 +76237,7 @@
         <v>131599</v>
       </c>
       <c r="B1485" s="13" t="s">
-        <v>1116</v>
+        <v>1161</v>
       </c>
       <c r="C1485" s="3">
         <v>0</v>
@@ -75308,7 +76257,7 @@
         <v>131699</v>
       </c>
       <c r="B1486" s="13" t="s">
-        <v>1117</v>
+        <v>1162</v>
       </c>
       <c r="C1486" s="3">
         <v>0</v>
@@ -75328,7 +76277,7 @@
         <v>131799</v>
       </c>
       <c r="B1487" s="13" t="s">
-        <v>1118</v>
+        <v>1163</v>
       </c>
       <c r="C1487" s="3">
         <v>0</v>
@@ -75908,7 +76857,7 @@
         <v>1280045299</v>
       </c>
       <c r="B1516" s="13" t="s">
-        <v>1119</v>
+        <v>1164</v>
       </c>
       <c r="C1516" s="3">
         <v>0</v>
@@ -76008,7 +76957,7 @@
         <v>1280045799</v>
       </c>
       <c r="B1521" s="13" t="s">
-        <v>1120</v>
+        <v>1165</v>
       </c>
       <c r="C1521" s="3">
         <v>0</v>
@@ -76028,7 +76977,7 @@
         <v>2081081199</v>
       </c>
       <c r="B1522" s="13" t="s">
-        <v>1121</v>
+        <v>1166</v>
       </c>
       <c r="C1522" s="3">
         <v>0</v>
@@ -76208,7 +77157,7 @@
         <v>1280065799</v>
       </c>
       <c r="B1531" s="13" t="s">
-        <v>1122</v>
+        <v>1167</v>
       </c>
       <c r="C1531" s="3">
         <v>0</v>
@@ -76228,7 +77177,7 @@
         <v>1280066299</v>
       </c>
       <c r="B1532" s="13" t="s">
-        <v>1123</v>
+        <v>1168</v>
       </c>
       <c r="C1532" s="3">
         <v>0</v>
@@ -76248,7 +77197,7 @@
         <v>2081101199</v>
       </c>
       <c r="B1533" s="13" t="s">
-        <v>1124</v>
+        <v>1169</v>
       </c>
       <c r="C1533" s="3">
         <v>0</v>
@@ -76268,7 +77217,7 @@
         <v>136499</v>
       </c>
       <c r="B1534" s="13" t="s">
-        <v>1125</v>
+        <v>1170</v>
       </c>
       <c r="C1534" s="3">
         <v>0</v>
@@ -76288,7 +77237,7 @@
         <v>1280031299</v>
       </c>
       <c r="B1535" s="13" t="s">
-        <v>1126</v>
+        <v>1171</v>
       </c>
       <c r="C1535" s="3">
         <v>0</v>
@@ -76308,7 +77257,7 @@
         <v>1280030299</v>
       </c>
       <c r="B1536" s="13" t="s">
-        <v>1127</v>
+        <v>1172</v>
       </c>
       <c r="C1536" s="3">
         <v>0</v>
@@ -76328,7 +77277,7 @@
         <v>2083081199</v>
       </c>
       <c r="B1537" s="13" t="s">
-        <v>1128</v>
+        <v>1173</v>
       </c>
       <c r="C1537" s="3">
         <v>0</v>
@@ -76348,7 +77297,7 @@
         <v>2083091199</v>
       </c>
       <c r="B1538" s="13" t="s">
-        <v>1129</v>
+        <v>1174</v>
       </c>
       <c r="C1538" s="3">
         <v>0</v>
@@ -76368,7 +77317,7 @@
         <v>136999</v>
       </c>
       <c r="B1539" s="13" t="s">
-        <v>1130</v>
+        <v>1175</v>
       </c>
       <c r="C1539" s="3">
         <v>0</v>
@@ -76388,7 +77337,7 @@
         <v>2082081199</v>
       </c>
       <c r="B1540" s="13" t="s">
-        <v>1131</v>
+        <v>1176</v>
       </c>
       <c r="C1540" s="3">
         <v>0</v>
@@ -76408,7 +77357,7 @@
         <v>1280066799</v>
       </c>
       <c r="B1541" s="13" t="s">
-        <v>1132</v>
+        <v>1177</v>
       </c>
       <c r="C1541" s="3">
         <v>0</v>
@@ -76428,7 +77377,7 @@
         <v>137299</v>
       </c>
       <c r="B1542" s="13" t="s">
-        <v>1133</v>
+        <v>1178</v>
       </c>
       <c r="C1542" s="3">
         <v>0</v>
@@ -76448,7 +77397,7 @@
         <v>2082101199</v>
       </c>
       <c r="B1543" s="13" t="s">
-        <v>1134</v>
+        <v>1179</v>
       </c>
       <c r="C1543" s="3">
         <v>0</v>
@@ -76468,7 +77417,7 @@
         <v>137499</v>
       </c>
       <c r="B1544" s="13" t="s">
-        <v>1135</v>
+        <v>1180</v>
       </c>
       <c r="C1544" s="3">
         <v>0</v>
@@ -76488,7 +77437,7 @@
         <v>137599</v>
       </c>
       <c r="B1545" s="13" t="s">
-        <v>1136</v>
+        <v>1181</v>
       </c>
       <c r="C1545" s="3">
         <v>0</v>
@@ -76508,7 +77457,7 @@
         <v>1280048799</v>
       </c>
       <c r="B1546" s="13" t="s">
-        <v>1137</v>
+        <v>1182</v>
       </c>
       <c r="C1546" s="3">
         <v>0</v>
@@ -76528,7 +77477,7 @@
         <v>137799</v>
       </c>
       <c r="B1547" s="13" t="s">
-        <v>1138</v>
+        <v>1183</v>
       </c>
       <c r="C1547" s="3">
         <v>0</v>
@@ -76548,7 +77497,7 @@
         <v>137899</v>
       </c>
       <c r="B1548" s="13" t="s">
-        <v>1139</v>
+        <v>1184</v>
       </c>
       <c r="C1548" s="3">
         <v>0</v>
@@ -76568,7 +77517,7 @@
         <v>137999</v>
       </c>
       <c r="B1549" s="13" t="s">
-        <v>1140</v>
+        <v>1185</v>
       </c>
       <c r="C1549" s="3">
         <v>0</v>
@@ -76608,7 +77557,7 @@
         <v>138499</v>
       </c>
       <c r="B1551" s="13" t="s">
-        <v>1141</v>
+        <v>1186</v>
       </c>
       <c r="C1551" s="3">
         <v>0</v>
@@ -76648,7 +77597,7 @@
         <v>138999</v>
       </c>
       <c r="B1553" s="13" t="s">
-        <v>1142</v>
+        <v>1187</v>
       </c>
       <c r="C1553" s="3">
         <v>0</v>
@@ -76668,7 +77617,7 @@
         <v>137899</v>
       </c>
       <c r="B1554" s="13" t="s">
-        <v>1139</v>
+        <v>1184</v>
       </c>
       <c r="C1554" s="3">
         <v>0</v>
@@ -76688,7 +77637,7 @@
         <v>139199</v>
       </c>
       <c r="B1555" s="13" t="s">
-        <v>1143</v>
+        <v>1188</v>
       </c>
       <c r="C1555" s="3">
         <v>0</v>
@@ -76708,7 +77657,7 @@
         <v>139299</v>
       </c>
       <c r="B1556" s="13" t="s">
-        <v>1144</v>
+        <v>1189</v>
       </c>
       <c r="C1556" s="3">
         <v>0</v>
@@ -76728,7 +77677,7 @@
         <v>2083101199</v>
       </c>
       <c r="B1557" s="13" t="s">
-        <v>1145</v>
+        <v>1190</v>
       </c>
       <c r="C1557" s="3">
         <v>0</v>
@@ -76748,7 +77697,7 @@
         <v>139499</v>
       </c>
       <c r="B1558" s="13" t="s">
-        <v>1146</v>
+        <v>1191</v>
       </c>
       <c r="C1558" s="3">
         <v>0</v>
@@ -76768,7 +77717,7 @@
         <v>139599</v>
       </c>
       <c r="B1559" s="13" t="s">
-        <v>1147</v>
+        <v>1192</v>
       </c>
       <c r="C1559" s="3">
         <v>0</v>
@@ -76788,7 +77737,7 @@
         <v>139699</v>
       </c>
       <c r="B1560" s="13" t="s">
-        <v>1148</v>
+        <v>1193</v>
       </c>
       <c r="C1560" s="3">
         <v>0</v>
@@ -76808,7 +77757,7 @@
         <v>139799</v>
       </c>
       <c r="B1561" s="13" t="s">
-        <v>1149</v>
+        <v>1194</v>
       </c>
       <c r="C1561" s="3">
         <v>0</v>
@@ -77388,7 +78337,7 @@
         <v>1280045499</v>
       </c>
       <c r="B1590" s="13" t="s">
-        <v>1150</v>
+        <v>1195</v>
       </c>
       <c r="C1590" s="3">
         <v>0</v>
@@ -77488,7 +78437,7 @@
         <v>1280045999</v>
       </c>
       <c r="B1595" s="13" t="s">
-        <v>1151</v>
+        <v>1196</v>
       </c>
       <c r="C1595" s="3">
         <v>0</v>
@@ -77508,7 +78457,7 @@
         <v>2071081199</v>
       </c>
       <c r="B1596" s="13" t="s">
-        <v>1152</v>
+        <v>1197</v>
       </c>
       <c r="C1596" s="3">
         <v>0</v>
@@ -77688,7 +78637,7 @@
         <v>1280065999</v>
       </c>
       <c r="B1605" s="13" t="s">
-        <v>1153</v>
+        <v>1198</v>
       </c>
       <c r="C1605" s="3">
         <v>0</v>
@@ -77708,7 +78657,7 @@
         <v>1280066499</v>
       </c>
       <c r="B1606" s="13" t="s">
-        <v>1154</v>
+        <v>1199</v>
       </c>
       <c r="C1606" s="3">
         <v>0</v>
@@ -77728,7 +78677,7 @@
         <v>2071101199</v>
       </c>
       <c r="B1607" s="13" t="s">
-        <v>1155</v>
+        <v>1200</v>
       </c>
       <c r="C1607" s="3">
         <v>0</v>
@@ -77748,7 +78697,7 @@
         <v>144499</v>
       </c>
       <c r="B1608" s="13" t="s">
-        <v>1156</v>
+        <v>1201</v>
       </c>
       <c r="C1608" s="3">
         <v>0</v>
@@ -77768,7 +78717,7 @@
         <v>1280031499</v>
       </c>
       <c r="B1609" s="13" t="s">
-        <v>1157</v>
+        <v>1202</v>
       </c>
       <c r="C1609" s="3">
         <v>0</v>
@@ -77788,7 +78737,7 @@
         <v>1280030499</v>
       </c>
       <c r="B1610" s="13" t="s">
-        <v>1158</v>
+        <v>1203</v>
       </c>
       <c r="C1610" s="3">
         <v>0</v>
@@ -77808,7 +78757,7 @@
         <v>2073081199</v>
       </c>
       <c r="B1611" s="13" t="s">
-        <v>1159</v>
+        <v>1204</v>
       </c>
       <c r="C1611" s="3">
         <v>0</v>
@@ -77828,7 +78777,7 @@
         <v>2073091199</v>
       </c>
       <c r="B1612" s="13" t="s">
-        <v>1160</v>
+        <v>1205</v>
       </c>
       <c r="C1612" s="3">
         <v>0</v>
@@ -77848,7 +78797,7 @@
         <v>144999</v>
       </c>
       <c r="B1613" s="13" t="s">
-        <v>1161</v>
+        <v>1206</v>
       </c>
       <c r="C1613" s="3">
         <v>0</v>
@@ -77868,7 +78817,7 @@
         <v>2072081199</v>
       </c>
       <c r="B1614" s="13" t="s">
-        <v>1162</v>
+        <v>1207</v>
       </c>
       <c r="C1614" s="3">
         <v>0</v>
@@ -77888,7 +78837,7 @@
         <v>1280066999</v>
       </c>
       <c r="B1615" s="13" t="s">
-        <v>1163</v>
+        <v>1208</v>
       </c>
       <c r="C1615" s="3">
         <v>0</v>
@@ -77908,7 +78857,7 @@
         <v>145299</v>
       </c>
       <c r="B1616" s="13" t="s">
-        <v>1164</v>
+        <v>1209</v>
       </c>
       <c r="C1616" s="3">
         <v>0</v>
@@ -77948,7 +78897,7 @@
         <v>145799</v>
       </c>
       <c r="B1618" s="13" t="s">
-        <v>1165</v>
+        <v>1210</v>
       </c>
       <c r="C1618" s="3">
         <v>0</v>
@@ -77988,7 +78937,7 @@
         <v>146299</v>
       </c>
       <c r="B1620" s="13" t="s">
-        <v>1166</v>
+        <v>1211</v>
       </c>
       <c r="C1620" s="3">
         <v>0</v>
@@ -78008,7 +78957,7 @@
         <v>146399</v>
       </c>
       <c r="B1621" s="13" t="s">
-        <v>1167</v>
+        <v>1212</v>
       </c>
       <c r="C1621" s="3">
         <v>0</v>
@@ -78028,7 +78977,7 @@
         <v>2073101199</v>
       </c>
       <c r="B1622" s="13" t="s">
-        <v>1168</v>
+        <v>1213</v>
       </c>
       <c r="C1622" s="3">
         <v>0</v>
@@ -78048,7 +78997,7 @@
         <v>146599</v>
       </c>
       <c r="B1623" s="13" t="s">
-        <v>1169</v>
+        <v>1214</v>
       </c>
       <c r="C1623" s="3">
         <v>0</v>
@@ -78068,7 +79017,7 @@
         <v>146699</v>
       </c>
       <c r="B1624" s="13" t="s">
-        <v>1170</v>
+        <v>1215</v>
       </c>
       <c r="C1624" s="3">
         <v>0</v>
@@ -78088,7 +79037,7 @@
         <v>146799</v>
       </c>
       <c r="B1625" s="13" t="s">
-        <v>1171</v>
+        <v>1216</v>
       </c>
       <c r="C1625" s="3">
         <v>0</v>
@@ -78108,7 +79057,7 @@
         <v>146899</v>
       </c>
       <c r="B1626" s="13" t="s">
-        <v>1172</v>
+        <v>1217</v>
       </c>
       <c r="C1626" s="3">
         <v>0</v>
@@ -78688,7 +79637,7 @@
         <v>1280045399</v>
       </c>
       <c r="B1655" s="13" t="s">
-        <v>1173</v>
+        <v>1218</v>
       </c>
       <c r="C1655" s="3">
         <v>0</v>
@@ -78788,7 +79737,7 @@
         <v>1280045899</v>
       </c>
       <c r="B1660" s="13" t="s">
-        <v>1174</v>
+        <v>1219</v>
       </c>
       <c r="C1660" s="3">
         <v>0</v>
@@ -78808,7 +79757,7 @@
         <v>2091081199</v>
       </c>
       <c r="B1661" s="13" t="s">
-        <v>1175</v>
+        <v>1220</v>
       </c>
       <c r="C1661" s="3">
         <v>0</v>
@@ -78988,7 +79937,7 @@
         <v>1280065899</v>
       </c>
       <c r="B1670" s="13" t="s">
-        <v>1176</v>
+        <v>1221</v>
       </c>
       <c r="C1670" s="3">
         <v>0</v>
@@ -79028,7 +79977,7 @@
         <v>2091101199</v>
       </c>
       <c r="B1672" s="13" t="s">
-        <v>1177</v>
+        <v>1222</v>
       </c>
       <c r="C1672" s="3">
         <v>0</v>
@@ -79048,7 +79997,7 @@
         <v>1280031399</v>
       </c>
       <c r="B1673" s="13" t="s">
-        <v>1178</v>
+        <v>1223</v>
       </c>
       <c r="C1673" s="3">
         <v>0</v>
@@ -79068,7 +80017,7 @@
         <v>1280030399</v>
       </c>
       <c r="B1674" s="13" t="s">
-        <v>1179</v>
+        <v>1224</v>
       </c>
       <c r="C1674" s="3">
         <v>0</v>
@@ -79088,7 +80037,7 @@
         <v>2093081199</v>
       </c>
       <c r="B1675" s="13" t="s">
-        <v>1180</v>
+        <v>1225</v>
       </c>
       <c r="C1675" s="3">
         <v>0</v>
@@ -79108,7 +80057,7 @@
         <v>2093091199</v>
       </c>
       <c r="B1676" s="13" t="s">
-        <v>1181</v>
+        <v>1226</v>
       </c>
       <c r="C1676" s="3">
         <v>0</v>
@@ -79148,7 +80097,7 @@
         <v>2092081199</v>
       </c>
       <c r="B1678" s="13" t="s">
-        <v>1182</v>
+        <v>1227</v>
       </c>
       <c r="C1678" s="3">
         <v>0</v>
@@ -79168,7 +80117,7 @@
         <v>1280066899</v>
       </c>
       <c r="B1679" s="13" t="s">
-        <v>1183</v>
+        <v>1228</v>
       </c>
       <c r="C1679" s="3">
         <v>0</v>
@@ -79188,7 +80137,7 @@
         <v>152399</v>
       </c>
       <c r="B1680" s="13" t="s">
-        <v>1184</v>
+        <v>1229</v>
       </c>
       <c r="C1680" s="3">
         <v>0</v>
@@ -79208,7 +80157,7 @@
         <v>2092101199</v>
       </c>
       <c r="B1681" s="13" t="s">
-        <v>1185</v>
+        <v>1230</v>
       </c>
       <c r="C1681" s="3">
         <v>0</v>
@@ -79228,7 +80177,7 @@
         <v>152599</v>
       </c>
       <c r="B1682" s="13" t="s">
-        <v>1186</v>
+        <v>1231</v>
       </c>
       <c r="C1682" s="3">
         <v>0</v>
@@ -79248,7 +80197,7 @@
         <v>152699</v>
       </c>
       <c r="B1683" s="13" t="s">
-        <v>1187</v>
+        <v>1232</v>
       </c>
       <c r="C1683" s="3">
         <v>0</v>
@@ -79268,7 +80217,7 @@
         <v>1280048899</v>
       </c>
       <c r="B1684" s="13" t="s">
-        <v>1188</v>
+        <v>1233</v>
       </c>
       <c r="C1684" s="3">
         <v>0</v>
@@ -79288,7 +80237,7 @@
         <v>152899</v>
       </c>
       <c r="B1685" s="13" t="s">
-        <v>1189</v>
+        <v>1234</v>
       </c>
       <c r="C1685" s="3">
         <v>0</v>
@@ -79308,7 +80257,7 @@
         <v>152999</v>
       </c>
       <c r="B1686" s="13" t="s">
-        <v>1190</v>
+        <v>1235</v>
       </c>
       <c r="C1686" s="3">
         <v>0</v>
@@ -79328,7 +80277,7 @@
         <v>153099</v>
       </c>
       <c r="B1687" s="13" t="s">
-        <v>1191</v>
+        <v>1236</v>
       </c>
       <c r="C1687" s="3">
         <v>0</v>
@@ -79368,7 +80317,7 @@
         <v>153599</v>
       </c>
       <c r="B1689" s="13" t="s">
-        <v>1192</v>
+        <v>1237</v>
       </c>
       <c r="C1689" s="3">
         <v>0</v>
@@ -79408,7 +80357,7 @@
         <v>154099</v>
       </c>
       <c r="B1691" s="13" t="s">
-        <v>1193</v>
+        <v>1238</v>
       </c>
       <c r="C1691" s="3">
         <v>0</v>
@@ -79428,7 +80377,7 @@
         <v>152999</v>
       </c>
       <c r="B1692" s="13" t="s">
-        <v>1190</v>
+        <v>1235</v>
       </c>
       <c r="C1692" s="3">
         <v>0</v>
@@ -79448,7 +80397,7 @@
         <v>154299</v>
       </c>
       <c r="B1693" s="13" t="s">
-        <v>1194</v>
+        <v>1239</v>
       </c>
       <c r="C1693" s="3">
         <v>0</v>
@@ -79468,7 +80417,7 @@
         <v>154399</v>
       </c>
       <c r="B1694" s="13" t="s">
-        <v>1195</v>
+        <v>1240</v>
       </c>
       <c r="C1694" s="3">
         <v>0</v>
@@ -79488,7 +80437,7 @@
         <v>2093101199</v>
       </c>
       <c r="B1695" s="13" t="s">
-        <v>1196</v>
+        <v>1241</v>
       </c>
       <c r="C1695" s="3">
         <v>0</v>
@@ -79508,7 +80457,7 @@
         <v>154599</v>
       </c>
       <c r="B1696" s="13" t="s">
-        <v>1197</v>
+        <v>1242</v>
       </c>
       <c r="C1696" s="3">
         <v>0</v>
@@ -79528,7 +80477,7 @@
         <v>154699</v>
       </c>
       <c r="B1697" s="13" t="s">
-        <v>1198</v>
+        <v>1243</v>
       </c>
       <c r="C1697" s="3">
         <v>0</v>
@@ -79548,7 +80497,7 @@
         <v>154799</v>
       </c>
       <c r="B1698" s="13" t="s">
-        <v>1199</v>
+        <v>1244</v>
       </c>
       <c r="C1698" s="3">
         <v>0</v>
@@ -79568,7 +80517,7 @@
         <v>154899</v>
       </c>
       <c r="B1699" s="13" t="s">
-        <v>1200</v>
+        <v>1245</v>
       </c>
       <c r="C1699" s="3">
         <v>0</v>
@@ -79588,7 +80537,7 @@
         <v>154999</v>
       </c>
       <c r="B1700" s="13" t="s">
-        <v>1201</v>
+        <v>1246</v>
       </c>
       <c r="C1700" s="3">
         <v>0</v>
@@ -79608,7 +80557,7 @@
         <v>155099</v>
       </c>
       <c r="B1701" s="13" t="s">
-        <v>1202</v>
+        <v>1247</v>
       </c>
       <c r="C1701" s="3">
         <v>0</v>
@@ -79628,7 +80577,7 @@
         <v>155199</v>
       </c>
       <c r="B1702" s="13" t="s">
-        <v>1203</v>
+        <v>1248</v>
       </c>
       <c r="C1702" s="3">
         <v>0</v>
@@ -79648,7 +80597,7 @@
         <v>155299</v>
       </c>
       <c r="B1703" s="13" t="s">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="C1703" s="3">
         <v>0</v>
@@ -79668,7 +80617,7 @@
         <v>155399</v>
       </c>
       <c r="B1704" s="13" t="s">
-        <v>1205</v>
+        <v>1250</v>
       </c>
       <c r="C1704" s="3">
         <v>0</v>
@@ -80368,7 +81317,7 @@
         <v>158599</v>
       </c>
       <c r="B1739" s="12" t="s">
-        <v>1206</v>
+        <v>1251</v>
       </c>
       <c r="C1739" s="3">
         <v>0</v>
@@ -80388,7 +81337,7 @@
         <v>158699</v>
       </c>
       <c r="B1740" s="12" t="s">
-        <v>1207</v>
+        <v>1252</v>
       </c>
       <c r="C1740" s="3">
         <v>0</v>
@@ -81428,7 +82377,7 @@
         <v>201999</v>
       </c>
       <c r="B1792" s="13" t="s">
-        <v>1208</v>
+        <v>1253</v>
       </c>
       <c r="C1792" s="3">
         <v>0</v>
@@ -81568,7 +82517,7 @@
         <v>2031082199</v>
       </c>
       <c r="B1799" s="13" t="s">
-        <v>1209</v>
+        <v>1254</v>
       </c>
       <c r="C1799" s="3">
         <v>0</v>
@@ -81588,7 +82537,7 @@
         <v>2031092199</v>
       </c>
       <c r="B1800" s="13" t="s">
-        <v>1210</v>
+        <v>1255</v>
       </c>
       <c r="C1800" s="3">
         <v>0</v>
@@ -81608,7 +82557,7 @@
         <v>2031102199</v>
       </c>
       <c r="B1801" s="13" t="s">
-        <v>1211</v>
+        <v>1256</v>
       </c>
       <c r="C1801" s="3">
         <v>0</v>
@@ -81628,7 +82577,7 @@
         <v>202999</v>
       </c>
       <c r="B1802" s="13" t="s">
-        <v>1212</v>
+        <v>1257</v>
       </c>
       <c r="C1802" s="3">
         <v>0</v>
@@ -81648,7 +82597,7 @@
         <v>203099</v>
       </c>
       <c r="B1803" s="13" t="s">
-        <v>1213</v>
+        <v>1258</v>
       </c>
       <c r="C1803" s="3">
         <v>0</v>
@@ -81688,7 +82637,7 @@
         <v>203299</v>
       </c>
       <c r="B1805" s="13" t="s">
-        <v>1214</v>
+        <v>1259</v>
       </c>
       <c r="C1805" s="3">
         <v>0</v>
@@ -81708,7 +82657,7 @@
         <v>203399</v>
       </c>
       <c r="B1806" s="13" t="s">
-        <v>1215</v>
+        <v>1260</v>
       </c>
       <c r="C1806" s="3">
         <v>0</v>
@@ -81728,7 +82677,7 @@
         <v>203499</v>
       </c>
       <c r="B1807" s="13" t="s">
-        <v>1216</v>
+        <v>1261</v>
       </c>
       <c r="C1807" s="3">
         <v>0</v>
@@ -82188,7 +83137,7 @@
         <v>205799</v>
       </c>
       <c r="B1830" s="12" t="s">
-        <v>1217</v>
+        <v>1262</v>
       </c>
       <c r="C1830" s="3">
         <v>0</v>
@@ -82208,7 +83157,7 @@
         <v>205899</v>
       </c>
       <c r="B1831" s="13" t="s">
-        <v>1218</v>
+        <v>1263</v>
       </c>
       <c r="C1831" s="3">
         <v>0</v>
@@ -82228,7 +83177,7 @@
         <v>206099</v>
       </c>
       <c r="B1832" s="13" t="s">
-        <v>1219</v>
+        <v>1264</v>
       </c>
       <c r="C1832" s="3">
         <v>0</v>
@@ -82268,7 +83217,7 @@
         <v>206299</v>
       </c>
       <c r="B1834" s="13" t="s">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="C1834" s="3">
         <v>0</v>
@@ -82288,7 +83237,7 @@
         <v>206399</v>
       </c>
       <c r="B1835" s="13" t="s">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="C1835" s="3">
         <v>0</v>
@@ -82308,7 +83257,7 @@
         <v>206499</v>
       </c>
       <c r="B1836" s="13" t="s">
-        <v>1222</v>
+        <v>1267</v>
       </c>
       <c r="C1836" s="3">
         <v>0</v>
@@ -82568,7 +83517,7 @@
         <v>207799</v>
       </c>
       <c r="B1849" s="13" t="s">
-        <v>1223</v>
+        <v>1268</v>
       </c>
       <c r="C1849" s="3">
         <v>0</v>
@@ -82948,7 +83897,7 @@
         <v>209699</v>
       </c>
       <c r="B1868" s="12" t="s">
-        <v>1224</v>
+        <v>1269</v>
       </c>
       <c r="C1868" s="3">
         <v>0</v>
@@ -83048,7 +83997,7 @@
         <v>2013082199</v>
       </c>
       <c r="B1873" s="13" t="s">
-        <v>1225</v>
+        <v>1270</v>
       </c>
       <c r="C1873" s="3">
         <v>0</v>
@@ -83088,7 +84037,7 @@
         <v>2013132199</v>
       </c>
       <c r="B1875" s="13" t="s">
-        <v>1226</v>
+        <v>1271</v>
       </c>
       <c r="C1875" s="3">
         <v>0</v>
@@ -83108,7 +84057,7 @@
         <v>210499</v>
       </c>
       <c r="B1876" s="13" t="s">
-        <v>1227</v>
+        <v>1272</v>
       </c>
       <c r="C1876" s="3">
         <v>0</v>
@@ -83128,7 +84077,7 @@
         <v>2013122199</v>
       </c>
       <c r="B1877" s="13" t="s">
-        <v>1228</v>
+        <v>1273</v>
       </c>
       <c r="C1877" s="3">
         <v>0</v>
@@ -83168,7 +84117,7 @@
         <v>210899</v>
       </c>
       <c r="B1879" s="13" t="s">
-        <v>1229</v>
+        <v>1274</v>
       </c>
       <c r="C1879" s="3">
         <v>0</v>
@@ -83188,7 +84137,7 @@
         <v>210999</v>
       </c>
       <c r="B1880" s="13" t="s">
-        <v>1230</v>
+        <v>1275</v>
       </c>
       <c r="C1880" s="3">
         <v>0</v>
@@ -83208,7 +84157,7 @@
         <v>211099</v>
       </c>
       <c r="B1881" s="13" t="s">
-        <v>1231</v>
+        <v>1276</v>
       </c>
       <c r="C1881" s="3">
         <v>0</v>
@@ -83428,7 +84377,7 @@
         <v>212199</v>
       </c>
       <c r="B1892" s="12" t="s">
-        <v>1232</v>
+        <v>1277</v>
       </c>
       <c r="C1892" s="3">
         <v>0</v>
@@ -83448,7 +84397,7 @@
         <v>2012072199</v>
       </c>
       <c r="B1893" s="13" t="s">
-        <v>1233</v>
+        <v>1278</v>
       </c>
       <c r="C1893" s="3">
         <v>0</v>
@@ -83588,7 +84537,7 @@
         <v>213099</v>
       </c>
       <c r="B1900" s="13" t="s">
-        <v>1234</v>
+        <v>1279</v>
       </c>
       <c r="C1900" s="3">
         <v>0</v>
@@ -83688,7 +84637,7 @@
         <v>213599</v>
       </c>
       <c r="B1905" s="13" t="s">
-        <v>1235</v>
+        <v>1280</v>
       </c>
       <c r="C1905" s="3">
         <v>0</v>
@@ -83708,7 +84657,7 @@
         <v>2012102199</v>
       </c>
       <c r="B1906" s="13" t="s">
-        <v>1236</v>
+        <v>1281</v>
       </c>
       <c r="C1906" s="3">
         <v>0</v>
@@ -83728,7 +84677,7 @@
         <v>213799</v>
       </c>
       <c r="B1907" s="13" t="s">
-        <v>1237</v>
+        <v>1282</v>
       </c>
       <c r="C1907" s="3">
         <v>0</v>
@@ -83748,7 +84697,7 @@
         <v>213899</v>
       </c>
       <c r="B1908" s="13" t="s">
-        <v>1238</v>
+        <v>1283</v>
       </c>
       <c r="C1908" s="3">
         <v>0</v>
@@ -83768,7 +84717,7 @@
         <v>213999</v>
       </c>
       <c r="B1909" s="13" t="s">
-        <v>1239</v>
+        <v>1284</v>
       </c>
       <c r="C1909" s="3">
         <v>0</v>
@@ -83788,7 +84737,7 @@
         <v>214099</v>
       </c>
       <c r="B1910" s="13" t="s">
-        <v>1240</v>
+        <v>1285</v>
       </c>
       <c r="C1910" s="3">
         <v>0</v>
@@ -83808,7 +84757,7 @@
         <v>214199</v>
       </c>
       <c r="B1911" s="12" t="s">
-        <v>1241</v>
+        <v>1286</v>
       </c>
       <c r="C1911" s="3">
         <v>0</v>
@@ -83828,7 +84777,7 @@
         <v>214299</v>
       </c>
       <c r="B1912" s="13" t="s">
-        <v>1242</v>
+        <v>1287</v>
       </c>
       <c r="C1912" s="3">
         <v>0</v>
@@ -83848,7 +84797,7 @@
         <v>214399</v>
       </c>
       <c r="B1913" s="12" t="s">
-        <v>1243</v>
+        <v>1288</v>
       </c>
       <c r="C1913" s="3">
         <v>0</v>
@@ -83868,7 +84817,7 @@
         <v>214499</v>
       </c>
       <c r="B1914" s="12" t="s">
-        <v>1244</v>
+        <v>1289</v>
       </c>
       <c r="C1914" s="3">
         <v>0</v>
@@ -84208,7 +85157,7 @@
         <v>216299</v>
       </c>
       <c r="B1931" s="13" t="s">
-        <v>1246</v>
+        <v>1291</v>
       </c>
       <c r="C1931" s="3">
         <v>0</v>
@@ -84728,7 +85677,7 @@
         <v>1280051099</v>
       </c>
       <c r="B1957" s="13" t="s">
-        <v>1247</v>
+        <v>1292</v>
       </c>
       <c r="C1957" s="3">
         <v>0</v>
@@ -84828,7 +85777,7 @@
         <v>2041082199</v>
       </c>
       <c r="B1962" s="13" t="s">
-        <v>1248</v>
+        <v>1293</v>
       </c>
       <c r="C1962" s="3">
         <v>0</v>
@@ -85008,7 +85957,7 @@
         <v>1280072099</v>
       </c>
       <c r="B1971" s="13" t="s">
-        <v>1249</v>
+        <v>1294</v>
       </c>
       <c r="C1971" s="3">
         <v>0</v>
@@ -85028,7 +85977,7 @@
         <v>2041102199</v>
       </c>
       <c r="B1972" s="13" t="s">
-        <v>1250</v>
+        <v>1295</v>
       </c>
       <c r="C1972" s="3">
         <v>0</v>
@@ -85048,7 +85997,7 @@
         <v>220499</v>
       </c>
       <c r="B1973" s="13" t="s">
-        <v>1251</v>
+        <v>1296</v>
       </c>
       <c r="C1973" s="3">
         <v>0</v>
@@ -85068,7 +86017,7 @@
         <v>2043082199</v>
       </c>
       <c r="B1974" s="13" t="s">
-        <v>1252</v>
+        <v>1297</v>
       </c>
       <c r="C1974" s="3">
         <v>0</v>
@@ -85088,7 +86037,7 @@
         <v>2043092199</v>
       </c>
       <c r="B1975" s="13" t="s">
-        <v>1253</v>
+        <v>1298</v>
       </c>
       <c r="C1975" s="3">
         <v>0</v>
@@ -85108,7 +86057,7 @@
         <v>220799</v>
       </c>
       <c r="B1976" s="13" t="s">
-        <v>1254</v>
+        <v>1299</v>
       </c>
       <c r="C1976" s="3">
         <v>0</v>
@@ -85128,7 +86077,7 @@
         <v>2042082199</v>
       </c>
       <c r="B1977" s="13" t="s">
-        <v>1255</v>
+        <v>1300</v>
       </c>
       <c r="C1977" s="3">
         <v>0</v>
@@ -85148,7 +86097,7 @@
         <v>1280072599</v>
       </c>
       <c r="B1978" s="13" t="s">
-        <v>1256</v>
+        <v>1301</v>
       </c>
       <c r="C1978" s="3">
         <v>0</v>
@@ -85168,7 +86117,7 @@
         <v>221099</v>
       </c>
       <c r="B1979" s="13" t="s">
-        <v>1257</v>
+        <v>1302</v>
       </c>
       <c r="C1979" s="3">
         <v>0</v>
@@ -85188,7 +86137,7 @@
         <v>2042102199</v>
       </c>
       <c r="B1980" s="13" t="s">
-        <v>1258</v>
+        <v>1303</v>
       </c>
       <c r="C1980" s="3">
         <v>0</v>
@@ -85208,7 +86157,7 @@
         <v>221299</v>
       </c>
       <c r="B1981" s="13" t="s">
-        <v>1259</v>
+        <v>1304</v>
       </c>
       <c r="C1981" s="3">
         <v>0</v>
@@ -85228,7 +86177,7 @@
         <v>1280054599</v>
       </c>
       <c r="B1982" s="13" t="s">
-        <v>1260</v>
+        <v>1305</v>
       </c>
       <c r="C1982" s="3">
         <v>0</v>
@@ -85248,7 +86197,7 @@
         <v>221499</v>
       </c>
       <c r="B1983" s="13" t="s">
-        <v>1261</v>
+        <v>1306</v>
       </c>
       <c r="C1983" s="3">
         <v>0</v>
@@ -85268,7 +86217,7 @@
         <v>221599</v>
       </c>
       <c r="B1984" s="13" t="s">
-        <v>1262</v>
+        <v>1307</v>
       </c>
       <c r="C1984" s="3">
         <v>0</v>
@@ -85288,7 +86237,7 @@
         <v>221699</v>
       </c>
       <c r="B1985" s="13" t="s">
-        <v>1263</v>
+        <v>1308</v>
       </c>
       <c r="C1985" s="3">
         <v>0</v>
@@ -85348,7 +86297,7 @@
         <v>221599</v>
       </c>
       <c r="B1988" s="13" t="s">
-        <v>1262</v>
+        <v>1307</v>
       </c>
       <c r="C1988" s="3">
         <v>0</v>
@@ -85368,7 +86317,7 @@
         <v>222699</v>
       </c>
       <c r="B1989" s="13" t="s">
-        <v>1264</v>
+        <v>1309</v>
       </c>
       <c r="C1989" s="3">
         <v>0</v>
@@ -85388,7 +86337,7 @@
         <v>222799</v>
       </c>
       <c r="B1990" s="13" t="s">
-        <v>1265</v>
+        <v>1310</v>
       </c>
       <c r="C1990" s="3">
         <v>0</v>
@@ -85408,7 +86357,7 @@
         <v>2043102199</v>
       </c>
       <c r="B1991" s="13" t="s">
-        <v>1266</v>
+        <v>1311</v>
       </c>
       <c r="C1991" s="3">
         <v>0</v>
@@ -85908,7 +86857,7 @@
         <v>1280070599</v>
       </c>
       <c r="B2016" s="13" t="s">
-        <v>1267</v>
+        <v>1312</v>
       </c>
       <c r="C2016" s="3">
         <v>0</v>
@@ -85968,7 +86917,7 @@
         <v>1280051199</v>
       </c>
       <c r="B2019" s="13" t="s">
-        <v>1268</v>
+        <v>1313</v>
       </c>
       <c r="C2019" s="3">
         <v>0</v>
@@ -86088,7 +87037,7 @@
         <v>2061082199</v>
       </c>
       <c r="B2025" s="13" t="s">
-        <v>1269</v>
+        <v>1314</v>
       </c>
       <c r="C2025" s="3">
         <v>0</v>
@@ -86188,7 +87137,7 @@
         <v>1280068699</v>
       </c>
       <c r="B2030" s="13" t="s">
-        <v>1270</v>
+        <v>1315</v>
       </c>
       <c r="C2030" s="3">
         <v>0</v>
@@ -86288,7 +87237,7 @@
         <v>1280072199</v>
       </c>
       <c r="B2035" s="13" t="s">
-        <v>1271</v>
+        <v>1316</v>
       </c>
       <c r="C2035" s="3">
         <v>0</v>
@@ -86308,7 +87257,7 @@
         <v>2061102199</v>
       </c>
       <c r="B2036" s="13" t="s">
-        <v>1272</v>
+        <v>1317</v>
       </c>
       <c r="C2036" s="3">
         <v>0</v>
@@ -86328,7 +87277,7 @@
         <v>227599</v>
       </c>
       <c r="B2037" s="13" t="s">
-        <v>1273</v>
+        <v>1318</v>
       </c>
       <c r="C2037" s="3">
         <v>0</v>
@@ -86348,7 +87297,7 @@
         <v>1280037199</v>
       </c>
       <c r="B2038" s="13" t="s">
-        <v>1274</v>
+        <v>1319</v>
       </c>
       <c r="C2038" s="3">
         <v>0</v>
@@ -86368,7 +87317,7 @@
         <v>1280036199</v>
       </c>
       <c r="B2039" s="13" t="s">
-        <v>1275</v>
+        <v>1320</v>
       </c>
       <c r="C2039" s="3">
         <v>0</v>
@@ -86388,7 +87337,7 @@
         <v>2063082199</v>
       </c>
       <c r="B2040" s="13" t="s">
-        <v>1276</v>
+        <v>1321</v>
       </c>
       <c r="C2040" s="3">
         <v>0</v>
@@ -86408,7 +87357,7 @@
         <v>2063092199</v>
       </c>
       <c r="B2041" s="13" t="s">
-        <v>1277</v>
+        <v>1322</v>
       </c>
       <c r="C2041" s="3">
         <v>0</v>
@@ -86428,7 +87377,7 @@
         <v>228099</v>
       </c>
       <c r="B2042" s="13" t="s">
-        <v>1278</v>
+        <v>1323</v>
       </c>
       <c r="C2042" s="3">
         <v>0</v>
@@ -86448,7 +87397,7 @@
         <v>2062082199</v>
       </c>
       <c r="B2043" s="13" t="s">
-        <v>1279</v>
+        <v>1324</v>
       </c>
       <c r="C2043" s="3">
         <v>0</v>
@@ -86468,7 +87417,7 @@
         <v>1280072699</v>
       </c>
       <c r="B2044" s="13" t="s">
-        <v>1280</v>
+        <v>1325</v>
       </c>
       <c r="C2044" s="3">
         <v>0</v>
@@ -86488,7 +87437,7 @@
         <v>228399</v>
       </c>
       <c r="B2045" s="13" t="s">
-        <v>1281</v>
+        <v>1326</v>
       </c>
       <c r="C2045" s="3">
         <v>0</v>
@@ -86508,7 +87457,7 @@
         <v>2062102199</v>
       </c>
       <c r="B2046" s="13" t="s">
-        <v>1282</v>
+        <v>1327</v>
       </c>
       <c r="C2046" s="3">
         <v>0</v>
@@ -86528,7 +87477,7 @@
         <v>228599</v>
       </c>
       <c r="B2047" s="13" t="s">
-        <v>1283</v>
+        <v>1328</v>
       </c>
       <c r="C2047" s="3">
         <v>0</v>
@@ -86548,7 +87497,7 @@
         <v>228699</v>
       </c>
       <c r="B2048" s="13" t="s">
-        <v>1284</v>
+        <v>1329</v>
       </c>
       <c r="C2048" s="3">
         <v>0</v>
@@ -86568,7 +87517,7 @@
         <v>1280054699</v>
       </c>
       <c r="B2049" s="13" t="s">
-        <v>1285</v>
+        <v>1330</v>
       </c>
       <c r="C2049" s="3">
         <v>0</v>
@@ -86588,7 +87537,7 @@
         <v>228899</v>
       </c>
       <c r="B2050" s="13" t="s">
-        <v>1286</v>
+        <v>1331</v>
       </c>
       <c r="C2050" s="3">
         <v>0</v>
@@ -86608,7 +87557,7 @@
         <v>228999</v>
       </c>
       <c r="B2051" s="13" t="s">
-        <v>1287</v>
+        <v>1332</v>
       </c>
       <c r="C2051" s="3">
         <v>0</v>
@@ -86628,7 +87577,7 @@
         <v>229099</v>
       </c>
       <c r="B2052" s="13" t="s">
-        <v>1288</v>
+        <v>1333</v>
       </c>
       <c r="C2052" s="3">
         <v>0</v>
@@ -86648,7 +87597,7 @@
         <v>1280068699</v>
       </c>
       <c r="B2053" s="13" t="s">
-        <v>1270</v>
+        <v>1315</v>
       </c>
       <c r="C2053" s="3">
         <v>0</v>
@@ -86688,7 +87637,7 @@
         <v>228999</v>
       </c>
       <c r="B2055" s="13" t="s">
-        <v>1287</v>
+        <v>1332</v>
       </c>
       <c r="C2055" s="3">
         <v>0</v>
@@ -86708,7 +87657,7 @@
         <v>230099</v>
       </c>
       <c r="B2056" s="13" t="s">
-        <v>1289</v>
+        <v>1334</v>
       </c>
       <c r="C2056" s="3">
         <v>0</v>
@@ -86728,7 +87677,7 @@
         <v>230199</v>
       </c>
       <c r="B2057" s="13" t="s">
-        <v>1290</v>
+        <v>1335</v>
       </c>
       <c r="C2057" s="3">
         <v>0</v>
@@ -86748,7 +87697,7 @@
         <v>2063102199</v>
       </c>
       <c r="B2058" s="13" t="s">
-        <v>1291</v>
+        <v>1336</v>
       </c>
       <c r="C2058" s="3">
         <v>0</v>
@@ -86768,7 +87717,7 @@
         <v>230399</v>
       </c>
       <c r="B2059" s="13" t="s">
-        <v>1292</v>
+        <v>1337</v>
       </c>
       <c r="C2059" s="3">
         <v>0</v>
@@ -87348,7 +88297,7 @@
         <v>1280051299</v>
       </c>
       <c r="B2088" s="13" t="s">
-        <v>1293</v>
+        <v>1338</v>
       </c>
       <c r="C2088" s="3">
         <v>0</v>
@@ -87468,7 +88417,7 @@
         <v>2081082199</v>
       </c>
       <c r="B2094" s="13" t="s">
-        <v>1294</v>
+        <v>1339</v>
       </c>
       <c r="C2094" s="3">
         <v>0</v>
@@ -87648,7 +88597,7 @@
         <v>1280071799</v>
       </c>
       <c r="B2103" s="13" t="s">
-        <v>1295</v>
+        <v>1340</v>
       </c>
       <c r="C2103" s="3">
         <v>0</v>
@@ -87668,7 +88617,7 @@
         <v>1280072299</v>
       </c>
       <c r="B2104" s="13" t="s">
-        <v>1296</v>
+        <v>1341</v>
       </c>
       <c r="C2104" s="3">
         <v>0</v>
@@ -87688,7 +88637,7 @@
         <v>2081102199</v>
       </c>
       <c r="B2105" s="13" t="s">
-        <v>1297</v>
+        <v>1342</v>
       </c>
       <c r="C2105" s="3">
         <v>0</v>
@@ -87708,7 +88657,7 @@
         <v>235099</v>
       </c>
       <c r="B2106" s="13" t="s">
-        <v>1298</v>
+        <v>1343</v>
       </c>
       <c r="C2106" s="3">
         <v>0</v>
@@ -87728,7 +88677,7 @@
         <v>1280037299</v>
       </c>
       <c r="B2107" s="13" t="s">
-        <v>1299</v>
+        <v>1344</v>
       </c>
       <c r="C2107" s="3">
         <v>0</v>
@@ -87748,7 +88697,7 @@
         <v>1280036299</v>
       </c>
       <c r="B2108" s="13" t="s">
-        <v>1300</v>
+        <v>1345</v>
       </c>
       <c r="C2108" s="3">
         <v>0</v>
@@ -87768,7 +88717,7 @@
         <v>2083082199</v>
       </c>
       <c r="B2109" s="13" t="s">
-        <v>1301</v>
+        <v>1346</v>
       </c>
       <c r="C2109" s="3">
         <v>0</v>
@@ -87788,7 +88737,7 @@
         <v>2083092199</v>
       </c>
       <c r="B2110" s="13" t="s">
-        <v>1302</v>
+        <v>1347</v>
       </c>
       <c r="C2110" s="3">
         <v>0</v>
@@ -87808,7 +88757,7 @@
         <v>235599</v>
       </c>
       <c r="B2111" s="13" t="s">
-        <v>1303</v>
+        <v>1348</v>
       </c>
       <c r="C2111" s="3">
         <v>0</v>
@@ -87828,7 +88777,7 @@
         <v>2082082199</v>
       </c>
       <c r="B2112" s="13" t="s">
-        <v>1304</v>
+        <v>1349</v>
       </c>
       <c r="C2112" s="3">
         <v>0</v>
@@ -87848,7 +88797,7 @@
         <v>1280072799</v>
       </c>
       <c r="B2113" s="13" t="s">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="C2113" s="3">
         <v>0</v>
@@ -87868,7 +88817,7 @@
         <v>235899</v>
       </c>
       <c r="B2114" s="13" t="s">
-        <v>1306</v>
+        <v>1351</v>
       </c>
       <c r="C2114" s="3">
         <v>0</v>
@@ -87888,7 +88837,7 @@
         <v>2082102199</v>
       </c>
       <c r="B2115" s="13" t="s">
-        <v>1307</v>
+        <v>1352</v>
       </c>
       <c r="C2115" s="3">
         <v>0</v>
@@ -87908,7 +88857,7 @@
         <v>236099</v>
       </c>
       <c r="B2116" s="13" t="s">
-        <v>1308</v>
+        <v>1353</v>
       </c>
       <c r="C2116" s="3">
         <v>0</v>
@@ -87928,7 +88877,7 @@
         <v>236199</v>
       </c>
       <c r="B2117" s="13" t="s">
-        <v>1309</v>
+        <v>1354</v>
       </c>
       <c r="C2117" s="3">
         <v>0</v>
@@ -87948,7 +88897,7 @@
         <v>1280054799</v>
       </c>
       <c r="B2118" s="13" t="s">
-        <v>1310</v>
+        <v>1355</v>
       </c>
       <c r="C2118" s="3">
         <v>0</v>
@@ -87968,7 +88917,7 @@
         <v>236399</v>
       </c>
       <c r="B2119" s="13" t="s">
-        <v>1311</v>
+        <v>1356</v>
       </c>
       <c r="C2119" s="3">
         <v>0</v>
@@ -87988,7 +88937,7 @@
         <v>236499</v>
       </c>
       <c r="B2120" s="13" t="s">
-        <v>1312</v>
+        <v>1357</v>
       </c>
       <c r="C2120" s="3">
         <v>0</v>
@@ -88008,7 +88957,7 @@
         <v>236599</v>
       </c>
       <c r="B2121" s="13" t="s">
-        <v>1313</v>
+        <v>1358</v>
       </c>
       <c r="C2121" s="3">
         <v>0</v>
@@ -88068,7 +89017,7 @@
         <v>236499</v>
       </c>
       <c r="B2124" s="13" t="s">
-        <v>1312</v>
+        <v>1357</v>
       </c>
       <c r="C2124" s="3">
         <v>0</v>
@@ -88088,7 +89037,7 @@
         <v>237599</v>
       </c>
       <c r="B2125" s="13" t="s">
-        <v>1314</v>
+        <v>1359</v>
       </c>
       <c r="C2125" s="3">
         <v>0</v>
@@ -88108,7 +89057,7 @@
         <v>237699</v>
       </c>
       <c r="B2126" s="13" t="s">
-        <v>1315</v>
+        <v>1360</v>
       </c>
       <c r="C2126" s="3">
         <v>0</v>
@@ -88128,7 +89077,7 @@
         <v>2083102199</v>
       </c>
       <c r="B2127" s="13" t="s">
-        <v>1316</v>
+        <v>1361</v>
       </c>
       <c r="C2127" s="3">
         <v>0</v>
@@ -88148,7 +89097,7 @@
         <v>237899</v>
       </c>
       <c r="B2128" s="13" t="s">
-        <v>1317</v>
+        <v>1362</v>
       </c>
       <c r="C2128" s="3">
         <v>0</v>
@@ -88728,7 +89677,7 @@
         <v>1280051499</v>
       </c>
       <c r="B2157" s="13" t="s">
-        <v>1318</v>
+        <v>1363</v>
       </c>
       <c r="C2157" s="3">
         <v>0</v>
@@ -88848,7 +89797,7 @@
         <v>2071082199</v>
       </c>
       <c r="B2163" s="13" t="s">
-        <v>1319</v>
+        <v>1364</v>
       </c>
       <c r="C2163" s="3">
         <v>0</v>
@@ -89028,7 +89977,7 @@
         <v>1280071999</v>
       </c>
       <c r="B2172" s="13" t="s">
-        <v>1320</v>
+        <v>1365</v>
       </c>
       <c r="C2172" s="3">
         <v>0</v>
@@ -89048,7 +89997,7 @@
         <v>1280072499</v>
       </c>
       <c r="B2173" s="13" t="s">
-        <v>1321</v>
+        <v>1366</v>
       </c>
       <c r="C2173" s="3">
         <v>0</v>
@@ -89068,7 +90017,7 @@
         <v>2071102199</v>
       </c>
       <c r="B2174" s="13" t="s">
-        <v>1322</v>
+        <v>1367</v>
       </c>
       <c r="C2174" s="3">
         <v>0</v>
@@ -89088,7 +90037,7 @@
         <v>242599</v>
       </c>
       <c r="B2175" s="13" t="s">
-        <v>1323</v>
+        <v>1368</v>
       </c>
       <c r="C2175" s="3">
         <v>0</v>
@@ -89108,7 +90057,7 @@
         <v>1280037499</v>
       </c>
       <c r="B2176" s="13" t="s">
-        <v>1324</v>
+        <v>1369</v>
       </c>
       <c r="C2176" s="3">
         <v>0</v>
@@ -89128,7 +90077,7 @@
         <v>1280036499</v>
       </c>
       <c r="B2177" s="13" t="s">
-        <v>1325</v>
+        <v>1370</v>
       </c>
       <c r="C2177" s="3">
         <v>0</v>
@@ -89148,7 +90097,7 @@
         <v>2073082199</v>
       </c>
       <c r="B2178" s="13" t="s">
-        <v>1326</v>
+        <v>1371</v>
       </c>
       <c r="C2178" s="3">
         <v>0</v>
@@ -89168,7 +90117,7 @@
         <v>2073092199</v>
       </c>
       <c r="B2179" s="13" t="s">
-        <v>1327</v>
+        <v>1372</v>
       </c>
       <c r="C2179" s="3">
         <v>0</v>
@@ -89188,7 +90137,7 @@
         <v>243099</v>
       </c>
       <c r="B2180" s="13" t="s">
-        <v>1328</v>
+        <v>1373</v>
       </c>
       <c r="C2180" s="3">
         <v>0</v>
@@ -89208,7 +90157,7 @@
         <v>2072082199</v>
       </c>
       <c r="B2181" s="13" t="s">
-        <v>1329</v>
+        <v>1374</v>
       </c>
       <c r="C2181" s="3">
         <v>0</v>
@@ -89228,7 +90177,7 @@
         <v>1280072999</v>
       </c>
       <c r="B2182" s="13" t="s">
-        <v>1330</v>
+        <v>1375</v>
       </c>
       <c r="C2182" s="3">
         <v>0</v>
@@ -89248,7 +90197,7 @@
         <v>243399</v>
       </c>
       <c r="B2183" s="13" t="s">
-        <v>1331</v>
+        <v>1376</v>
       </c>
       <c r="C2183" s="3">
         <v>0</v>
@@ -89308,7 +90257,7 @@
         <v>244299</v>
       </c>
       <c r="B2186" s="13" t="s">
-        <v>1332</v>
+        <v>1377</v>
       </c>
       <c r="C2186" s="3">
         <v>0</v>
@@ -89328,7 +90277,7 @@
         <v>2073102199</v>
       </c>
       <c r="B2187" s="13" t="s">
-        <v>1333</v>
+        <v>1378</v>
       </c>
       <c r="C2187" s="3">
         <v>0</v>
@@ -89348,7 +90297,7 @@
         <v>244499</v>
       </c>
       <c r="B2188" s="13" t="s">
-        <v>1334</v>
+        <v>1379</v>
       </c>
       <c r="C2188" s="3">
         <v>0</v>
@@ -89928,7 +90877,7 @@
         <v>1280051399</v>
       </c>
       <c r="B2217" s="13" t="s">
-        <v>1335</v>
+        <v>1380</v>
       </c>
       <c r="C2217" s="3">
         <v>0</v>
@@ -90048,7 +90997,7 @@
         <v>2091082199</v>
       </c>
       <c r="B2223" s="13" t="s">
-        <v>1336</v>
+        <v>1381</v>
       </c>
       <c r="C2223" s="3">
         <v>0</v>
@@ -90248,7 +91197,7 @@
         <v>1280072399</v>
       </c>
       <c r="B2233" s="13" t="s">
-        <v>1337</v>
+        <v>1382</v>
       </c>
       <c r="C2233" s="3">
         <v>0</v>
@@ -90268,7 +91217,7 @@
         <v>2091102199</v>
       </c>
       <c r="B2234" s="13" t="s">
-        <v>1338</v>
+        <v>1383</v>
       </c>
       <c r="C2234" s="3">
         <v>0</v>
@@ -90288,7 +91237,7 @@
         <v>249199</v>
       </c>
       <c r="B2235" s="13" t="s">
-        <v>1339</v>
+        <v>1384</v>
       </c>
       <c r="C2235" s="3">
         <v>0</v>
@@ -90308,7 +91257,7 @@
         <v>1280037399</v>
       </c>
       <c r="B2236" s="13" t="s">
-        <v>1340</v>
+        <v>1385</v>
       </c>
       <c r="C2236" s="3">
         <v>0</v>
@@ -90328,7 +91277,7 @@
         <v>1280036399</v>
       </c>
       <c r="B2237" s="13" t="s">
-        <v>1341</v>
+        <v>1386</v>
       </c>
       <c r="C2237" s="3">
         <v>0</v>
@@ -90348,7 +91297,7 @@
         <v>2093082199</v>
       </c>
       <c r="B2238" s="13" t="s">
-        <v>1342</v>
+        <v>1387</v>
       </c>
       <c r="C2238" s="3">
         <v>0</v>
@@ -90368,7 +91317,7 @@
         <v>2093092199</v>
       </c>
       <c r="B2239" s="13" t="s">
-        <v>1343</v>
+        <v>1388</v>
       </c>
       <c r="C2239" s="3">
         <v>0</v>
@@ -90388,7 +91337,7 @@
         <v>249699</v>
       </c>
       <c r="B2240" s="13" t="s">
-        <v>1344</v>
+        <v>1389</v>
       </c>
       <c r="C2240" s="3">
         <v>0</v>
@@ -90408,7 +91357,7 @@
         <v>2092082199</v>
       </c>
       <c r="B2241" s="13" t="s">
-        <v>1345</v>
+        <v>1390</v>
       </c>
       <c r="C2241" s="3">
         <v>0</v>
@@ -90428,7 +91377,7 @@
         <v>1280072899</v>
       </c>
       <c r="B2242" s="13" t="s">
-        <v>1346</v>
+        <v>1391</v>
       </c>
       <c r="C2242" s="3">
         <v>0</v>
@@ -90448,7 +91397,7 @@
         <v>249999</v>
       </c>
       <c r="B2243" s="13" t="s">
-        <v>1347</v>
+        <v>1392</v>
       </c>
       <c r="C2243" s="3">
         <v>0</v>
@@ -90468,7 +91417,7 @@
         <v>2092102199</v>
       </c>
       <c r="B2244" s="13" t="s">
-        <v>1348</v>
+        <v>1393</v>
       </c>
       <c r="C2244" s="3">
         <v>0</v>
@@ -90488,7 +91437,7 @@
         <v>250199</v>
       </c>
       <c r="B2245" s="13" t="s">
-        <v>1349</v>
+        <v>1394</v>
       </c>
       <c r="C2245" s="3">
         <v>0</v>
@@ -90508,7 +91457,7 @@
         <v>250299</v>
       </c>
       <c r="B2246" s="13" t="s">
-        <v>1350</v>
+        <v>1395</v>
       </c>
       <c r="C2246" s="3">
         <v>0</v>
@@ -90528,7 +91477,7 @@
         <v>1280054899</v>
       </c>
       <c r="B2247" s="13" t="s">
-        <v>1351</v>
+        <v>1396</v>
       </c>
       <c r="C2247" s="3">
         <v>0</v>
@@ -90548,7 +91497,7 @@
         <v>250499</v>
       </c>
       <c r="B2248" s="13" t="s">
-        <v>1352</v>
+        <v>1397</v>
       </c>
       <c r="C2248" s="3">
         <v>0</v>
@@ -90568,7 +91517,7 @@
         <v>250599</v>
       </c>
       <c r="B2249" s="13" t="s">
-        <v>1353</v>
+        <v>1398</v>
       </c>
       <c r="C2249" s="3">
         <v>0</v>
@@ -90588,7 +91537,7 @@
         <v>250699</v>
       </c>
       <c r="B2250" s="13" t="s">
-        <v>1354</v>
+        <v>1399</v>
       </c>
       <c r="C2250" s="3">
         <v>0</v>
@@ -90648,7 +91597,7 @@
         <v>250599</v>
       </c>
       <c r="B2253" s="13" t="s">
-        <v>1353</v>
+        <v>1398</v>
       </c>
       <c r="C2253" s="3">
         <v>0</v>
@@ -90668,7 +91617,7 @@
         <v>251699</v>
       </c>
       <c r="B2254" s="13" t="s">
-        <v>1355</v>
+        <v>1400</v>
       </c>
       <c r="C2254" s="3">
         <v>0</v>
@@ -90688,7 +91637,7 @@
         <v>251799</v>
       </c>
       <c r="B2255" s="13" t="s">
-        <v>1356</v>
+        <v>1401</v>
       </c>
       <c r="C2255" s="3">
         <v>0</v>
@@ -90708,7 +91657,7 @@
         <v>2093102199</v>
       </c>
       <c r="B2256" s="13" t="s">
-        <v>1357</v>
+        <v>1402</v>
       </c>
       <c r="C2256" s="3">
         <v>0</v>
@@ -90728,7 +91677,7 @@
         <v>251999</v>
       </c>
       <c r="B2257" s="13" t="s">
-        <v>1358</v>
+        <v>1403</v>
       </c>
       <c r="C2257" s="3">
         <v>0</v>
@@ -90748,7 +91697,7 @@
         <v>2041013199</v>
       </c>
       <c r="B2258" s="12" t="s">
-        <v>1359</v>
+        <v>1404</v>
       </c>
       <c r="C2258" s="3">
         <v>0</v>
@@ -90768,7 +91717,7 @@
         <v>2061013199</v>
       </c>
       <c r="B2259" s="12" t="s">
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="C2259" s="3">
         <v>0</v>
@@ -90788,7 +91737,7 @@
         <v>2081013199</v>
       </c>
       <c r="B2260" s="12" t="s">
-        <v>1361</v>
+        <v>1406</v>
       </c>
       <c r="C2260" s="3">
         <v>0</v>
@@ -90808,7 +91757,7 @@
         <v>2071013199</v>
       </c>
       <c r="B2261" s="12" t="s">
-        <v>1362</v>
+        <v>1407</v>
       </c>
       <c r="C2261" s="3">
         <v>0</v>
@@ -90828,7 +91777,7 @@
         <v>2091013199</v>
       </c>
       <c r="B2262" s="12" t="s">
-        <v>1363</v>
+        <v>1408</v>
       </c>
       <c r="C2262" s="3">
         <v>0</v>
@@ -90868,7 +91817,7 @@
         <v>252699</v>
       </c>
       <c r="B2264" s="12" t="s">
-        <v>1364</v>
+        <v>1409</v>
       </c>
       <c r="C2264" s="3">
         <v>0</v>
@@ -90888,7 +91837,7 @@
         <v>252799</v>
       </c>
       <c r="B2265" s="12" t="s">
-        <v>1365</v>
+        <v>1410</v>
       </c>
       <c r="C2265" s="3">
         <v>0</v>
@@ -90928,7 +91877,7 @@
         <v>252999</v>
       </c>
       <c r="B2267" s="12" t="s">
-        <v>1366</v>
+        <v>1411</v>
       </c>
       <c r="C2267" s="3">
         <v>0</v>
@@ -90948,7 +91897,7 @@
         <v>253099</v>
       </c>
       <c r="B2268" s="12" t="s">
-        <v>1367</v>
+        <v>1412</v>
       </c>
       <c r="C2268" s="3">
         <v>0</v>
@@ -90968,7 +91917,7 @@
         <v>253199</v>
       </c>
       <c r="B2269" s="12" t="s">
-        <v>1368</v>
+        <v>1413</v>
       </c>
       <c r="C2269" s="3">
         <v>0</v>
@@ -90988,7 +91937,7 @@
         <v>253299</v>
       </c>
       <c r="B2270" s="12" t="s">
-        <v>1369</v>
+        <v>1414</v>
       </c>
       <c r="C2270" s="3">
         <v>0</v>
@@ -91068,7 +92017,7 @@
         <v>2061023199</v>
       </c>
       <c r="B2274" s="12" t="s">
-        <v>1370</v>
+        <v>1415</v>
       </c>
       <c r="C2274" s="3">
         <v>0</v>
@@ -91088,7 +92037,7 @@
         <v>2081023199</v>
       </c>
       <c r="B2275" s="12" t="s">
-        <v>1371</v>
+        <v>1416</v>
       </c>
       <c r="C2275" s="3">
         <v>0</v>
@@ -91108,7 +92057,7 @@
         <v>2071023199</v>
       </c>
       <c r="B2276" s="12" t="s">
-        <v>1372</v>
+        <v>1417</v>
       </c>
       <c r="C2276" s="3">
         <v>0</v>
@@ -91128,7 +92077,7 @@
         <v>2091023199</v>
       </c>
       <c r="B2277" s="12" t="s">
-        <v>1373</v>
+        <v>1418</v>
       </c>
       <c r="C2277" s="3">
         <v>0</v>
@@ -91168,7 +92117,7 @@
         <v>2061033199</v>
       </c>
       <c r="B2279" s="12" t="s">
-        <v>1374</v>
+        <v>1419</v>
       </c>
       <c r="C2279" s="3">
         <v>0</v>
@@ -91208,7 +92157,7 @@
         <v>2071033199</v>
       </c>
       <c r="B2281" s="12" t="s">
-        <v>1375</v>
+        <v>1420</v>
       </c>
       <c r="C2281" s="3">
         <v>0</v>
@@ -91228,7 +92177,7 @@
         <v>2091033199</v>
       </c>
       <c r="B2282" s="12" t="s">
-        <v>1376</v>
+        <v>1421</v>
       </c>
       <c r="C2282" s="3">
         <v>0</v>
@@ -91348,7 +92297,7 @@
         <v>2042013199</v>
       </c>
       <c r="B2288" s="12" t="s">
-        <v>1377</v>
+        <v>1422</v>
       </c>
       <c r="C2288" s="3">
         <v>0</v>
@@ -91368,7 +92317,7 @@
         <v>2062013199</v>
       </c>
       <c r="B2289" s="12" t="s">
-        <v>1378</v>
+        <v>1423</v>
       </c>
       <c r="C2289" s="3">
         <v>0</v>
@@ -91388,7 +92337,7 @@
         <v>2082013199</v>
       </c>
       <c r="B2290" s="12" t="s">
-        <v>1379</v>
+        <v>1424</v>
       </c>
       <c r="C2290" s="3">
         <v>0</v>
@@ -91408,7 +92357,7 @@
         <v>2072013199</v>
       </c>
       <c r="B2291" s="12" t="s">
-        <v>1380</v>
+        <v>1425</v>
       </c>
       <c r="C2291" s="3">
         <v>0</v>
@@ -91548,7 +92497,7 @@
         <v>2042033199</v>
       </c>
       <c r="B2298" s="12" t="s">
-        <v>1381</v>
+        <v>1426</v>
       </c>
       <c r="C2298" s="3">
         <v>0</v>
@@ -91568,7 +92517,7 @@
         <v>2062033199</v>
       </c>
       <c r="B2299" s="12" t="s">
-        <v>1382</v>
+        <v>1427</v>
       </c>
       <c r="C2299" s="3">
         <v>0</v>
@@ -91588,7 +92537,7 @@
         <v>2082033199</v>
       </c>
       <c r="B2300" s="12" t="s">
-        <v>1383</v>
+        <v>1428</v>
       </c>
       <c r="C2300" s="3">
         <v>0</v>
@@ -91608,7 +92557,7 @@
         <v>2072033199</v>
       </c>
       <c r="B2301" s="12" t="s">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="C2301" s="3">
         <v>0</v>
@@ -91628,7 +92577,7 @@
         <v>2092033199</v>
       </c>
       <c r="B2302" s="12" t="s">
-        <v>1385</v>
+        <v>1430</v>
       </c>
       <c r="C2302" s="3">
         <v>0</v>
@@ -91848,7 +92797,7 @@
         <v>2043023199</v>
       </c>
       <c r="B2313" s="12" t="s">
-        <v>1386</v>
+        <v>1431</v>
       </c>
       <c r="C2313" s="3">
         <v>0</v>
@@ -91868,7 +92817,7 @@
         <v>2063023199</v>
       </c>
       <c r="B2314" s="12" t="s">
-        <v>1387</v>
+        <v>1432</v>
       </c>
       <c r="C2314" s="3">
         <v>0</v>
@@ -91888,7 +92837,7 @@
         <v>2083023199</v>
       </c>
       <c r="B2315" s="12" t="s">
-        <v>1388</v>
+        <v>1433</v>
       </c>
       <c r="C2315" s="3">
         <v>0</v>
@@ -91908,7 +92857,7 @@
         <v>2073023199</v>
       </c>
       <c r="B2316" s="12" t="s">
-        <v>1389</v>
+        <v>1434</v>
       </c>
       <c r="C2316" s="3">
         <v>0</v>
@@ -92068,7 +93017,7 @@
         <v>258699</v>
       </c>
       <c r="B2324" s="12" t="s">
-        <v>1390</v>
+        <v>1435</v>
       </c>
       <c r="C2324" s="3">
         <v>0</v>
@@ -92088,7 +93037,7 @@
         <v>258799</v>
       </c>
       <c r="B2325" s="12" t="s">
-        <v>1391</v>
+        <v>1436</v>
       </c>
       <c r="C2325" s="3">
         <v>0</v>
@@ -92108,7 +93057,7 @@
         <v>258899</v>
       </c>
       <c r="B2326" s="12" t="s">
-        <v>1392</v>
+        <v>1437</v>
       </c>
       <c r="C2326" s="3">
         <v>0</v>
@@ -92148,7 +93097,7 @@
         <v>2043043199</v>
       </c>
       <c r="B2328" s="12" t="s">
-        <v>1393</v>
+        <v>1438</v>
       </c>
       <c r="C2328" s="3">
         <v>0</v>
@@ -92168,7 +93117,7 @@
         <v>2063043199</v>
       </c>
       <c r="B2329" s="12" t="s">
-        <v>1394</v>
+        <v>1439</v>
       </c>
       <c r="C2329" s="3">
         <v>0</v>
@@ -92188,7 +93137,7 @@
         <v>2083043199</v>
       </c>
       <c r="B2330" s="12" t="s">
-        <v>1395</v>
+        <v>1440</v>
       </c>
       <c r="C2330" s="3">
         <v>0</v>
@@ -92208,7 +93157,7 @@
         <v>2073043199</v>
       </c>
       <c r="B2331" s="12" t="s">
-        <v>1396</v>
+        <v>1441</v>
       </c>
       <c r="C2331" s="3">
         <v>0</v>
@@ -92228,7 +93177,7 @@
         <v>2093043199</v>
       </c>
       <c r="B2332" s="12" t="s">
-        <v>1397</v>
+        <v>1442</v>
       </c>
       <c r="C2332" s="3">
         <v>0</v>
@@ -92448,7 +93397,7 @@
         <v>101534399</v>
       </c>
       <c r="B2343" s="19" t="s">
-        <v>1398</v>
+        <v>1443</v>
       </c>
       <c r="C2343" s="3">
         <v>0</v>
